--- a/tame_output/ON/bt/strategyON_20240703.xlsx
+++ b/tame_output/ON/bt/strategyON_20240703.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>57.2%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.4%</t>
+          <t>-73.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.9%</t>
+          <t>94.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.5%</t>
+          <t>-49.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.9%</t>
+          <t>-68.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>451.4%</t>
+          <t>452.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-528.1%</t>
+          <t>-527.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,32 +1140,32 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.2%</t>
+          <t>-37.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-39.0%</t>
+          <t>-39.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-165.6%</t>
+          <t>-165.3%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.2%</t>
+          <t>-31.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-14.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-171.6%</t>
+          <t>-170.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-215.2%</t>
+          <t>-214.6%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-26.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-83.5%</t>
+          <t>-83.1%</t>
         </is>
       </c>
     </row>
@@ -47413,16 +47413,16 @@
         <v>3.14834383409649</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.803873741529084</v>
+        <v>-3.787118617365016</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.626437913171109</v>
+        <v>1.633139962836736</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.153428384757457</v>
+        <v>0.1601107170171605</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.240400864950964</v>
+        <v>3.244410264306786</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.165898239823281</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.794981280135801</v>
+        <v>-3.778226155971733</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.647549303455214</v>
+        <v>1.654251353120841</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.153428384757457</v>
+        <v>0.1601107170171605</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.257955270677756</v>
+        <v>3.261964670033578</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.157753287227865</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.963457397105679</v>
+        <v>-3.94670227294161</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.572013904071846</v>
+        <v>1.578715953737474</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1254805490408762</v>
+        <v>0.1321628813005797</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.233041616652391</v>
+        <v>3.237051016008213</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.139022984415727</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.265657868244095</v>
+        <v>-3.248902744080027</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.832403412804342</v>
+        <v>1.839105462469969</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.05513248967046552</v>
+        <v>0.06181482193016902</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.172102478218006</v>
+        <v>3.176111877573828</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.129687006912631</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.242936764560943</v>
+        <v>-3.226181640396875</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.832155876774507</v>
+        <v>1.838857926440134</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.05513248967046552</v>
+        <v>0.06181482193016902</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.162766500714911</v>
+        <v>3.166775900070733</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.2885931327638</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.241211721270899</v>
+        <v>-3.224456597106831</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.991752019941694</v>
+        <v>1.998454069607321</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.05685753296050927</v>
+        <v>0.06353986522021277</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.322707652540106</v>
+        <v>3.326717051895928</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.325670955257447</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.395992728049154</v>
+        <v>-3.379237603885086</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.966917439724038</v>
+        <v>1.973619489389665</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.02348985890603317</v>
+        <v>0.03017219116573666</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.339764870601067</v>
+        <v>3.34377426995689</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.322346311246992</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.344557394664494</v>
+        <v>-3.327802270500426</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.984166929067447</v>
+        <v>1.990868978733074</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.07492519229069283</v>
+        <v>0.08160752455039633</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.367301426621408</v>
+        <v>3.37131082597723</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.332352464891734</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.317606170338006</v>
+        <v>-3.300851046173938</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.004953572442784</v>
+        <v>2.011655622108411</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.08980553831841198</v>
+        <v>0.09648787057811548</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.386235787882781</v>
+        <v>3.390245187238603</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.516455597036694</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.453559178394323</v>
+        <v>-3.436804054230254</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.134675501365217</v>
+        <v>2.141377551030844</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.08980553831841198</v>
+        <v>0.09648787057811548</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.570338920027741</v>
+        <v>3.574348319383563</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.508572291939687</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.475967296199195</v>
+        <v>-3.459212172035127</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.117828949146261</v>
+        <v>2.124530998811889</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.08980553831841198</v>
+        <v>0.09648787057811548</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.562455614930734</v>
+        <v>3.566465014286556</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.510626291489324</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.623973063678594</v>
+        <v>-3.503617852537541</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.060680641704139</v>
+        <v>2.10882272616056</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.003078529454870527</v>
+        <v>0.07095471891576455</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.512473409162247</v>
+        <v>3.553199122838783</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.566880009211171</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.633413989567124</v>
+        <v>-3.513058778426071</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.113157989070574</v>
+        <v>2.161300073526995</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.1255056469982619</v>
+        <v>0.193381836459156</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.642183397410129</v>
+        <v>3.682909111086665</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.569771103756472</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.632127226027568</v>
+        <v>-3.511772014886515</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.116563789031698</v>
+        <v>2.164705873488119</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.1267924105378185</v>
+        <v>0.1946685999987126</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.645846550079164</v>
+        <v>3.6865722637557</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.567882916650247</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.633684280016859</v>
+        <v>-3.513329068875806</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.114052780329756</v>
+        <v>2.162194864786177</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.1267924105378185</v>
+        <v>0.1946685999987126</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.643958362972939</v>
+        <v>3.684684076649475</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.56270314625311</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.640956165540324</v>
+        <v>-3.520600954399271</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.105964255723233</v>
+        <v>2.154106340179654</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.1195205250143538</v>
+        <v>0.1873967144752478</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.634415461261722</v>
+        <v>3.675141174938259</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.561137156463262</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.639115146482073</v>
+        <v>-3.518759935341019</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.105134673556686</v>
+        <v>2.153276758013107</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.1207887516858222</v>
+        <v>0.1886649411467162</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.633610407474755</v>
+        <v>3.674336121151292</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.574210563329181</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.646023851981753</v>
+        <v>-3.5256686408407</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.115444598222732</v>
+        <v>2.163586682679153</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.1207887516858222</v>
+        <v>0.1886649411467162</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.646683814340674</v>
+        <v>3.687409528017211</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.574210563329181</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.647585494796613</v>
+        <v>-3.52723028365556</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.114819941096788</v>
+        <v>2.16296202555321</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.1207887516858222</v>
+        <v>0.1886649411467162</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.646683814340674</v>
+        <v>3.687409528017211</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.720648061639954</v>
+        <v>3.852945727666548</v>
       </c>
       <c r="C2013" t="n">
         <v>3.572734604456183</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.664864442645413</v>
+        <v>-3.658673204014194</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.10643240308427</v>
+        <v>2.108908898536757</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.08794417339456062</v>
+        <v>0.0938183289566456</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.625501108492919</v>
+        <v>3.62902560183017</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240703.xlsx
+++ b/tame_output/ON/bt/strategyON_20240703.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>16.8%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.3%</t>
+          <t>-73.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>109.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>124.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.9%</t>
+          <t>-50.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.6%</t>
+          <t>-70.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.0%</t>
+          <t>447.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-527.4%</t>
+          <t>-532.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.5%</t>
+          <t>-38.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-39.1%</t>
+          <t>-46.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-165.3%</t>
+          <t>-167.3%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.3%</t>
+          <t>-22.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.5%</t>
+          <t>-31.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.1%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-170.4%</t>
+          <t>-174.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-214.6%</t>
+          <t>-222.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-26.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-83.1%</t>
+          <t>-87.6%</t>
         </is>
       </c>
     </row>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355689</v>
+        <v>3.311888301355688</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279813</v>
+        <v>3.385382209279812</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082123</v>
+        <v>3.299560092082122</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757921</v>
+        <v>3.29349053375792</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760739</v>
+        <v>3.293766719760738</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296836</v>
+        <v>3.299918119296835</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201487</v>
+        <v>3.295507330201486</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153006</v>
+        <v>3.258791981153005</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207813</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191737</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.30502326510864</v>
+        <v>3.305023265108639</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097821</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094117</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199287</v>
+        <v>3.405960511199286</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969594</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297749</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539466</v>
+        <v>3.501052558539465</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937501</v>
+        <v>3.4924487119375</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141704</v>
+        <v>3.502790399141703</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729893</v>
+        <v>3.496851904729892</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440636</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608602</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297401</v>
+        <v>3.4921016412974</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322546</v>
+        <v>3.573674025322545</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158924</v>
+        <v>3.600038265158923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940722</v>
+        <v>3.691571733940721</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770583</v>
+        <v>3.676841549770582</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615287</v>
+        <v>3.685161381615286</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646221</v>
+        <v>3.71093553364622</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611572</v>
+        <v>3.768951674611571</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955332</v>
+        <v>3.728577929955331</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436234</v>
+        <v>3.766317079436233</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311954</v>
+        <v>3.784684521311953</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.80082935409725</v>
+        <v>3.800829354097249</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017778</v>
+        <v>3.789311112017777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388735</v>
+        <v>3.839374447388733</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626481</v>
+        <v>3.856161751626479</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291817</v>
+        <v>3.787330429291815</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785793</v>
+        <v>3.80163712278579</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390433</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105957</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960992</v>
+        <v>3.75388257196099</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607651</v>
+        <v>3.692931855607648</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.77042258398791</v>
+        <v>3.770422583987907</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710817</v>
+        <v>3.760333686710815</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.72356622940921</v>
+        <v>3.723566229409208</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098115</v>
+        <v>3.729969716098112</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.415011912359931</v>
+        <v>-7.328957195843939</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.01439839550936384</v>
+        <v>0.02002349109703294</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.431940725828709</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493426</v>
+        <v>3.782922533493423</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.172863518906072</v>
+        <v>-7.086808802390081</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.09692331625332251</v>
+        <v>0.1313452028597193</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.431940725828709</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722822</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.064604381783551</v>
+        <v>-6.978549665267559</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1347590915615262</v>
+        <v>0.169180978167923</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.431940725828709</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792051</v>
+        <v>3.828052928792048</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.94131324696642</v>
+        <v>-6.855258530450429</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1815736394989558</v>
+        <v>0.2159955261053521</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.308649591011578</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919913</v>
+        <v>3.81245367891991</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.920164048062976</v>
+        <v>-6.834109331546985</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1977342972976581</v>
+        <v>0.2321561839040545</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.287500392108135</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318099</v>
+        <v>3.748328408318097</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.676398606079532</v>
+        <v>-6.590343889563541</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2910211824380866</v>
+        <v>0.3254430690444829</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.287500392108135</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057532</v>
+        <v>3.82431123305753</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.574635785802237</v>
+        <v>-6.488581069286246</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3338506244690205</v>
+        <v>0.3682725110754168</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.274281323715706</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279192</v>
+        <v>3.826354974279189</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.324785391853163</v>
+        <v>-6.238730675337171</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4265328570323526</v>
+        <v>0.4609547436387489</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.274281323715706</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011505</v>
+        <v>3.835957987011502</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.14889329938573</v>
+        <v>-6.062838582869739</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5004888175399742</v>
+        <v>0.5349107041463705</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.274281323715706</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392994</v>
+        <v>3.780933911392991</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.977446836363266</v>
+        <v>-5.891392119847276</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5823949088035136</v>
+        <v>0.6168167954099095</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.102834860693243</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632789</v>
+        <v>3.773765222632785</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.903157270624927</v>
+        <v>-5.817102554108937</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6111312127151463</v>
+        <v>0.6455530993215421</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.028545294954904</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883081</v>
+        <v>3.764617879883078</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.839521528390993</v>
+        <v>-5.753466811875002</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6412803106630371</v>
+        <v>0.6757021972694335</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.9649095527209691</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074792</v>
+        <v>3.798814771074788</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.728094769065073</v>
+        <v>-5.642040052549082</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6670452731772007</v>
+        <v>0.7014671597835971</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.9649095527209691</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242303</v>
+        <v>3.7976948842423</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.487664272260212</v>
+        <v>-5.401609555744222</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7649605485240225</v>
+        <v>0.7993824351304184</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.7244790559161088</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367694</v>
+        <v>3.82159350936769</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.415421704089018</v>
+        <v>-5.329366987573027</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7977868896273206</v>
+        <v>0.8322087762337165</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.7244790559161088</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879975</v>
+        <v>3.822326997879971</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.36242338180763</v>
+        <v>-5.276368665291639</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8196648024572157</v>
+        <v>0.8540866890636116</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.66914279691417</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502347</v>
+        <v>3.848616626502343</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.253618496327903</v>
+        <v>-5.167563779811912</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8601848278690998</v>
+        <v>0.8946067144754961</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.66914279691417</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675948</v>
+        <v>3.818668951675945</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.033597698290892</v>
+        <v>-4.947542981774902</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9497721840945181</v>
+        <v>0.9841940707009145</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.5279229518461898</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539959</v>
+        <v>3.843274527539956</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.900730009227614</v>
+        <v>-4.814675292711624</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.018813442521653</v>
+        <v>1.053235329128049</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.5279229518461898</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496267</v>
+        <v>3.845047386496264</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.780556925863116</v>
+        <v>-4.694502209347125</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.068028520307754</v>
+        <v>1.10245040691415</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4077498684816908</v>
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577004</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.635884780763378</v>
+        <v>-4.586019929937089</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.135985480909089</v>
+        <v>1.155931421239604</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2630777233819534</v>
+        <v>-0.2992675890716551</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.832849183499015</v>
+        <v>2.811135264085195</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942109</v>
+        <v>3.735839222942105</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.695759608121071</v>
+        <v>-4.645894757294782</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.098073041367438</v>
+        <v>1.118018981697953</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3229525507396455</v>
+        <v>-0.3591424164293472</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.782961778485826</v>
+        <v>2.761247859072005</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674521</v>
+        <v>3.762647477674517</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.608960110342062</v>
+        <v>-4.559095259515773</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.155193333801607</v>
+        <v>1.175139274132123</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3229525507396455</v>
+        <v>-0.3591424164293472</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.805362271808392</v>
+        <v>2.783648352394571</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.7291463984307</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.611429816803868</v>
+        <v>-4.561564965977579</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.154277852590297</v>
+        <v>1.174223792920813</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3254222572014517</v>
+        <v>-0.3616121228911534</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.803952849304721</v>
+        <v>2.7822389298909</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003609</v>
+        <v>3.743220196003605</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.679800003127879</v>
+        <v>-4.62993515230159</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.137936700535395</v>
+        <v>1.15788264086591</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3161465581652367</v>
+        <v>-0.3523364238549384</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.820525191201152</v>
+        <v>2.798811271787331</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508377</v>
+        <v>3.714179139508373</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.693588055974925</v>
+        <v>-4.643723205148636</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.122858188028467</v>
+        <v>1.142804128358983</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3161465581652367</v>
+        <v>-0.3523364238549384</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.810961899833043</v>
+        <v>2.789247980419222</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417712</v>
+        <v>3.710906731417708</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.724581215303631</v>
+        <v>-4.674716364477342</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9351704893373722</v>
+        <v>0.9551164296678878</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3161465581652367</v>
+        <v>-0.3523364238549384</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.63567146487343</v>
+        <v>2.613957545459609</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205908</v>
+        <v>3.746042526205905</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.549106955511162</v>
+        <v>-4.499242104684873</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.009927425246147</v>
+        <v>1.029873365576663</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3161465581652367</v>
+        <v>-0.3523364238549384</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.640238696865218</v>
+        <v>2.618524777451396</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225453</v>
+        <v>3.765024323225449</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.660043208152411</v>
+        <v>-4.610178357326122</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.941294952950855</v>
+        <v>0.9612408932813705</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3161465581652367</v>
+        <v>-0.3523364238549384</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.615980725626425</v>
+        <v>2.594266806212604</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111302</v>
+        <v>3.773210297111298</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.626379662680129</v>
+        <v>-4.57651481185384</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9578917563596734</v>
+        <v>0.9778376966901889</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2824830126929549</v>
+        <v>-0.3186728783826566</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.6393102381297</v>
+        <v>2.617596318715878</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264171</v>
+        <v>3.784343952264168</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.566527043476405</v>
+        <v>-4.516662192650116</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9920051904732949</v>
+        <v>1.01195113080381</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2824830126929549</v>
+        <v>-0.3186728783826566</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.649482624561832</v>
+        <v>2.627768705148011</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742308</v>
+        <v>3.786949957742304</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.480283580450028</v>
+        <v>-4.430418729623739</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.021448846257706</v>
+        <v>1.041394786588222</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2824830126929549</v>
+        <v>-0.3186728783826566</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.644428895135692</v>
+        <v>2.622714975721871</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316054</v>
+        <v>3.75202749931605</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.525590399849007</v>
+        <v>-4.475725549022719</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9951018939426399</v>
+        <v>1.015047834273155</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3232931757021857</v>
+        <v>-0.3594830413918874</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.611718572774679</v>
+        <v>2.590004653360858</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.7535711658032</v>
+        <v>3.753571165803194</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.554623504551309</v>
+        <v>-4.50475865372502</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9840405250948212</v>
+        <v>1.003986465425337</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3232931757021857</v>
+        <v>-0.3594830413918874</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.612270445807781</v>
+        <v>2.59055652639396</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809506</v>
+        <v>3.733390600809502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.461813023100449</v>
+        <v>-4.41194817227416</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9504374095665307</v>
+        <v>0.9703833498970462</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2304826942513263</v>
+        <v>-0.266672559941028</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.597229426569662</v>
+        <v>2.575515507155841</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560433</v>
+        <v>3.748285816560428</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.506202492429876</v>
+        <v>-4.456337641603588</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9345550977593604</v>
+        <v>0.954501038089876</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.274872163580754</v>
+        <v>-0.3110620292704557</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.572469220896606</v>
+        <v>2.550755301482785</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472746</v>
+        <v>3.721077195472741</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.393531274193626</v>
+        <v>-4.343666423367337</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9746992935655836</v>
+        <v>0.9946452338960992</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1622009453445038</v>
+        <v>-0.1983908110342055</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.635147660350079</v>
+        <v>2.613433740936258</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798545</v>
+        <v>3.743047603798541</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.281154273010953</v>
+        <v>-4.231289422184664</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.02514138986932</v>
+        <v>1.045087330199836</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1622009453445038</v>
+        <v>-0.1983908110342055</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.640638956180747</v>
+        <v>2.618925036766925</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498873</v>
+        <v>3.689597840498869</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.308934670912306</v>
+        <v>-4.259069820086017</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.025526432477318</v>
+        <v>1.045472372807833</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1899813432458569</v>
+        <v>-0.2261712089355585</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.635467919208474</v>
+        <v>2.613753999794653</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705334</v>
+        <v>3.64306962170533</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.391935951937585</v>
+        <v>-4.342071101111296</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8306816400678596</v>
+        <v>0.8506275803983752</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2085522277730306</v>
+        <v>-0.2447420934627323</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.462681108492823</v>
+        <v>2.440967189079002</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729278</v>
+        <v>3.682716310729274</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.500550030380916</v>
+        <v>-4.450685179554627</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9073856694097329</v>
+        <v>0.9273316097402484</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2085522277730306</v>
+        <v>-0.2447420934627323</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.582830769212028</v>
+        <v>2.561116849798208</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190778</v>
+        <v>3.733012441190773</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.465140992132773</v>
+        <v>-4.415276141306484</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9360623108113129</v>
+        <v>0.9560082511418284</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2085522277730306</v>
+        <v>-0.2447420934627323</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.597343795314351</v>
+        <v>2.57562987590053</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913435</v>
+        <v>3.741174069913431</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.426757329574622</v>
+        <v>-4.376892478748333</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9488352171769421</v>
+        <v>0.9687811575074576</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1701685652148794</v>
+        <v>-0.2063584309045811</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.617793434191611</v>
+        <v>2.59607951477779</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532496</v>
+        <v>3.751147197532491</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.249640999539456</v>
+        <v>-4.199776148713167</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.016410778036311</v>
+        <v>1.036356718366826</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1701685652148794</v>
+        <v>-0.2063584309045811</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.614522463036913</v>
+        <v>2.592808543623092</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793913</v>
+        <v>3.741328448793909</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.294733244373002</v>
+        <v>-4.244868393546713</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9990572718648052</v>
+        <v>1.019003212195321</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2320646083842692</v>
+        <v>-0.2682544740739709</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.578068228897192</v>
+        <v>2.556354309483371</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011246</v>
+        <v>3.750729377011242</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.115357823134234</v>
+        <v>-4.065492972307945</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.064594415666727</v>
+        <v>1.084540355997242</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.07528785021355056</v>
+        <v>-0.1114777159032522</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.665921259106037</v>
+        <v>2.644207339692216</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898224</v>
+        <v>3.716991718982236</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.16037203665484</v>
+        <v>-4.110507185828551</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.027396185590074</v>
+        <v>1.04734212592059</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1056367455281552</v>
+        <v>-0.1418266112178568</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.628519377248864</v>
+        <v>2.606805457835044</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509549</v>
+        <v>3.737026608509544</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.427376546927275</v>
+        <v>-4.377511696100986</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9262859438200459</v>
+        <v>0.9462318841505615</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2999997835711037</v>
+        <v>-0.3361896492608054</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.517593116762041</v>
+        <v>2.49587919734822</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476082</v>
+        <v>3.702309454760815</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.528574328364448</v>
+        <v>-4.478709477538159</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8850107531416782</v>
+        <v>0.9049566934721938</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3684085971164229</v>
+        <v>-0.4045984628061246</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.475751750531351</v>
+        <v>2.45403783111753</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815464</v>
+        <v>3.705571661815459</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.522063361750135</v>
+        <v>-4.472198510923846</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.88521510134172</v>
+        <v>0.9051610416722355</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3684085971164229</v>
+        <v>-0.4045984628061246</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.473351712085668</v>
+        <v>2.451637792671847</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378107</v>
+        <v>3.709510443378104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.503025234042838</v>
+        <v>-4.453160383216549</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8893550716328837</v>
+        <v>0.9093010119633993</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4265922084476175</v>
+        <v>-0.4627820741373191</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.434966264495196</v>
+        <v>2.413252345081375</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131259</v>
+        <v>3.731064473131255</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.534151865193456</v>
+        <v>-4.484287014367167</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.054486288111317</v>
+        <v>1.074432228441833</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4265922084476175</v>
+        <v>-0.4627820741373191</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.612548133433877</v>
+        <v>2.590834214020056</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067875</v>
+        <v>3.722447362067872</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.548018626527374</v>
+        <v>-4.498153775701085</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.049772912563883</v>
+        <v>1.069718852894399</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4644501251814404</v>
+        <v>-0.5006399908711421</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.590666712379716</v>
+        <v>2.568952792965895</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789131</v>
+        <v>3.787425580789128</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.503214454987444</v>
+        <v>-4.453349604161155</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.073703111576781</v>
+        <v>1.093649051907297</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4644501251814404</v>
+        <v>-0.5006399908711421</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.596675242776642</v>
+        <v>2.574961323362821</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519918</v>
+        <v>3.781501250519915</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.355471484752441</v>
+        <v>-4.305606633926153</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.211952947462804</v>
+        <v>1.23189888779332</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2966427679465573</v>
+        <v>-0.3328326336362589</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.776512304909594</v>
+        <v>2.754798385495773</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918118</v>
+        <v>3.802245929181177</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.457486167283663</v>
+        <v>-4.407621316457374</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.173940695981797</v>
+        <v>1.193886636312312</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2966427679465573</v>
+        <v>-0.3328326336362589</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.779305926441075</v>
+        <v>2.757592007027254</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539474</v>
+        <v>3.805608985394737</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.451333461230878</v>
+        <v>-4.401468610404589</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.177064126794569</v>
+        <v>1.197010067125084</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.290490061893773</v>
+        <v>-0.3266799275834746</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.783659898464404</v>
+        <v>2.761945979050583</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890617</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.46814275938138</v>
+        <v>-4.418277908555091</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.169420884274478</v>
+        <v>1.189366824604994</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3072993600442746</v>
+        <v>-0.3434892257339763</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.772654796314213</v>
+        <v>2.750940876900392</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798434</v>
+        <v>3.867362636798431</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.405844760605258</v>
+        <v>-4.355979909778969</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.260675637581748</v>
+        <v>1.280621577912264</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3072993600442746</v>
+        <v>-0.3434892257339763</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.838990350111034</v>
+        <v>2.817276430697213</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992201</v>
+        <v>3.848729139992198</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.2040545629401</v>
+        <v>-4.154189712113811</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.049972589037209</v>
+        <v>1.069918529367725</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1092811678751202</v>
+        <v>-0.1454710335648219</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.666382137801925</v>
+        <v>2.644668218388104</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852431</v>
+        <v>3.841444817852428</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.130676465851364</v>
+        <v>-4.080811615025075</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.149614060194879</v>
+        <v>1.169560000525395</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.03590307078638366</v>
+        <v>-0.07209293647608533</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.780699228377342</v>
+        <v>2.758985308963521</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319556</v>
+        <v>3.819063300319552</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.228417010476338</v>
+        <v>-4.005448975476306</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.125145578460933</v>
+        <v>1.214332792460946</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.05179234891936385</v>
+        <v>-0.02969053916763015</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.785793397613598</v>
+        <v>2.799054483464638</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489395</v>
+        <v>3.831819032489391</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.404754770599268</v>
+        <v>-4.181786735599236</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.053146455236433</v>
+        <v>1.142333669236446</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2281301090422932</v>
+        <v>-0.2060282992905595</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.678526722364512</v>
+        <v>2.691787808215552</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397804</v>
+        <v>3.836411672397801</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.328332724167341</v>
+        <v>-4.105364689167309</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.082206891849132</v>
+        <v>1.171394105849145</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2281301090422932</v>
+        <v>-0.2060282992905595</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.67701834040444</v>
+        <v>2.69027942625548</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316259</v>
+        <v>3.833513460316255</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.283959592528772</v>
+        <v>-4.06099155752874</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.099819011939996</v>
+        <v>1.189006225940008</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1837569774037247</v>
+        <v>-0.1616551676519909</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.703505086823017</v>
+        <v>2.716766172674058</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105973</v>
+        <v>3.821562117105969</v>
       </c>
       <c r="C1977" t="n">
         <v>2.808153067403842</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.161125371641605</v>
+        <v>-3.938157336641573</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.143346494433453</v>
+        <v>1.232533708433466</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1837569774037247</v>
+        <v>-0.1616551676519909</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.697898880961608</v>
+        <v>2.711159966812648</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190331</v>
+        <v>3.833011148190328</v>
       </c>
       <c r="C1978" t="n">
         <v>2.814534824431647</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.113469641080549</v>
+        <v>-3.890501606080517</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.16879054368568</v>
+        <v>1.257977757685693</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.136101246842669</v>
+        <v>-0.1139994370909353</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.732874076326045</v>
+        <v>2.746135162177086</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569624</v>
+        <v>3.82267821056962</v>
       </c>
       <c r="C1979" t="n">
         <v>2.819427197806371</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.012951482581794</v>
+        <v>-3.789983447581762</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.213890180459906</v>
+        <v>1.303077394459919</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.03558308834391444</v>
+        <v>-0.01348127859218073</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.798077344800023</v>
+        <v>2.811338430651063</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557299</v>
+        <v>3.828808877557297</v>
       </c>
       <c r="C1980" t="n">
         <v>2.806181870282244</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.073618072984184</v>
+        <v>-3.850650037984151</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.176378216774823</v>
+        <v>1.265565430774836</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.1172814050624481</v>
+        <v>-0.0951795953107144</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.735813027244775</v>
+        <v>2.749074113095815</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932774</v>
+        <v>3.816837033932772</v>
       </c>
       <c r="C1981" t="n">
         <v>2.810279572892872</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.028779671375785</v>
+        <v>-3.805811636375753</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.198411280028811</v>
+        <v>1.287598494028824</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.1127379721175786</v>
+        <v>-0.09063616236584493</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.742636789622325</v>
+        <v>2.755897875473365</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917058</v>
+        <v>3.817932354917057</v>
       </c>
       <c r="C1982" t="n">
         <v>2.81444051252395</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.129538307132783</v>
+        <v>-3.906570272132752</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.16226876535709</v>
+        <v>1.251455979357102</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.2015635408445841</v>
+        <v>-0.1794617310928504</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.6935023880172</v>
+        <v>2.70676347386824</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405967</v>
+        <v>3.826684745405966</v>
       </c>
       <c r="C1983" t="n">
         <v>2.820320115051787</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.085335470046883</v>
+        <v>-3.862367435046851</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.185829502719287</v>
+        <v>1.2750167167193</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1573607037586836</v>
+        <v>-0.1352588940069499</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.725903692796578</v>
+        <v>2.739164778647618</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265652</v>
+        <v>3.838199629265651</v>
       </c>
       <c r="C1984" t="n">
         <v>2.818730115521035</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.122314497710326</v>
+        <v>-3.899346462710295</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.169447892123157</v>
+        <v>1.25863510612317</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.1203868019673531</v>
+        <v>-0.09828499221561937</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.746498034340624</v>
+        <v>2.759759120191664</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284887</v>
+        <v>3.863895080284885</v>
       </c>
       <c r="C1985" t="n">
         <v>2.869977880704075</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.142372576575166</v>
+        <v>-3.919404541575135</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.212672425760261</v>
+        <v>1.301859639760274</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.1203868019673531</v>
+        <v>-0.09828499221561937</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.797745799523663</v>
+        <v>2.811006885374703</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321029</v>
+        <v>3.865338681321028</v>
       </c>
       <c r="C1986" t="n">
         <v>2.868418585298328</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.102441903397276</v>
+        <v>-3.879473868397244</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.22708539962567</v>
+        <v>1.316272613625683</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.08045612878946273</v>
+        <v>-0.05835431903772903</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.82014490802465</v>
+        <v>2.833405993875691</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475146</v>
+        <v>3.864489842475145</v>
       </c>
       <c r="C1987" t="n">
         <v>2.863366813536598</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.051409810674748</v>
+        <v>-3.828441775674716</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.242446464952951</v>
+        <v>1.331633678952964</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.02942403606693478</v>
+        <v>-0.007322226315201075</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.845712391896437</v>
+        <v>2.858973477747477</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404862</v>
+        <v>3.84254736040486</v>
       </c>
       <c r="C1988" t="n">
         <v>2.880554217629303</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.986185629547543</v>
+        <v>-3.763217594547511</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.285723541496538</v>
+        <v>1.374910755496551</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.03580014506027085</v>
+        <v>0.05790195481200455</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.902034304665465</v>
+        <v>2.915295390516506</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882566</v>
+        <v>3.840061186882564</v>
       </c>
       <c r="C1989" t="n">
         <v>2.876515189928583</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.948758609476409</v>
+        <v>-3.725790574476377</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.296655321824272</v>
+        <v>1.385842535824285</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.04105168308945251</v>
+        <v>0.06315349284118621</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.901146199782255</v>
+        <v>2.914407285633295</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899267</v>
+        <v>3.845169808992669</v>
       </c>
       <c r="C1990" t="n">
         <v>2.877771982259823</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.968870265511117</v>
+        <v>-3.745902230511085</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.289867451741629</v>
+        <v>1.379054665741642</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.0520790280868717</v>
+        <v>0.07418083783860541</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.909019399111947</v>
+        <v>2.922280484962987</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636296</v>
+        <v>3.828661445636294</v>
       </c>
       <c r="C1991" t="n">
         <v>3.038329753281034</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.915125451083913</v>
+        <v>-3.692157416083881</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.471923148533722</v>
+        <v>1.561110362533735</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.06214233752733367</v>
+        <v>0.08424414727906737</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.075615155797434</v>
+        <v>3.088876241648475</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957634</v>
+        <v>3.813222820957632</v>
       </c>
       <c r="C1992" t="n">
         <v>3.158442662498851</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.89133388247777</v>
+        <v>-3.668365847477738</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.601552685193996</v>
+        <v>1.690739899194009</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.08593390613347596</v>
+        <v>0.1080357158852097</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.210003006178937</v>
+        <v>3.223264092029977</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799876</v>
+        <v>3.814230727998758</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15015063851271</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.865249798213962</v>
+        <v>-3.64228176321393</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.603694294913378</v>
+        <v>1.692881508913391</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.08593390613347596</v>
+        <v>0.1080357158852097</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.201710982192796</v>
+        <v>3.214972068043836</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896934</v>
+        <v>3.803397818896932</v>
       </c>
       <c r="C1994" t="n">
         <v>3.14834383409649</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.787118617365016</v>
+        <v>-3.564150582364983</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.633139962836736</v>
+        <v>1.722327176836749</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.1601107170171605</v>
+        <v>0.1822125267688942</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.244410264306786</v>
+        <v>3.257671350157826</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.165898239823281</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.778226155971733</v>
+        <v>-3.5552581209717</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.654251353120841</v>
+        <v>1.743438567120854</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.1601107170171605</v>
+        <v>0.1822125267688942</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.261964670033578</v>
+        <v>3.275225755884618</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.157753287227865</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.94670227294161</v>
+        <v>-3.723734237941578</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.578715953737474</v>
+        <v>1.667903167737486</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1321628813005797</v>
+        <v>0.1542646910523134</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.237051016008213</v>
+        <v>3.250312101859254</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.139022984415727</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.248902744080027</v>
+        <v>-3.025934709079995</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.839105462469969</v>
+        <v>1.928292676469982</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.06181482193016902</v>
+        <v>0.08391663168190272</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.176111877573828</v>
+        <v>3.189372963424869</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.129687006912631</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.226181640396875</v>
+        <v>-3.003213605396843</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.838857926440134</v>
+        <v>1.928045140440148</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.06181482193016902</v>
+        <v>0.08391663168190272</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.166775900070733</v>
+        <v>3.180036985921773</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.2885931327638</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.224456597106831</v>
+        <v>-3.001488562106799</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.998454069607321</v>
+        <v>2.087641283607334</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.06353986522021277</v>
+        <v>0.08564167497194647</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.326717051895928</v>
+        <v>3.339978137746969</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.325670955257447</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.379237603885086</v>
+        <v>-3.156269568885054</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.973619489389665</v>
+        <v>2.062806703389678</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.03017219116573666</v>
+        <v>0.05227400091747036</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.34377426995689</v>
+        <v>3.35703535580793</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799969</v>
+        <v>3.769443619799968</v>
       </c>
       <c r="C2001" t="n">
         <v>3.322346311246992</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.327802270500426</v>
+        <v>-3.104834235500394</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.990868978733074</v>
+        <v>2.080056192733087</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.08160752455039633</v>
+        <v>0.10370933430213</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.37131082597723</v>
+        <v>3.38457191182827</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.332352464891734</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.300851046173938</v>
+        <v>-3.077883011173906</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.011655622108411</v>
+        <v>2.100842836108424</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.09648787057811548</v>
+        <v>0.1185896803298492</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.390245187238603</v>
+        <v>3.403506273089643</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.516455597036694</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.436804054230254</v>
+        <v>-3.213836019230222</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.141377551030844</v>
+        <v>2.230564765030858</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.09648787057811548</v>
+        <v>0.1185896803298492</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.574348319383563</v>
+        <v>3.587609405234603</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.508572291939687</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.459212172035127</v>
+        <v>-3.236244137035095</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.124530998811889</v>
+        <v>2.213718212811902</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.09648787057811548</v>
+        <v>0.1185896803298492</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.566465014286556</v>
+        <v>3.579726100137596</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.510626291489324</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.503617852537541</v>
+        <v>-3.384249904514494</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.10882272616056</v>
+        <v>2.156569905369779</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.07095471891576455</v>
+        <v>0.03186267146630772</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.553199122838783</v>
+        <v>3.529743894369109</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.566880009211171</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.513058778426071</v>
+        <v>-3.393690830403024</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.161300073526995</v>
+        <v>2.209047252736214</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.193381836459156</v>
+        <v>0.1542897890096991</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.682909111086665</v>
+        <v>3.659453882616991</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.569771103756472</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.511772014886515</v>
+        <v>-3.392404066863468</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.164705873488119</v>
+        <v>2.212453052697338</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.1946685999987126</v>
+        <v>0.1555765525492557</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.6865722637557</v>
+        <v>3.663117035286026</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.567882916650247</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.513329068875806</v>
+        <v>-3.393961120852759</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.162194864786177</v>
+        <v>2.209942043995397</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.1946685999987126</v>
+        <v>0.1555765525492557</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.684684076649475</v>
+        <v>3.661228848179801</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.56270314625311</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.520600954399271</v>
+        <v>-3.401233006376223</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.154106340179654</v>
+        <v>2.201853519388873</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.1873967144752478</v>
+        <v>0.148304667025791</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.675141174938259</v>
+        <v>3.651685946468584</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.561137156463262</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.518759935341019</v>
+        <v>-3.399391987317972</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.153276758013107</v>
+        <v>2.201023937222326</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.1886649411467162</v>
+        <v>0.1495728936972594</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.674336121151292</v>
+        <v>3.650880892681618</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.574210563329181</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.5256686408407</v>
+        <v>-3.406300692817653</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.163586682679153</v>
+        <v>2.211333861888372</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.1886649411467162</v>
+        <v>0.1495728936972594</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.687409528017211</v>
+        <v>3.663954299547536</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.574210563329181</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.52723028365556</v>
+        <v>-3.407862335632513</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.16296202555321</v>
+        <v>2.210709204762428</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.1886649411467162</v>
+        <v>0.1495728936972594</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.687409528017211</v>
+        <v>3.663954299547536</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.852945727666548</v>
+        <v>3.449168676895135</v>
       </c>
       <c r="C2013" t="n">
         <v>3.572734604456183</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.658673204014194</v>
+        <v>-3.706684033014926</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.108908898536757</v>
+        <v>2.089704566936465</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.0938183289566456</v>
+        <v>0.01894949604906637</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.62902560183017</v>
+        <v>3.584104302085623</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240703.xlsx
+++ b/tame_output/ON/bt/strategyON_20240703.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>57.0%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.8%</t>
+          <t>-72.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.5%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.3%</t>
+          <t>121.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>94.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,27 +977,27 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-680.3%</t>
+          <t>-658.8%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.5%</t>
+          <t>-48.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.7%</t>
+          <t>-67.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>447.3%</t>
+          <t>425.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-532.2%</t>
+          <t>-506.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,27 +1135,27 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-272.5%</t>
+          <t>-263.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.0%</t>
+          <t>-36.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-46.1%</t>
+          <t>-25.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-167.3%</t>
+          <t>-156.8%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.6%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-300.5%</t>
+          <t>-279.1%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.8%</t>
+          <t>-29.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>109.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-174.7%</t>
+          <t>-136.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-222.1%</t>
+          <t>-193.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>95.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-180.7%</t>
+          <t>-167.9%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.7%</t>
+          <t>-25.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-87.6%</t>
+          <t>-70.3%</t>
         </is>
       </c>
     </row>
@@ -43733,16 +43733,16 @@
         <v>3.13991794227561</v>
       </c>
       <c r="D1834" t="n">
-        <v>0.7497961784502833</v>
+        <v>0.9638453345512126</v>
       </c>
       <c r="E1834" t="n">
-        <v>3.439479989341976</v>
+        <v>3.525099651782348</v>
       </c>
       <c r="F1834" t="n">
-        <v>1.631764624679707</v>
+        <v>1.845813780780637</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.118976717083434</v>
+        <v>4.247406210743993</v>
       </c>
     </row>
     <row r="1835">
@@ -43756,16 +43756,16 @@
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.5532457673970779</v>
+        <v>0.7672949234980071</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.359117660783038</v>
+        <v>3.44473732322341</v>
       </c>
       <c r="F1835" t="n">
-        <v>1.668418790368211</v>
+        <v>1.88246794646914</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.139227052358882</v>
+        <v>4.267656546019438</v>
       </c>
     </row>
     <row r="1836">
@@ -43779,16 +43779,16 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.3997263829116132</v>
+        <v>0.6137755390125424</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.2775351796163</v>
+        <v>3.363154842056671</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.705385264837735</v>
+        <v>1.919434420938664</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.141232209668043</v>
+        <v>4.2696617033286</v>
       </c>
     </row>
     <row r="1837">
@@ -43802,16 +43802,16 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.3353526130940819</v>
+        <v>0.549401769195011</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.252274810415162</v>
+        <v>3.337894472855533</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.705385264837735</v>
+        <v>1.919434420938664</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.141721348393917</v>
+        <v>4.270150842054475</v>
       </c>
     </row>
     <row r="1838">
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.1989077228666692</v>
+        <v>0.4129568789675984</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.201776836945863</v>
+        <v>3.287396499386235</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.568940374610322</v>
+        <v>1.782989530711252</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.063934396879136</v>
+        <v>4.192363890539694</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.03822376898312591</v>
+        <v>0.1758253871178033</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.141865324703487</v>
+        <v>3.227484987143858</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.568940374610322</v>
+        <v>1.782989530711252</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.098875481376678</v>
+        <v>4.227304975037235</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.03318617825553938</v>
+        <v>0.1808629778453898</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.142457801179859</v>
+        <v>3.228077463620231</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.62458483087664</v>
+        <v>1.838633986977569</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.130839595321806</v>
+        <v>4.259269088982364</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.2903802129635961</v>
+        <v>-0.07633105686266695</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.018326568920374</v>
+        <v>3.103946231360745</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.367390796168583</v>
+        <v>1.581439952269512</v>
       </c>
       <c r="G1841" t="n">
-        <v>3.95526955612071</v>
+        <v>4.083699049781267</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.3561476030130082</v>
+        <v>-0.142098446912079</v>
       </c>
       <c r="E1842" t="n">
-        <v>2.993037222031079</v>
+        <v>3.078656884471451</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.367390796168583</v>
+        <v>1.581439952269512</v>
       </c>
       <c r="G1842" t="n">
-        <v>3.95628716525118</v>
+        <v>4.084716658911737</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.5613922800702528</v>
+        <v>-0.3473431239693236</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.901567383195937</v>
+        <v>2.987187045636309</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.367390796168583</v>
+        <v>1.581439952269512</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.946915197238935</v>
+        <v>4.075344690899493</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.6431641804980044</v>
+        <v>-0.4291150243970753</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.858941348980074</v>
+        <v>2.944561011420446</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.394426369574719</v>
+        <v>1.608475525675649</v>
       </c>
       <c r="G1844" t="n">
-        <v>3.953219267237856</v>
+        <v>4.081648760898413</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.7103732883698821</v>
+        <v>-0.4963241322689529</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.836823022665026</v>
+        <v>2.922442685105398</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.394426369574719</v>
+        <v>1.608475525675649</v>
       </c>
       <c r="G1845" t="n">
-        <v>3.957984584071558</v>
+        <v>4.086414077732115</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.917939072761494</v>
+        <v>-0.7038899166605648</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.751621505027621</v>
+        <v>2.837241167467993</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.186860585183108</v>
+        <v>1.400909741284037</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.831269909555831</v>
+        <v>3.959699403216389</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.335693096308331</v>
+        <v>-1.121643940207402</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.58244678711395</v>
+        <v>2.668066449554321</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.7691065616362706</v>
+        <v>0.9831557177371998</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.578544386932792</v>
+        <v>3.706973880593349</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.625824762913762</v>
+        <v>-1.411775606812833</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.466260337070699</v>
+        <v>2.551879999511071</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.7931883563764505</v>
+        <v>1.00723751247738</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.592859680375822</v>
+        <v>3.721289174036379</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.83382882126684</v>
+        <v>-1.61977966516591</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.387950858283393</v>
+        <v>2.473570520723765</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.7931883563764505</v>
+        <v>1.00723751247738</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.597751824929747</v>
+        <v>3.726181318590304</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.045241242154815</v>
+        <v>-1.831192086053886</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.298467346266191</v>
+        <v>2.384087008706563</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.5817759354884754</v>
+        <v>0.7958250915894045</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.46598582873495</v>
+        <v>3.594415322395507</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.411309969299468</v>
+        <v>-2.197260813198538</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.145124154714779</v>
+        <v>2.230743817155151</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.2157072083438227</v>
+        <v>0.4297563644447518</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.239428891754608</v>
+        <v>3.367858385415165</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.619800750751152</v>
+        <v>-2.405751594650222</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.082066131872874</v>
+        <v>2.167685794313245</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.007216426892138306</v>
+        <v>0.2212655829930674</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.134672712622365</v>
+        <v>3.263102206282923</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.867001935516374</v>
+        <v>-2.652952779415444</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.991284408375353</v>
+        <v>2.076904070815726</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.02736978039095073</v>
+        <v>0.2414189364918798</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.154863475130221</v>
+        <v>3.283292968790779</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.359386963540471</v>
+        <v>-3.145337807439541</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.795436789209447</v>
+        <v>1.881056451649819</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.465015247633146</v>
+        <v>-0.2509660915322169</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.860538850359495</v>
+        <v>2.988968344020053</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.744567354470543</v>
+        <v>-3.530518198369613</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.639907171650281</v>
+        <v>1.725526834090653</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.465015247633146</v>
+        <v>-0.2509660915322169</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.859081389172359</v>
+        <v>2.987510882832916</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.994438034485125</v>
+        <v>-3.780388878384195</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.541728023099065</v>
+        <v>1.627347685539437</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.4287525278026827</v>
+        <v>-0.2147033717017536</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.882608144525252</v>
+        <v>3.01103763818581</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.200949811372146</v>
+        <v>-3.986900655271216</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.455229371000514</v>
+        <v>1.540849033440886</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.6352643046897042</v>
+        <v>-0.4212151485887751</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.754807137049298</v>
+        <v>2.883236630709855</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.520293886452648</v>
+        <v>-4.306244730351718</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.329264667668573</v>
+        <v>1.414884330108945</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.6352643046897042</v>
+        <v>-0.4212151485887751</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.756580063749557</v>
+        <v>2.885009557410115</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.952099679602435</v>
+        <v>-4.738050523501506</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.142875237876062</v>
+        <v>1.228494900316434</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.7716818011309712</v>
+        <v>-0.5576326450300422</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.661062453352201</v>
+        <v>2.789491947012759</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.186793673734988</v>
+        <v>-4.972744517634058</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.037282415225132</v>
+        <v>1.122902077665504</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.765345533901716</v>
+        <v>-0.551296377800787</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.653148988691845</v>
+        <v>2.781578482352403</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.52245632096544</v>
+        <v>-5.30840716486451</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9015979479889165</v>
+        <v>0.9872176104292882</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8332765193906209</v>
+        <v>-0.6192273632896919</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.610970989054468</v>
+        <v>2.739400482715025</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.886082565865753</v>
+        <v>-5.672033409764824</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7626350102630326</v>
+        <v>0.8482546727034044</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9314981562577467</v>
+        <v>-0.7174490001568177</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.558525567168433</v>
+        <v>2.686955060828991</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.2512099485045</v>
+        <v>-6.03716079240357</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6158385722133652</v>
+        <v>0.701458234653737</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.227808940556759</v>
+        <v>-1.01375978445583</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.379993611594857</v>
+        <v>2.508423105255415</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.659798725685178</v>
+        <v>-6.445749569584249</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4511646053558529</v>
+        <v>0.5367842677962247</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.422348561636509</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.133601889301209</v>
+        <v>2.262031382961767</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.936374826001011</v>
+        <v>-6.722325669900082</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3357195977009808</v>
+        <v>0.4213392601413521</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.422348561636509</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.12878732177267</v>
+        <v>2.257216815433227</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.352766700288008</v>
+        <v>-7.138717544187079</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1671568985950591</v>
+        <v>0.2527765610354304</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.422348561636509</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.126781372381547</v>
+        <v>2.255210866042105</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.597038101015078</v>
+        <v>-7.382988944914149</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.07970702897291027</v>
+        <v>0.1653266914132816</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.422348561636509</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.137040063050226</v>
+        <v>2.265469556710784</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.802289120251838</v>
+        <v>-7.588239964150909</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.006293813576098817</v>
+        <v>0.07932584886427296</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.422348561636509</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.133139628195922</v>
+        <v>2.261569121856479</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.965868998436221</v>
+        <v>-7.751819842335292</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.07332084479485124</v>
+        <v>0.01229881764552054</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.422348561636509</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.131544548250923</v>
+        <v>2.25997404191148</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.262530340246419</v>
+        <v>-8.048481184145491</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.1882064055897223</v>
+        <v>-0.1025867431493506</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.705140853471316</v>
+        <v>-1.491091697370387</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.094077642739804</v>
+        <v>2.222507136400361</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.449250048555722</v>
+        <v>-8.235200892454793</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2669205934478462</v>
+        <v>-0.1813009310074749</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.705140853471316</v>
+        <v>-1.491091697370387</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.0900513382054</v>
+        <v>2.218480831865958</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.832251437298353</v>
+        <v>-8.618202281197425</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4202232502664831</v>
+        <v>-0.3346035878261113</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.705140853471316</v>
+        <v>-1.491091697370387</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.089949236883816</v>
+        <v>2.218378730544374</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.014121228283388</v>
+        <v>-8.800072072182459</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4903996506890667</v>
+        <v>-0.4047799882486953</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.887010644456351</v>
+        <v>-1.672961488355422</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.983398878264226</v>
+        <v>2.111828371924783</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.37365155078739</v>
+        <v>-9.159602394686461</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.628861476392617</v>
+        <v>-0.5432418139522457</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.887010644456351</v>
+        <v>-1.672961488355422</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.988749181562276</v>
+        <v>2.117178675222833</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.424000614241612</v>
+        <v>-9.209951458140683</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6410850818171285</v>
+        <v>-0.5554654193767568</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.937359707910573</v>
+        <v>-1.723310551809644</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.96645576344692</v>
+        <v>2.094885257107477</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.521619891663008</v>
+        <v>-9.307570735562079</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.677091042163918</v>
+        <v>-0.5914713797235467</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.03497898533197</v>
+        <v>-1.820929829231041</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.91092594761585</v>
+        <v>2.039355441276408</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.669145979668651</v>
+        <v>-9.455096823567722</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.733207921044603</v>
+        <v>-0.6475882586042316</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.182505073337614</v>
+        <v>-1.968455917236684</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.825303851134037</v>
+        <v>1.953733344794594</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.873404154998514</v>
+        <v>-9.659354998897586</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8093979940579059</v>
+        <v>-0.7237783316175346</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.310144017951603</v>
+        <v>-2.096094861850673</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.754233681484286</v>
+        <v>1.882663175144843</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.907056993506988</v>
+        <v>-9.693007837406059</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8183765749768592</v>
+        <v>-0.7327569125364879</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.41055738586864</v>
+        <v>-2.196508229767711</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.698468215218499</v>
+        <v>1.826897708879057</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.833587161839539</v>
+        <v>-9.61953800573861</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7736169408164586</v>
+        <v>-0.6879972783760873</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.337087554201192</v>
+        <v>-2.123038398100262</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.757921815712389</v>
+        <v>1.886351309372947</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.00871157922608</v>
+        <v>-9.794662423125153</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8291114870235594</v>
+        <v>-0.7434918245831876</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.512211971587735</v>
+        <v>-2.298162815486806</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.66740238602798</v>
+        <v>1.795831879688538</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.24316367324057</v>
+        <v>-10.02911451713964</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9301114895309515</v>
+        <v>-0.8444918270905792</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.512211971587735</v>
+        <v>-2.298162815486806</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.660183221126384</v>
+        <v>1.788612714786942</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.34753840426702</v>
+        <v>-10.13348924816609</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.9785335727155062</v>
+        <v>-0.892913910275134</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.616586702614181</v>
+        <v>-2.402537546513252</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.59088619173654</v>
+        <v>1.719315685397098</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.40032455986734</v>
+        <v>-10.18627540376642</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.9985322451170804</v>
+        <v>-0.9129125826767091</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.712262189196578</v>
+        <v>-2.498213033095649</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.534596689625658</v>
+        <v>1.663026183286216</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.52636135323563</v>
+        <v>-10.31231219713471</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.046253233835281</v>
+        <v>-0.9606335713949101</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.687010566386836</v>
+        <v>-2.472961410285906</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.552441391940618</v>
+        <v>1.680870885601176</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.47434583926682</v>
+        <v>-10.26029668316589</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.021456692561356</v>
+        <v>-0.9358370301209833</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.687010566386836</v>
+        <v>-2.472961410285906</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.556431727627019</v>
+        <v>1.684861221287577</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.61601768099094</v>
+        <v>-10.40196852489001</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.079600656149745</v>
+        <v>-0.9939809937093731</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.687010566386836</v>
+        <v>-2.472961410285906</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.554956500728278</v>
+        <v>1.683385994388835</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.56642683656611</v>
+        <v>-10.35237768046518</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.044710908214939</v>
+        <v>-0.9590912457745673</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.637419721962002</v>
+        <v>-2.423370565861072</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.59976441754805</v>
+        <v>1.728193911208608</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.55361944356133</v>
+        <v>-10.3395702874604</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.052639084659713</v>
+        <v>-0.9670194222193405</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.686275496970903</v>
+        <v>-2.472226340869974</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.557399818896027</v>
+        <v>1.685829312556584</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.32777429084192</v>
+        <v>-10.11372513474099</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9527219505357398</v>
+        <v>-0.8671022880953676</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.64434882138374</v>
+        <v>-2.43029966528281</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.592134897284533</v>
+        <v>1.720564390945091</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.20319563450433</v>
+        <v>-9.9891464784034</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9017513434446438</v>
+        <v>-0.8161316810042716</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.64434882138374</v>
+        <v>-2.43029966528281</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.593274041840592</v>
+        <v>1.72170353550115</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.25609092254862</v>
+        <v>-10.04204176644769</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9202756845002513</v>
+        <v>-0.8346560220598791</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.639393475295293</v>
+        <v>-2.425344319194364</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.598881023655768</v>
+        <v>1.727310517316325</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.18395774726074</v>
+        <v>-9.969908591159806</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8856887101464617</v>
+        <v>-0.8000690477060899</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.639393475295293</v>
+        <v>-2.425344319194364</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.604614727894404</v>
+        <v>1.733044221554962</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.11259135465109</v>
+        <v>-9.898542198550158</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8668794154964683</v>
+        <v>-0.7812597530560961</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.568027082685645</v>
+        <v>-2.353977926584716</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.637697301066328</v>
+        <v>1.766126794726886</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.01913232066586</v>
+        <v>-9.805083164564934</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8393792832152864</v>
+        <v>-0.7537596207749138</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.568027082685645</v>
+        <v>-2.353977926584716</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.62781381975342</v>
+        <v>1.756243313413978</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.751890519797467</v>
+        <v>-9.537841363696536</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7343171233673007</v>
+        <v>-0.6486974609269285</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.568027082685645</v>
+        <v>-2.353977926584716</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.625979259254047</v>
+        <v>1.754408752914604</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.653983481120976</v>
+        <v>-9.439934325020046</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6954546228701655</v>
+        <v>-0.6098349604297932</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.500041332825089</v>
+        <v>-2.285992176724159</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.66647039419692</v>
+        <v>1.794899887857477</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.630029940145018</v>
+        <v>-9.415980784044088</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6852047003342885</v>
+        <v>-0.5995850378939163</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.476087791849131</v>
+        <v>-2.262038635748202</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.681511024927988</v>
+        <v>1.809940518588546</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.365970001822221</v>
+        <v>-9.151920845721291</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5928410411669218</v>
+        <v>-0.5072213787265496</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.212027853526335</v>
+        <v>-1.997978697425405</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.826686671759913</v>
+        <v>1.955116165420471</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.658890378317384</v>
+        <v>-8.444841222216454</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3127962254252878</v>
+        <v>-0.2271765629849156</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.212027853526335</v>
+        <v>-1.997978697425405</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.823899638099612</v>
+        <v>1.95232913176017</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.618706079951194</v>
+        <v>-8.404656923850263</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2963788821909703</v>
+        <v>-0.2107592197505981</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.171843555160144</v>
+        <v>-1.957794399059215</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.848353841007168</v>
+        <v>1.976783334667726</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.45530620901183</v>
+        <v>-8.2412570529109</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2316521125944679</v>
+        <v>-0.1460324501540957</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.008443684220782</v>
+        <v>-1.794394528119852</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.945760584791542</v>
+        <v>2.074190078452101</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.221824986782231</v>
+        <v>-8.0077758306813</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.130335194864776</v>
+        <v>-0.04471553242440418</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.774962461991183</v>
+        <v>-1.560913305890254</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.093773746967154</v>
+        <v>2.222203240627712</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.072158595774717</v>
+        <v>-7.858109439673785</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.07336084877472926</v>
+        <v>0.01225881366564296</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.682058970748648</v>
+        <v>-1.468009814647718</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.146623631399716</v>
+        <v>2.275053125060274</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.93988312214383</v>
+        <v>-7.725833966042899</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.02508317257534776</v>
+        <v>0.06053648986502447</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.549783497117761</v>
+        <v>-1.335734341016831</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.221356402325275</v>
+        <v>2.349785895985833</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.784144789584088</v>
+        <v>-7.570095633483157</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.04002722113618562</v>
+        <v>0.1256468835765578</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.394045164558019</v>
+        <v>-1.17999600845709</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.317614462548757</v>
+        <v>2.446043956209315</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.535144990900507</v>
+        <v>-7.321095834799576</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1525334818332769</v>
+        <v>0.2381531442736491</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.394045164558019</v>
+        <v>-1.17999600845709</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.330520803772416</v>
+        <v>2.458950297432974</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.640734980673612</v>
+        <v>-7.42668582457268</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.01767844367518379</v>
+        <v>0.06794121876518844</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.499635154331124</v>
+        <v>-1.285585998230194</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.139190880309334</v>
+        <v>2.267620373969892</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.659469882792209</v>
+        <v>-7.445420726691277</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.02337193735446386</v>
+        <v>0.1089915997948361</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.505231163991255</v>
+        <v>-1.291182007890325</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.184377616390342</v>
+        <v>2.3128071100509</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.511529841384609</v>
+        <v>-7.297480685283678</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.037330968770664</v>
+        <v>0.04828869366970823</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.484910248082697</v>
+        <v>-1.270861091981768</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.076691243247309</v>
+        <v>2.205120736907867</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.458560319130621</v>
+        <v>-7.244511163029689</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.02485714612254686</v>
+        <v>0.06076251631782537</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.431940725828709</v>
+        <v>-1.217891569727779</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.099758970346224</v>
+        <v>2.228188464006782</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.328957195843939</v>
+        <v>-7.200962756258999</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.02002349109703294</v>
+        <v>0.07122126693100839</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.431940725828709</v>
+        <v>-1.217891569727779</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.092798358251131</v>
+        <v>2.221227851911689</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.086808802390081</v>
+        <v>-6.958814362805141</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1313452028597193</v>
+        <v>0.1825429786936947</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.431940725828709</v>
+        <v>-1.217891569727779</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.107260712632274</v>
+        <v>2.235690206292832</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.978549665267559</v>
+        <v>-6.850555225682619</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.169180978167923</v>
+        <v>0.2203787540018984</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.431940725828709</v>
+        <v>-1.217891569727779</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.101792833091469</v>
+        <v>2.230222326752027</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.855258530450429</v>
+        <v>-6.727264090865488</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2159955261053521</v>
+        <v>0.267193301939328</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.308649591011578</v>
+        <v>-1.094600434910649</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.173265607992324</v>
+        <v>2.301695101652882</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.834109331546985</v>
+        <v>-6.706114891962045</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2321561839040545</v>
+        <v>0.2833539597380303</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.287500392108135</v>
+        <v>-1.073451236007205</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.193656105571716</v>
+        <v>2.322085599232273</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.590343889563541</v>
+        <v>-6.462349449978601</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3254430690444829</v>
+        <v>0.3766408448784588</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.287500392108135</v>
+        <v>-1.073451236007205</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.189436813918766</v>
+        <v>2.317866307579324</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.488581069286246</v>
+        <v>-6.360586629701306</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3682725110754168</v>
+        <v>0.4194702869093927</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.274281323715706</v>
+        <v>-1.060232167614777</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.199492568874239</v>
+        <v>2.327922062534797</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.238730675337171</v>
+        <v>-6.110736235752231</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4609547436387489</v>
+        <v>0.5121525194727248</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.274281323715706</v>
+        <v>-1.060232167614777</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.192234643857941</v>
+        <v>2.320664137518499</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.062838582869739</v>
+        <v>-5.934844143284798</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5349107041463705</v>
+        <v>0.5861084799803469</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.274281323715706</v>
+        <v>-1.060232167614777</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.19583376737859</v>
+        <v>2.324263261039148</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.891392119847276</v>
+        <v>-5.763397680262335</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6168167954099095</v>
+        <v>0.6680145712438859</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.102834860693243</v>
+        <v>-0.8887857045923134</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.312029151246622</v>
+        <v>2.44045864490718</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.817102554108937</v>
+        <v>-5.689108114523996</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6455530993215421</v>
+        <v>0.6967508751555185</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.028545294954904</v>
+        <v>-0.8144961388539742</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.355623368305922</v>
+        <v>2.48405286196648</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.753466811875002</v>
+        <v>-5.625472372290061</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6757021972694335</v>
+        <v>0.7268999731034094</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9649095527209691</v>
+        <v>-0.7508603966200397</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.3984996147006</v>
+        <v>2.526929108361158</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.642040052549082</v>
+        <v>-5.514045612964141</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7014671597835971</v>
+        <v>0.752664935617573</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9649095527209691</v>
+        <v>-0.7508603966200397</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.379693873484396</v>
+        <v>2.508123367144954</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.401609555744222</v>
+        <v>-5.273615116159281</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7993824351304184</v>
+        <v>0.8505802109643947</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7244790559161088</v>
+        <v>-0.5104298998151794</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.52569524819219</v>
+        <v>2.654124741852747</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.329366987573027</v>
+        <v>-5.201372547988086</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8322087762337165</v>
+        <v>0.8834065520676928</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7244790559161088</v>
+        <v>-0.5104298998151794</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.52962456202701</v>
+        <v>2.658054055687567</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.276368665291639</v>
+        <v>-5.148374225706698</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8540866890636116</v>
+        <v>0.905284464897588</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.66914279691417</v>
+        <v>-0.4550936408132406</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.563504901345513</v>
+        <v>2.691934395006071</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.167563779811912</v>
+        <v>-5.039569340226971</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8946067144754961</v>
+        <v>0.945804490309472</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.66914279691417</v>
+        <v>-0.4550936408132406</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.560502972565506</v>
+        <v>2.688932466226064</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.947542981774902</v>
+        <v>-4.819548542189961</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9841940707009145</v>
+        <v>1.035391846534891</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5279229518461898</v>
+        <v>-0.3138737957452603</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.646813916616909</v>
+        <v>2.775243410277466</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.814675292711624</v>
+        <v>-4.686680853126683</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.053235329128049</v>
+        <v>1.104433104962025</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5279229518461898</v>
+        <v>-0.3138737957452603</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.662708099418732</v>
+        <v>2.79113759307929</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.694502209347125</v>
+        <v>-4.566507769762184</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.10245040691415</v>
+        <v>1.153648182748126</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4077498684816908</v>
+        <v>-0.1937007123807614</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.735957793877733</v>
+        <v>2.864387287538291</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.586019929937089</v>
+        <v>-4.421835624662447</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.155931421239604</v>
+        <v>1.221605143349461</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2992675890716551</v>
+        <v>-0.04902856728102395</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.811135264085195</v>
+        <v>2.961278677159573</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.645894757294782</v>
+        <v>-4.481710452020139</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.118018981697953</v>
+        <v>1.18369270380781</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3591424164293472</v>
+        <v>-0.1089033946387161</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.761247859072005</v>
+        <v>2.911391272146384</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.559095259515773</v>
+        <v>-4.394910954241131</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.175139274132123</v>
+        <v>1.240812996241979</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3591424164293472</v>
+        <v>-0.1089033946387161</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.783648352394571</v>
+        <v>2.93379176546895</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.561564965977579</v>
+        <v>-4.397380660702937</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.174223792920813</v>
+        <v>1.239897515030669</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3616121228911534</v>
+        <v>-0.1113731011005222</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.7822389298909</v>
+        <v>2.932382342965278</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.62993515230159</v>
+        <v>-4.465750847026947</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.15788264086591</v>
+        <v>1.223556362975767</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3523364238549384</v>
+        <v>-0.1020974020643073</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.798811271787331</v>
+        <v>2.94895468486171</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.643723205148636</v>
+        <v>-4.479538899873994</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.142804128358983</v>
+        <v>1.20847785046884</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3523364238549384</v>
+        <v>-0.1020974020643073</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.789247980419222</v>
+        <v>2.939391393493601</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.674716364477342</v>
+        <v>-4.510532059202699</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9551164296678878</v>
+        <v>1.020790151777744</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3523364238549384</v>
+        <v>-0.1020974020643073</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.613957545459609</v>
+        <v>2.764100958533988</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.499242104684873</v>
+        <v>-4.33505779941023</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.029873365576663</v>
+        <v>1.09554708768652</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3523364238549384</v>
+        <v>-0.1020974020643073</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.618524777451396</v>
+        <v>2.768668190525776</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.610178357326122</v>
+        <v>-4.445994052051479</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9612408932813705</v>
+        <v>1.026914615391227</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3523364238549384</v>
+        <v>-0.1020974020643073</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.594266806212604</v>
+        <v>2.744410219286983</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.57651481185384</v>
+        <v>-4.412330506579197</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9778376966901889</v>
+        <v>1.043511418800046</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3186728783826566</v>
+        <v>-0.06843385659202544</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.617596318715878</v>
+        <v>2.767739731790257</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.516662192650116</v>
+        <v>-4.352477887375474</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.01195113080381</v>
+        <v>1.077624852913667</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3186728783826566</v>
+        <v>-0.06843385659202544</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.627768705148011</v>
+        <v>2.777912118222389</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.430418729623739</v>
+        <v>-4.266234424349096</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.041394786588222</v>
+        <v>1.107068508698079</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3186728783826566</v>
+        <v>-0.06843385659202544</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.622714975721871</v>
+        <v>2.77285838879625</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.475725549022719</v>
+        <v>-4.311541243748076</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.015047834273155</v>
+        <v>1.080721556383012</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3594830413918874</v>
+        <v>-0.1092440196012562</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.590004653360858</v>
+        <v>2.740148066435237</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.50475865372502</v>
+        <v>-4.340574348450377</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.003986465425337</v>
+        <v>1.069660187535193</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3594830413918874</v>
+        <v>-0.1092440196012562</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.59055652639396</v>
+        <v>2.740699939468338</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.41194817227416</v>
+        <v>-4.247763866999517</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9703833498970462</v>
+        <v>1.036057072006903</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.266672559941028</v>
+        <v>-0.01643353815039689</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.575515507155841</v>
+        <v>2.72565892023022</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.456337641603588</v>
+        <v>-4.292153336328945</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.954501038089876</v>
+        <v>1.020174760199733</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.3110620292704557</v>
+        <v>-0.06082300747982455</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.550755301482785</v>
+        <v>2.700898714557164</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.343666423367337</v>
+        <v>-4.179482118092695</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9946452338960992</v>
+        <v>1.060318956005956</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1983908110342055</v>
+        <v>0.05184821075642565</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.613433740936258</v>
+        <v>2.763577154010637</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.231289422184664</v>
+        <v>-4.067105116910022</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.045087330199836</v>
+        <v>1.110761052309692</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1983908110342055</v>
+        <v>0.05184821075642565</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.618925036766925</v>
+        <v>2.769068449841304</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.259069820086017</v>
+        <v>-4.094885514811375</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.045472372807833</v>
+        <v>1.11114609491769</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2261712089355585</v>
+        <v>0.02406781285507259</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.613753999794653</v>
+        <v>2.763897412869031</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.342071101111296</v>
+        <v>-4.177886795836653</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8506275803983752</v>
+        <v>0.9163013025082318</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2447420934627323</v>
+        <v>0.005496928327898831</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.440967189079002</v>
+        <v>2.591110602153381</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.450685179554627</v>
+        <v>-4.286500874279985</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9273316097402484</v>
+        <v>0.9930053318501051</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2447420934627323</v>
+        <v>0.005496928327898831</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.561116849798208</v>
+        <v>2.711260262872586</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.415276141306484</v>
+        <v>-4.251091836031842</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9560082511418284</v>
+        <v>1.021681973251685</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2447420934627323</v>
+        <v>0.005496928327898831</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.57562987590053</v>
+        <v>2.725773288974909</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.376892478748333</v>
+        <v>-4.212708173473691</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9687811575074576</v>
+        <v>1.034454879617314</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2063584309045811</v>
+        <v>0.04388059088605001</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.59607951477779</v>
+        <v>2.746222927852168</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.199776148713167</v>
+        <v>-4.035591843438525</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.036356718366826</v>
+        <v>1.102030440476683</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2063584309045811</v>
+        <v>0.04388059088605001</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.592808543623092</v>
+        <v>2.74295195669747</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.244868393546713</v>
+        <v>-4.08068408827207</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.019003212195321</v>
+        <v>1.084676934305177</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2682544740739709</v>
+        <v>-0.01801545228333978</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.556354309483371</v>
+        <v>2.70649772255775</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.065492972307945</v>
+        <v>-3.901308667033303</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.084540355997242</v>
+        <v>1.150214078107099</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.1114777159032522</v>
+        <v>0.1387613058873789</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.644207339692216</v>
+        <v>2.794350752766595</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.110507185828551</v>
+        <v>-3.946322880553909</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.04734212592059</v>
+        <v>1.113015848030446</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1418266112178568</v>
+        <v>0.1084124105727743</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.606805457835044</v>
+        <v>2.756948870909422</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.377511696100986</v>
+        <v>-4.213327390826344</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9462318841505615</v>
+        <v>1.011905606260418</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3361896492608054</v>
+        <v>-0.08595062747017429</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.49587919734822</v>
+        <v>2.646022610422599</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.478709477538159</v>
+        <v>-4.314525172263517</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9049566934721938</v>
+        <v>0.97063041558205</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4045984628061246</v>
+        <v>-0.1543594410154935</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.45403783111753</v>
+        <v>2.604181244191909</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.472198510923846</v>
+        <v>-4.308014205649204</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9051610416722355</v>
+        <v>0.9708347637820918</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4045984628061246</v>
+        <v>-0.1543594410154935</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.451637792671847</v>
+        <v>2.601781205746225</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.453160383216549</v>
+        <v>-4.288976077941907</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9093010119633993</v>
+        <v>0.9749747340732557</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4627820741373191</v>
+        <v>-0.212543052346688</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.413252345081375</v>
+        <v>2.563395758155754</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.484287014367167</v>
+        <v>-4.320102709092525</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.074432228441833</v>
+        <v>1.140105950551689</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4627820741373191</v>
+        <v>-0.212543052346688</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.590834214020056</v>
+        <v>2.740977627094434</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.498153775701085</v>
+        <v>-4.333969470426443</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.069718852894399</v>
+        <v>1.135392575004255</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.5006399908711421</v>
+        <v>-0.250400969080511</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.568952792965895</v>
+        <v>2.719096206040274</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.453349604161155</v>
+        <v>-4.289165298886513</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.093649051907297</v>
+        <v>1.159322774017153</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.5006399908711421</v>
+        <v>-0.250400969080511</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.574961323362821</v>
+        <v>2.7251047364372</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.305606633926153</v>
+        <v>-4.141422328651511</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.23189888779332</v>
+        <v>1.297572609903176</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3328326336362589</v>
+        <v>-0.0825936118456278</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.754798385495773</v>
+        <v>2.904941798570152</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.407621316457374</v>
+        <v>-4.243437011182732</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.193886636312312</v>
+        <v>1.259560358422169</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3328326336362589</v>
+        <v>-0.0825936118456278</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.757592007027254</v>
+        <v>2.907735420101633</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.401468610404589</v>
+        <v>-4.237284305129948</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.197010067125084</v>
+        <v>1.262683789234941</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.3266799275834746</v>
+        <v>-0.07644090579284352</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.761945979050583</v>
+        <v>2.912089392124962</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.418277908555091</v>
+        <v>-4.25409360328045</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.189366824604994</v>
+        <v>1.25504054671485</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3434892257339763</v>
+        <v>-0.09325020394334516</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.750940876900392</v>
+        <v>2.901084289974771</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.355979909778969</v>
+        <v>-4.191795604504327</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.280621577912264</v>
+        <v>1.34629530002212</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3434892257339763</v>
+        <v>-0.09325020394334516</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.817276430697213</v>
+        <v>2.967419843771592</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.154189712113811</v>
+        <v>-3.990005406839169</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.069918529367725</v>
+        <v>1.135592251477581</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1454710335648219</v>
+        <v>0.1047679882258092</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.644668218388104</v>
+        <v>2.794811631462482</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.080811615025075</v>
+        <v>-3.916627309750433</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.169560000525395</v>
+        <v>1.235233722635251</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.07209293647608533</v>
+        <v>0.1781460853145458</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.758985308963521</v>
+        <v>2.9091287220379</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.005448975476306</v>
+        <v>-4.014367854375407</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.214332792460946</v>
+        <v>1.210765240901305</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.02969053916763015</v>
+        <v>0.1622568071815656</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.799054483464638</v>
+        <v>2.914222891274155</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.181786735599236</v>
+        <v>-4.190705614498336</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.142333669236446</v>
+        <v>1.138766117676805</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2060282992905595</v>
+        <v>-0.0140809529413638</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.691787808215552</v>
+        <v>2.806956216025069</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.105364689167309</v>
+        <v>-4.114283568066409</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.171394105849145</v>
+        <v>1.167826554289504</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2060282992905595</v>
+        <v>-0.0140809529413638</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.69027942625548</v>
+        <v>2.805447834064998</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.06099155752874</v>
+        <v>-4.069910436427841</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.189006225940008</v>
+        <v>1.185438674380368</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1616551676519909</v>
+        <v>0.0302921786972048</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.716766172674058</v>
+        <v>2.831934580483575</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.808153067403842</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.938157336641573</v>
+        <v>-3.947076215540673</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.232533708433466</v>
+        <v>1.228966156873825</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1616551676519909</v>
+        <v>0.0302921786972048</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.711159966812648</v>
+        <v>2.826328374622165</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.814534824431647</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.890501606080517</v>
+        <v>-3.899420484979617</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.257977757685693</v>
+        <v>1.254410206126052</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1139994370909353</v>
+        <v>0.07794790925826045</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.746135162177086</v>
+        <v>2.861303569986603</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.819427197806371</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.789983447581762</v>
+        <v>-3.798902326480863</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.303077394459919</v>
+        <v>1.299509842900279</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.01348127859218073</v>
+        <v>0.178466067757015</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.811338430651063</v>
+        <v>2.926506838460581</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.806181870282244</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.850650037984151</v>
+        <v>-3.859568916883252</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.265565430774836</v>
+        <v>1.261997879215195</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.0951795953107144</v>
+        <v>0.09676775103848134</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.749074113095815</v>
+        <v>2.864242520905333</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.810279572892872</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.805811636375753</v>
+        <v>-3.814730515274854</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.287598494028824</v>
+        <v>1.284030942469183</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.09063616236584493</v>
+        <v>0.1013111839833508</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.755897875473365</v>
+        <v>2.871066283282883</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.81444051252395</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.906570272132752</v>
+        <v>-3.915489151031852</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.251455979357102</v>
+        <v>1.247888427797462</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1794617310928504</v>
+        <v>0.01248561525634539</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.70676347386824</v>
+        <v>2.821931881677758</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.820320115051787</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.862367435046851</v>
+        <v>-3.871286313945952</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.2750167167193</v>
+        <v>1.271449165159659</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1352588940069499</v>
+        <v>0.05668845234224584</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.739164778647618</v>
+        <v>2.854333186457135</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.818730115521035</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.899346462710295</v>
+        <v>-3.908265341609395</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.25863510612317</v>
+        <v>1.255067554563529</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.09828499221561937</v>
+        <v>0.09366235413357638</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.759759120191664</v>
+        <v>2.874927528001181</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.869977880704075</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.919404541575135</v>
+        <v>-3.928323420474235</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.301859639760274</v>
+        <v>1.298292088200633</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.09828499221561937</v>
+        <v>0.09366235413357638</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.811006885374703</v>
+        <v>2.926175293184221</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.868418585298328</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.879473868397244</v>
+        <v>-3.888392747296345</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.316272613625683</v>
+        <v>1.312705062066042</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.05835431903772903</v>
+        <v>0.1335930273114667</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.833405993875691</v>
+        <v>2.948574401685208</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.863366813536598</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.828441775674716</v>
+        <v>-3.837360654573817</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.331633678952964</v>
+        <v>1.328066127393323</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.007322226315201075</v>
+        <v>0.1846251200339947</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.858973477747477</v>
+        <v>2.974141885556995</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.880554217629303</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.763217594547511</v>
+        <v>-3.772136473446611</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.374910755496551</v>
+        <v>1.37134320393691</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.05790195481200455</v>
+        <v>0.2498493011612003</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.915295390516506</v>
+        <v>3.030463798326023</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.876515189928583</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.725790574476377</v>
+        <v>-3.734709453375478</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.385842535824285</v>
+        <v>1.382274984264644</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.06315349284118621</v>
+        <v>0.255100839190382</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.914407285633295</v>
+        <v>3.029575693442812</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.877771982259823</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.745902230511085</v>
+        <v>-3.754821109410186</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.379054665741642</v>
+        <v>1.375487114182001</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.07418083783860541</v>
+        <v>0.2661281841878012</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.922280484962987</v>
+        <v>3.037448892772504</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.038329753281034</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.692157416083881</v>
+        <v>-3.701076294982981</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.561110362533735</v>
+        <v>1.557542810974094</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.08424414727906737</v>
+        <v>0.2761914936282631</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.088876241648475</v>
+        <v>3.204044649457992</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.158442662498851</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.668365847477738</v>
+        <v>-3.677284726376839</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.690739899194009</v>
+        <v>1.687172347634368</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.1080357158852097</v>
+        <v>0.2999830622344054</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.223264092029977</v>
+        <v>3.338432499839495</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.15015063851271</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.64228176321393</v>
+        <v>-3.651200642113031</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.692881508913391</v>
+        <v>1.68931395735375</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.1080357158852097</v>
+        <v>0.2999830622344054</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.214972068043836</v>
+        <v>3.330140475853354</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.14834383409649</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.564150582364983</v>
+        <v>-3.573069461264084</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.722327176836749</v>
+        <v>1.718759625277108</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.1822125267688942</v>
+        <v>0.37415987311809</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.257671350157826</v>
+        <v>3.372839757967344</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.165898239823281</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.5552581209717</v>
+        <v>-3.564176999870801</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.743438567120854</v>
+        <v>1.739871015561213</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.1822125267688942</v>
+        <v>0.37415987311809</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.275225755884618</v>
+        <v>3.390394163694135</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.157753287227865</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.723734237941578</v>
+        <v>-3.732653116840679</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.667903167737486</v>
+        <v>1.664335616177846</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1542646910523134</v>
+        <v>0.3462120374015092</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.250312101859254</v>
+        <v>3.365480509668771</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.139022984415727</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.025934709079995</v>
+        <v>-3.034853587979096</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.928292676469982</v>
+        <v>1.924725124910341</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.08391663168190272</v>
+        <v>0.2758639780310985</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.189372963424869</v>
+        <v>3.304541371234386</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.129687006912631</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.003213605396843</v>
+        <v>-3.012132484295943</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.928045140440148</v>
+        <v>1.924477588880507</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.08391663168190272</v>
+        <v>0.2758639780310985</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.180036985921773</v>
+        <v>3.295205393731291</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.2885931327638</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.001488562106799</v>
+        <v>-3.010407441005899</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.087641283607334</v>
+        <v>2.084073732047693</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.08564167497194647</v>
+        <v>0.2775890213211422</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.339978137746969</v>
+        <v>3.455146545556486</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.325670955257447</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.156269568885054</v>
+        <v>-3.165188447784154</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.062806703389678</v>
+        <v>2.059239151830038</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.05227400091747036</v>
+        <v>0.2442213472666661</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.35703535580793</v>
+        <v>3.472203763617447</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.322346311246992</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.104834235500394</v>
+        <v>-3.113753114399495</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.080056192733087</v>
+        <v>2.076488641173447</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.10370933430213</v>
+        <v>0.2956566806513258</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.38457191182827</v>
+        <v>3.499740319637788</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.332352464891734</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.077883011173906</v>
+        <v>-3.086801890073007</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.100842836108424</v>
+        <v>2.097275284548783</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.1185896803298492</v>
+        <v>0.3105370266790449</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.403506273089643</v>
+        <v>3.518674680899161</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.516455597036694</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.213836019230222</v>
+        <v>-3.222754898129323</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.230564765030858</v>
+        <v>2.226997213471217</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.1185896803298492</v>
+        <v>0.3105370266790449</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.587609405234603</v>
+        <v>3.702777813044121</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.508572291939687</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.236244137035095</v>
+        <v>-3.245163015934195</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.213718212811902</v>
+        <v>2.210150661252261</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.1185896803298492</v>
+        <v>0.3105370266790449</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.579726100137596</v>
+        <v>3.694894507947114</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.510626291489324</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.384249904514494</v>
+        <v>-3.393168783413595</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.156569905369779</v>
+        <v>2.153002353810138</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.03186267146630772</v>
+        <v>0.2238100178155035</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.529743894369109</v>
+        <v>3.644912302178626</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.566880009211171</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.393690830403024</v>
+        <v>-3.402609709302125</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.209047252736214</v>
+        <v>2.205479701176574</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.1542897890096991</v>
+        <v>0.3462371353588949</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.659453882616991</v>
+        <v>3.774622290426509</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.569771103756472</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.392404066863468</v>
+        <v>-3.401322945762568</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.212453052697338</v>
+        <v>2.208885501137697</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.1555765525492557</v>
+        <v>0.3475238988984515</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.663117035286026</v>
+        <v>3.778285443095543</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.567882916650247</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.393961120852759</v>
+        <v>-3.40287999975186</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.209942043995397</v>
+        <v>2.206374492435756</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.1555765525492557</v>
+        <v>0.3475238988984515</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.661228848179801</v>
+        <v>3.776397255989318</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.56270314625311</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.401233006376223</v>
+        <v>-3.410151885275324</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.201853519388873</v>
+        <v>2.198285967829232</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.148304667025791</v>
+        <v>0.3402520133749867</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.651685946468584</v>
+        <v>3.766854354278102</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.561137156463262</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.399391987317972</v>
+        <v>-3.408310866217073</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.201023937222326</v>
+        <v>2.197456385662685</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.1495728936972594</v>
+        <v>0.3415202400464551</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.650880892681618</v>
+        <v>3.766049300491135</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.574210563329181</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.406300692817653</v>
+        <v>-3.415219571716753</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.211333861888372</v>
+        <v>2.207766310328731</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.1495728936972594</v>
+        <v>0.3415202400464551</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.663954299547536</v>
+        <v>3.779122707357054</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.574210563329181</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.407862335632513</v>
+        <v>-3.416781214531613</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.210709204762428</v>
+        <v>2.207141653202788</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.1495728936972594</v>
+        <v>0.3415202400464551</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.663954299547536</v>
+        <v>3.779122707357054</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.449168676895135</v>
+        <v>3.85064586963974</v>
       </c>
       <c r="C2013" t="n">
         <v>3.572734604456183</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.706684033014926</v>
+        <v>-3.444682001641086</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.089704566936465</v>
+        <v>2.194505379486</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.01894949604906637</v>
+        <v>0.3069233159035203</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.584104302085623</v>
+        <v>3.756888593998295</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240703.xlsx
+++ b/tame_output/ON/bt/strategyON_20240703.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -709,10 +709,8 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
+      <c r="Y2" t="n">
+        <v>1</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -746,7 +744,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>53.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +756,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>78.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +775,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,22 +784,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +817,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -834,12 +832,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +847,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -867,14 +865,12 @@
           <t>0.2</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>-6.5%</t>
-        </is>
+      <c r="Y3" t="n">
+        <v>-0.0616172931916848</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +900,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>49.7%</t>
         </is>
       </c>
     </row>
@@ -916,7 +912,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.0%</t>
+          <t>-71.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -935,7 +931,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +940,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.6%</t>
+          <t>121.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +969,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1007,17 +1003,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.1%</t>
+          <t>-67.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1025,10 +1021,8 @@
           <t>-0.1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>425.9%</t>
-        </is>
+      <c r="Y4" t="n">
+        <v>4.258812073042996</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
@@ -1074,7 +1068,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,16 +1078,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1096,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1125,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,7 +1144,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1159,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1183,14 +1177,12 @@
           <t>0.1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>-25.5%</t>
-        </is>
+      <c r="Y5" t="n">
+        <v>102.5183581257701</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1212,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-156.8%</t>
+          <t>-169.3%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1243,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1252,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1281,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,7 +1315,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1341,14 +1333,12 @@
           <t>-0.1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>109.8%</t>
-        </is>
+      <c r="Y6" t="n">
+        <v>1.097788583625984</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-136.6%</t>
+          <t>-136.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,17 +1380,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1399,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1408,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1418,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1437,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,7 +1446,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1456,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-25.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1471,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1481,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1499,10 +1489,8 @@
           <t>0.1</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>-17.5%</t>
-        </is>
+      <c r="Y7" t="n">
+        <v>-0.1700699457340738</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
@@ -1536,7 +1524,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-70.3%</t>
+          <t>-85.4%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2013"/>
+  <dimension ref="A1:G2014"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43773,7 +43761,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355688</v>
+        <v>3.311888301355689</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43784,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279812</v>
+        <v>3.385382209279813</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43807,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511403</v>
+        <v>3.367379938511404</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43888,7 +43876,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082122</v>
+        <v>3.299560092082123</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43899,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.29349053375792</v>
+        <v>3.293490533757921</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43922,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760738</v>
+        <v>3.293766719760739</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43980,7 +43968,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296835</v>
+        <v>3.299918119296836</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +43991,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201486</v>
+        <v>3.295507330201487</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44014,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153005</v>
+        <v>3.258791981153006</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44037,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44060,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44083,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44106,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44129,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44152,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44175,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44198,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44221,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44244,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44302,7 +44290,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207813</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44371,7 +44359,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44382,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44440,7 +44428,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191737</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44451,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108639</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44474,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097821</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44497,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094117</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44520,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199286</v>
+        <v>3.405960511199287</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44543,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.424633354969594</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44566,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44589,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297749</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44612,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44635,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44658,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44681,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539465</v>
+        <v>3.501052558539466</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44704,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.4924487119375</v>
+        <v>3.492448711937501</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44727,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141703</v>
+        <v>3.502790399141704</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44785,7 +44773,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440635</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44796,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.490059241608602</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44854,7 +44842,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44865,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44888,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4921016412974</v>
+        <v>3.492101641297401</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44911,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322545</v>
+        <v>3.573674025322546</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44934,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158923</v>
+        <v>3.600038265158924</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44957,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940721</v>
+        <v>3.691571733940722</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44980,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770582</v>
+        <v>3.676841549770583</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45003,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615286</v>
+        <v>3.685161381615287</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45061,7 +45049,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.71093553364622</v>
+        <v>3.710935533646221</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45072,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611571</v>
+        <v>3.768951674611572</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45095,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955331</v>
+        <v>3.728577929955332</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45153,7 +45141,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436233</v>
+        <v>3.766317079436234</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45164,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311953</v>
+        <v>3.784684521311954</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45187,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097249</v>
+        <v>3.80082935409725</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45210,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017777</v>
+        <v>3.789311112017778</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45268,7 +45256,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388733</v>
+        <v>3.839374447388735</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45279,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626479</v>
+        <v>3.856161751626481</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45302,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291815</v>
+        <v>3.787330429291817</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45325,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.80163712278579</v>
+        <v>3.801637122785792</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,22 +45348,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390432</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.151226500595932</v>
+        <v>3.025520419828138</v>
       </c>
       <c r="D1905" t="n">
         <v>-7.725833966042899</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.06053648986502447</v>
+        <v>-0.06516959090276941</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.335734341016831</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.349785895985833</v>
+        <v>2.224079815218039</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45371,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105956</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.154041561283568</v>
+        <v>3.028335480515775</v>
       </c>
       <c r="D1906" t="n">
         <v>-7.570095633483157</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1256468835765578</v>
+        <v>-5.919719123603784e-05</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.17999600845709</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.446043956209315</v>
+        <v>2.320337875441521</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45394,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.75388257196099</v>
+        <v>3.753882571960991</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.166947902507227</v>
+        <v>3.041241821739433</v>
       </c>
       <c r="D1907" t="n">
         <v>-7.321095834799576</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2381531442736491</v>
+        <v>0.1124470635058552</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.17999600845709</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.458950297432974</v>
+        <v>2.33324421666518</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45417,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607648</v>
+        <v>3.69293185560765</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.038971972908008</v>
+        <v>2.913265892140214</v>
       </c>
       <c r="D1908" t="n">
         <v>-7.42668582457268</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.06794121876518844</v>
+        <v>-0.05776486200260589</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.285585998230194</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.267620373969892</v>
+        <v>2.141914293202098</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45440,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987907</v>
+        <v>3.770422583987909</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.087516314785095</v>
+        <v>2.9618102340173</v>
       </c>
       <c r="D1909" t="n">
         <v>-7.445420726691277</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.1089915997948361</v>
+        <v>-0.01671448097295825</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.291182007890325</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.3128071100509</v>
+        <v>2.187101029283105</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45463,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710815</v>
+        <v>3.760333686710817</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.967637392096927</v>
+        <v>2.841931311329133</v>
       </c>
       <c r="D1910" t="n">
         <v>-7.297480685283678</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.04828869366970823</v>
+        <v>-0.0774173870980861</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.270861091981768</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.205120736907867</v>
+        <v>2.079414656140072</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45486,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409208</v>
+        <v>3.72356622940921</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.958923405843449</v>
+        <v>2.833217325075655</v>
       </c>
       <c r="D1911" t="n">
         <v>-7.244511163029689</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.06076251631782537</v>
+        <v>-0.06494356444996896</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.217891569727779</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.228188464006782</v>
+        <v>2.102482383238987</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45509,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098112</v>
+        <v>3.729969716098114</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.951962793748356</v>
+        <v>2.826256712980562</v>
       </c>
       <c r="D1912" t="n">
         <v>-7.200962756258999</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.07122126693100839</v>
+        <v>-0.05448481383678594</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.217891569727779</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.221227851911689</v>
+        <v>2.095521771143894</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45532,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493423</v>
+        <v>3.782922533493425</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.966425148129499</v>
+        <v>2.840719067361705</v>
       </c>
       <c r="D1913" t="n">
         <v>-6.958814362805141</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1825429786936947</v>
+        <v>0.05683689792590041</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.217891569727779</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.235690206292832</v>
+        <v>2.109984125525037</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45555,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722821</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.960957268588694</v>
+        <v>2.8352511878209</v>
       </c>
       <c r="D1914" t="n">
         <v>-6.850555225682619</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.2203787540018984</v>
+        <v>0.09467267323410411</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.217891569727779</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.230222326752027</v>
+        <v>2.104516245984232</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45578,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792048</v>
+        <v>3.82805292879205</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.958455362599271</v>
+        <v>2.832749281831477</v>
       </c>
       <c r="D1915" t="n">
         <v>-6.727264090865488</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.267193301939328</v>
+        <v>0.1414872211715337</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.094600434910649</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.301695101652882</v>
+        <v>2.175989020885088</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45601,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.81245367891991</v>
+        <v>3.812453678919912</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.966156340836596</v>
+        <v>2.840450260068802</v>
       </c>
       <c r="D1916" t="n">
         <v>-6.706114891962045</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2833539597380303</v>
+        <v>0.157647878970236</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.073451236007205</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.322085599232273</v>
+        <v>2.196379518464479</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45624,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318097</v>
+        <v>3.748328408318098</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.961937049183647</v>
+        <v>2.836230968415852</v>
       </c>
       <c r="D1917" t="n">
         <v>-6.462349449978601</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3766408448784588</v>
+        <v>0.2509347641106645</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.073451236007205</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.317866307579324</v>
+        <v>2.192160226811529</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45647,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.82431123305753</v>
+        <v>3.824311233057531</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.964061363103663</v>
+        <v>2.838355282335868</v>
       </c>
       <c r="D1918" t="n">
         <v>-6.360586629701306</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4194702869093927</v>
+        <v>0.2937642061415984</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.060232167614777</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.327922062534797</v>
+        <v>2.202215981767003</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45670,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279189</v>
+        <v>3.826354974279191</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.956803438087365</v>
+        <v>2.831097357319571</v>
       </c>
       <c r="D1919" t="n">
         <v>-6.110736235752231</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5121525194727248</v>
+        <v>0.3864464387049305</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.060232167614777</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.320664137518499</v>
+        <v>2.194958056750705</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45693,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011502</v>
+        <v>3.835957987011504</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.960402561608014</v>
+        <v>2.834696480840219</v>
       </c>
       <c r="D1920" t="n">
         <v>-5.934844143284798</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5861084799803469</v>
+        <v>0.4604023992125525</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.060232167614777</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.324263261039148</v>
+        <v>2.198557180271353</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45716,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392991</v>
+        <v>3.780933911392992</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.973730067662567</v>
+        <v>2.848023986894773</v>
       </c>
       <c r="D1921" t="n">
         <v>-5.763397680262335</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6680145712438859</v>
+        <v>0.5423084904760915</v>
       </c>
       <c r="F1921" t="n">
         <v>-0.8887857045923134</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.44045864490718</v>
+        <v>2.314752564139385</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45739,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632785</v>
+        <v>3.773765222632787</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.972750545278864</v>
+        <v>2.84704446451107</v>
       </c>
       <c r="D1922" t="n">
         <v>-5.689108114523996</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6967508751555185</v>
+        <v>0.5710447943877242</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.8144961388539742</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.48405286196648</v>
+        <v>2.358346781198686</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45762,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883078</v>
+        <v>3.76461787988308</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.977445346333182</v>
+        <v>2.851739265565387</v>
       </c>
       <c r="D1923" t="n">
         <v>-5.625472372290061</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7268999731034094</v>
+        <v>0.601193892335615</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.7508603966200397</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.526929108361158</v>
+        <v>2.401223027593364</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45785,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074788</v>
+        <v>3.79881477107479</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.958639605116977</v>
+        <v>2.832933524349183</v>
       </c>
       <c r="D1924" t="n">
         <v>-5.514045612964141</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.752664935617573</v>
+        <v>0.6269588548497786</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.7508603966200397</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.508123367144954</v>
+        <v>2.38241728637716</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45808,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.7976948842423</v>
+        <v>3.797694884242302</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.960382681741855</v>
+        <v>2.83467660097406</v>
       </c>
       <c r="D1925" t="n">
         <v>-5.273615116159281</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8505802109643947</v>
+        <v>0.7248741301966004</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.5104298998151794</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.654124741852747</v>
+        <v>2.528418661084953</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45831,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936769</v>
+        <v>3.821593509367692</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.964311995576675</v>
+        <v>2.83860591480888</v>
       </c>
       <c r="D1926" t="n">
         <v>-5.201372547988086</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8834065520676928</v>
+        <v>0.7577004712998985</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.5104298998151794</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.658054055687567</v>
+        <v>2.532347974919773</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45854,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879971</v>
+        <v>3.822326997879973</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.964990579494015</v>
+        <v>2.83928449872622</v>
       </c>
       <c r="D1927" t="n">
         <v>-5.148374225706698</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.905284464897588</v>
+        <v>0.7795783841297936</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.4550936408132406</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.691934395006071</v>
+        <v>2.566228314238276</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45877,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502343</v>
+        <v>3.848616626502345</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.961988650714008</v>
+        <v>2.836282569946214</v>
       </c>
       <c r="D1928" t="n">
         <v>-5.039569340226971</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.945804490309472</v>
+        <v>0.8200984095416777</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.4550936408132406</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.688932466226064</v>
+        <v>2.56322638545827</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45900,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675945</v>
+        <v>3.818668951675947</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.963567687724622</v>
+        <v>2.837861606956828</v>
       </c>
       <c r="D1929" t="n">
         <v>-4.819548542189961</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.035391846534891</v>
+        <v>0.9096857657670963</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.3138737957452603</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.775243410277466</v>
+        <v>2.649537329509672</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45923,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539956</v>
+        <v>3.843274527539958</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.979461870526446</v>
+        <v>2.853755789758651</v>
       </c>
       <c r="D1930" t="n">
         <v>-4.686680853126683</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.104433104962025</v>
+        <v>0.9787270241942305</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.3138737957452603</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.79113759307929</v>
+        <v>2.665431512311495</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45946,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496264</v>
+        <v>3.845047386496265</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.980607714966748</v>
+        <v>2.854901634198953</v>
       </c>
       <c r="D1931" t="n">
         <v>-4.566507769762184</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.153648182748126</v>
+        <v>1.027942101980332</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.1937007123807614</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.864387287538291</v>
+        <v>2.738681206770497</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45969,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551577001</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.990695817528187</v>
+        <v>2.864989736760393</v>
       </c>
       <c r="D1932" t="n">
         <v>-4.421835624662447</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.221605143349461</v>
+        <v>1.095899062581667</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.04902856728102395</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.961278677159573</v>
+        <v>2.835572596391779</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +45992,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942105</v>
+        <v>3.735839222942107</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.976733308929613</v>
+        <v>2.851027228161819</v>
       </c>
       <c r="D1933" t="n">
         <v>-4.481710452020139</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.18369270380781</v>
+        <v>1.057986623040016</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.1089033946387161</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.911391272146384</v>
+        <v>2.785685191378589</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46015,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674517</v>
+        <v>3.762647477674519</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.999133802252179</v>
+        <v>2.873427721484385</v>
       </c>
       <c r="D1934" t="n">
         <v>-4.394910954241131</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.240812996241979</v>
+        <v>1.115106915474185</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.1089033946387161</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.93379176546895</v>
+        <v>2.808085684701155</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46038,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430697</v>
+        <v>3.729146398430698</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.999206203625592</v>
+        <v>2.873500122857797</v>
       </c>
       <c r="D1935" t="n">
         <v>-4.397380660702937</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.239897515030669</v>
+        <v>1.114191434262875</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.1113731011005222</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.932382342965278</v>
+        <v>2.806676262197484</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46061,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003605</v>
+        <v>3.743220196003607</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.010213126100294</v>
+        <v>2.884507045332499</v>
       </c>
       <c r="D1936" t="n">
         <v>-4.465750847026947</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.223556362975767</v>
+        <v>1.097850282207973</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.1020974020643073</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.94895468486171</v>
+        <v>2.823248604093915</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46084,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508373</v>
+        <v>3.714179139508375</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.000649834732185</v>
+        <v>2.874943753964391</v>
       </c>
       <c r="D1937" t="n">
         <v>-4.479538899873994</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.20847785046884</v>
+        <v>1.082771769701045</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.1020974020643073</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.939391393493601</v>
+        <v>2.813685312725807</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46107,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417708</v>
+        <v>3.71090673141771</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.825359399772572</v>
+        <v>2.699653319004777</v>
       </c>
       <c r="D1938" t="n">
         <v>-4.510532059202699</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.020790151777744</v>
+        <v>0.8950840710099501</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.1020974020643073</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.764100958533988</v>
+        <v>2.638394877766193</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46130,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205905</v>
+        <v>3.746042526205906</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.829926631764359</v>
+        <v>2.704220550996565</v>
       </c>
       <c r="D1939" t="n">
         <v>-4.33505779941023</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.09554708768652</v>
+        <v>0.9698410069187253</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.1020974020643073</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.768668190525776</v>
+        <v>2.642962109757981</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46153,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225449</v>
+        <v>3.765024323225451</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.805668660525567</v>
+        <v>2.679962579757772</v>
       </c>
       <c r="D1940" t="n">
         <v>-4.445994052051479</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.026914615391227</v>
+        <v>0.9012085346234329</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.1020974020643073</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.744410219286983</v>
+        <v>2.618704138519188</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46176,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111298</v>
+        <v>3.7732102971113</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.808800045745472</v>
+        <v>2.683093964977678</v>
       </c>
       <c r="D1941" t="n">
         <v>-4.412330506579197</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.043511418800046</v>
+        <v>0.9178053380322513</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.06843385659202544</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.767739731790257</v>
+        <v>2.642033651022463</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46199,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264168</v>
+        <v>3.78434395226417</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.818972432177604</v>
+        <v>2.69326635140981</v>
       </c>
       <c r="D1942" t="n">
         <v>-4.352477887375474</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.077624852913667</v>
+        <v>0.9519187721458728</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.06843385659202544</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.777912118222389</v>
+        <v>2.652206037454595</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46222,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742304</v>
+        <v>3.786949957742306</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.813918702751465</v>
+        <v>2.68821262198367</v>
       </c>
       <c r="D1943" t="n">
         <v>-4.266234424349096</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.107068508698079</v>
+        <v>0.9813624279302844</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.06843385659202544</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.77285838879625</v>
+        <v>2.647152308028455</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46245,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.75202749931605</v>
+        <v>3.752027499316052</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.80569447819599</v>
+        <v>2.679988397428196</v>
       </c>
       <c r="D1944" t="n">
         <v>-4.311541243748076</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.080721556383012</v>
+        <v>0.9550154756152178</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.1092440196012562</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.740148066435237</v>
+        <v>2.614441985667443</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46268,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803194</v>
+        <v>3.753571165803196</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.806246351229092</v>
+        <v>2.680540270461298</v>
       </c>
       <c r="D1945" t="n">
         <v>-4.340574348450377</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.069660187535193</v>
+        <v>0.9439541067673991</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.1092440196012562</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.740699939468338</v>
+        <v>2.614993858700544</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46291,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809502</v>
+        <v>3.733390600809503</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.735519043120457</v>
+        <v>2.609812962352663</v>
       </c>
       <c r="D1946" t="n">
         <v>-4.247763866999517</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.036057072006903</v>
+        <v>0.9103509912391086</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.01643353815039689</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.72565892023022</v>
+        <v>2.599952839462425</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46314,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560428</v>
+        <v>3.74828581656043</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.737392519045058</v>
+        <v>2.611686438277264</v>
       </c>
       <c r="D1947" t="n">
         <v>-4.292153336328945</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.020174760199733</v>
+        <v>0.8944686794319383</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.06082300747982455</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.700898714557164</v>
+        <v>2.575192633789369</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46337,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472741</v>
+        <v>3.721077195472743</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.732468227556781</v>
+        <v>2.606762146788987</v>
       </c>
       <c r="D1948" t="n">
         <v>-4.179482118092695</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.060318956005956</v>
+        <v>0.9346128752381615</v>
       </c>
       <c r="F1948" t="n">
         <v>0.05184821075642565</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.763577154010637</v>
+        <v>2.637871073242843</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46360,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798541</v>
+        <v>3.743047603798543</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.737959523387449</v>
+        <v>2.612253442619654</v>
       </c>
       <c r="D1949" t="n">
         <v>-4.067105116910022</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.110761052309692</v>
+        <v>0.9850549715418979</v>
       </c>
       <c r="F1949" t="n">
         <v>0.05184821075642565</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.769068449841304</v>
+        <v>2.64336236907351</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46383,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498869</v>
+        <v>3.689597840498871</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.749456725155988</v>
+        <v>2.623750644388193</v>
       </c>
       <c r="D1950" t="n">
         <v>-4.094885514811375</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.11114609491769</v>
+        <v>0.9854400141498958</v>
       </c>
       <c r="F1950" t="n">
         <v>0.02406781285507259</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.763897412869031</v>
+        <v>2.638191332101237</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46406,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306962170533</v>
+        <v>3.643069621705331</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.587812445156641</v>
+        <v>2.462106364388847</v>
       </c>
       <c r="D1951" t="n">
         <v>-4.177886795836653</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9163013025082318</v>
+        <v>0.7905952217404375</v>
       </c>
       <c r="F1951" t="n">
         <v>0.005496928327898831</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.591110602153381</v>
+        <v>2.465404521385586</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46429,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729274</v>
+        <v>3.682716310729276</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.707962105875847</v>
+        <v>2.582256025108052</v>
       </c>
       <c r="D1952" t="n">
         <v>-4.286500874279985</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9930053318501051</v>
+        <v>0.8672992510823108</v>
       </c>
       <c r="F1952" t="n">
         <v>0.005496928327898831</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.711260262872586</v>
+        <v>2.585554182104792</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46452,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190773</v>
+        <v>3.733012441190775</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.722475131978169</v>
+        <v>2.596769051210375</v>
       </c>
       <c r="D1953" t="n">
         <v>-4.251091836031842</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.021681973251685</v>
+        <v>0.8959758924838908</v>
       </c>
       <c r="F1953" t="n">
         <v>0.005496928327898831</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.725773288974909</v>
+        <v>2.600067208207115</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46475,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913431</v>
+        <v>3.741174069913432</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.719894573320538</v>
+        <v>2.594188492552744</v>
       </c>
       <c r="D1954" t="n">
         <v>-4.212708173473691</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.034454879617314</v>
+        <v>0.90874879884952</v>
       </c>
       <c r="F1954" t="n">
         <v>0.04388059088605001</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.746222927852168</v>
+        <v>2.620516847084374</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46498,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532491</v>
+        <v>3.751147197532493</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.71662360216584</v>
+        <v>2.590917521398046</v>
       </c>
       <c r="D1955" t="n">
         <v>-4.035591843438525</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.102030440476683</v>
+        <v>0.9763243597088884</v>
       </c>
       <c r="F1955" t="n">
         <v>0.04388059088605001</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.74295195669747</v>
+        <v>2.617245875929676</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46521,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793909</v>
+        <v>3.741328448793911</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.717306993927753</v>
+        <v>2.591600913159959</v>
       </c>
       <c r="D1956" t="n">
         <v>-4.08068408827207</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.084676934305177</v>
+        <v>0.9589708535373831</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.01801545228333978</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.70649772255775</v>
+        <v>2.580791641789955</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46544,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011242</v>
+        <v>3.750729377011243</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.711093969234168</v>
+        <v>2.585387888466373</v>
       </c>
       <c r="D1957" t="n">
         <v>-3.901308667033303</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.150214078107099</v>
+        <v>1.024507997339305</v>
       </c>
       <c r="F1957" t="n">
         <v>0.1387613058873789</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.794350752766595</v>
+        <v>2.668644671998801</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46567,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982236</v>
+        <v>3.716991718982237</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.691901424565757</v>
+        <v>2.566195343797963</v>
       </c>
       <c r="D1958" t="n">
         <v>-3.946322880553909</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.113015848030446</v>
+        <v>0.9873097672626518</v>
       </c>
       <c r="F1958" t="n">
         <v>0.1084124105727743</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.756948870909422</v>
+        <v>2.631242790141628</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46590,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509544</v>
+        <v>3.737026608509546</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.697592986904703</v>
+        <v>2.571886906136909</v>
       </c>
       <c r="D1959" t="n">
         <v>-4.213327390826344</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.011905606260418</v>
+        <v>0.8861995254926234</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.08595062747017429</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.646022610422599</v>
+        <v>2.520316529654804</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46613,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760815</v>
+        <v>3.702309454760817</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.696796908801204</v>
+        <v>2.57109082803341</v>
       </c>
       <c r="D1960" t="n">
         <v>-4.314525172263517</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.97063041558205</v>
+        <v>0.8449243348142557</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.1543594410154935</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.604181244191909</v>
+        <v>2.478475163424114</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46636,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815459</v>
+        <v>3.705571661815461</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.694396870355521</v>
+        <v>2.568690789587727</v>
       </c>
       <c r="D1961" t="n">
         <v>-4.308014205649204</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9708347637820918</v>
+        <v>0.8451286830142974</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.1543594410154935</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.601781205746225</v>
+        <v>2.476075124978431</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46659,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.709510443378106</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.690921589563766</v>
+        <v>2.565215508795972</v>
       </c>
       <c r="D1962" t="n">
         <v>-4.288976077941907</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9749747340732557</v>
+        <v>0.8492686533054614</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.212543052346688</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.563395758155754</v>
+        <v>2.437689677387959</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46682,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131255</v>
+        <v>3.731064473131257</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.868503458502447</v>
+        <v>2.742797377734652</v>
       </c>
       <c r="D1963" t="n">
         <v>-4.320102709092525</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.140105950551689</v>
+        <v>1.014399869783895</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.212543052346688</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.740977627094434</v>
+        <v>2.61527154632664</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46705,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067872</v>
+        <v>3.722447362067873</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.86933678748858</v>
+        <v>2.743630706720786</v>
       </c>
       <c r="D1964" t="n">
         <v>-4.333969470426443</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.135392575004255</v>
+        <v>1.009686494236461</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.250400969080511</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.719096206040274</v>
+        <v>2.59339012527248</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46728,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789128</v>
+        <v>3.787425580789129</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.875345317885506</v>
+        <v>2.749639237117712</v>
       </c>
       <c r="D1965" t="n">
         <v>-4.289165298886513</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.159322774017153</v>
+        <v>1.033616693249359</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.250400969080511</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.7251047364372</v>
+        <v>2.599398655669406</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46751,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519915</v>
+        <v>3.781501250519916</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.954497965677528</v>
+        <v>2.828791884909734</v>
       </c>
       <c r="D1966" t="n">
         <v>-4.141422328651511</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.297572609903176</v>
+        <v>1.171866529135382</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.0825936118456278</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.904941798570152</v>
+        <v>2.779235717802357</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46774,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181177</v>
+        <v>3.802245929181178</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.957291587209009</v>
+        <v>2.831585506441215</v>
       </c>
       <c r="D1967" t="n">
         <v>-4.243437011182732</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.259560358422169</v>
+        <v>1.133854277654374</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.0825936118456278</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.907735420101633</v>
+        <v>2.782029339333838</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46797,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394737</v>
+        <v>3.805608985394739</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.957953935600667</v>
+        <v>2.832247854832873</v>
       </c>
       <c r="D1968" t="n">
         <v>-4.237284305129948</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.262683789234941</v>
+        <v>1.136977708467146</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.07644090579284352</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.912089392124962</v>
+        <v>2.786383311357167</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46820,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890615</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.957034412340778</v>
+        <v>2.831328331572983</v>
       </c>
       <c r="D1969" t="n">
         <v>-4.25409360328045</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.25504054671485</v>
+        <v>1.129334465947056</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.09325020394334516</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.901084289974771</v>
+        <v>2.775378209206977</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46843,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798431</v>
+        <v>3.867362636798433</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.023369966137599</v>
+        <v>2.897663885369804</v>
       </c>
       <c r="D1970" t="n">
         <v>-4.191795604504327</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.34629530002212</v>
+        <v>1.220589219254326</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.09325020394334516</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.967419843771592</v>
+        <v>2.841713763003797</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46866,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992198</v>
+        <v>3.8487291399922</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>2.606244757759202</v>
       </c>
       <c r="D1971" t="n">
         <v>-3.990005406839169</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.135592251477581</v>
+        <v>1.009886170709787</v>
       </c>
       <c r="F1971" t="n">
         <v>0.1047679882258092</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.794811631462482</v>
+        <v>2.669105550694688</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46889,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852428</v>
+        <v>3.841444817852429</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>2.676534990081378</v>
       </c>
       <c r="D1972" t="n">
         <v>-3.916627309750433</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.235233722635251</v>
+        <v>1.109527641867457</v>
       </c>
       <c r="F1972" t="n">
         <v>0.1781460853145458</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.9091287220379</v>
+        <v>2.783422641270105</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46912,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319552</v>
+        <v>3.819063300319554</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>2.691162726197421</v>
       </c>
       <c r="D1973" t="n">
         <v>-4.014367854375407</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.210765240901305</v>
+        <v>1.085059160133511</v>
       </c>
       <c r="F1973" t="n">
         <v>0.1622568071815656</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.914222891274155</v>
+        <v>2.788516810506361</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46935,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489391</v>
+        <v>3.831819032489393</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>2.689698707022093</v>
       </c>
       <c r="D1974" t="n">
         <v>-4.190705614498336</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.138766117676805</v>
+        <v>1.013060036909011</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.0140809529413638</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.806956216025069</v>
+        <v>2.681250135257275</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46958,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397801</v>
+        <v>3.836411672397802</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>2.688190325062021</v>
       </c>
       <c r="D1975" t="n">
         <v>-4.114283568066409</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.167826554289504</v>
+        <v>1.04212047352171</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.0140809529413638</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.805447834064998</v>
+        <v>2.679741753297203</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46981,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316255</v>
+        <v>3.833513460316257</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>2.688053192497458</v>
       </c>
       <c r="D1976" t="n">
         <v>-4.069910436427841</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.185438674380368</v>
+        <v>1.059732593612574</v>
       </c>
       <c r="F1976" t="n">
         <v>0.0302921786972048</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.831934580483575</v>
+        <v>2.706228499715781</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47004,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105969</v>
+        <v>3.821562117105971</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.808153067403842</v>
+        <v>2.682446986636048</v>
       </c>
       <c r="D1977" t="n">
         <v>-3.947076215540673</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.228966156873825</v>
+        <v>1.103260076106031</v>
       </c>
       <c r="F1977" t="n">
         <v>0.0302921786972048</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.826328374622165</v>
+        <v>2.700622293854371</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47030,19 @@
         <v>3.833011148190328</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.814534824431647</v>
+        <v>2.688828743663852</v>
       </c>
       <c r="D1978" t="n">
         <v>-3.899420484979617</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.254410206126052</v>
+        <v>1.128704125358258</v>
       </c>
       <c r="F1978" t="n">
         <v>0.07794790925826045</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.861303569986603</v>
+        <v>2.735597489218809</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47050,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.82267821056962</v>
+        <v>3.822678210569621</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.819427197806371</v>
+        <v>2.693721117038577</v>
       </c>
       <c r="D1979" t="n">
         <v>-3.798902326480863</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.299509842900279</v>
+        <v>1.173803762132484</v>
       </c>
       <c r="F1979" t="n">
         <v>0.178466067757015</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.926506838460581</v>
+        <v>2.800800757692786</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47076,19 @@
         <v>3.828808877557297</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.806181870282244</v>
+        <v>2.680475789514449</v>
       </c>
       <c r="D1980" t="n">
         <v>-3.859568916883252</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.261997879215195</v>
+        <v>1.136291798447401</v>
       </c>
       <c r="F1980" t="n">
         <v>0.09676775103848134</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.864242520905333</v>
+        <v>2.738536440137538</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47099,19 @@
         <v>3.816837033932772</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.810279572892872</v>
+        <v>2.684573492125078</v>
       </c>
       <c r="D1981" t="n">
         <v>-3.814730515274854</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.284030942469183</v>
+        <v>1.158324861701389</v>
       </c>
       <c r="F1981" t="n">
         <v>0.1013111839833508</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.871066283282883</v>
+        <v>2.745360202515088</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47122,19 @@
         <v>3.817932354917057</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.81444051252395</v>
+        <v>2.688734431756156</v>
       </c>
       <c r="D1982" t="n">
         <v>-3.915489151031852</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.247888427797462</v>
+        <v>1.122182347029667</v>
       </c>
       <c r="F1982" t="n">
         <v>0.01248561525634539</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.821931881677758</v>
+        <v>2.696225800909963</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47145,19 @@
         <v>3.826684745405966</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.820320115051787</v>
+        <v>2.694614034283993</v>
       </c>
       <c r="D1983" t="n">
         <v>-3.871286313945952</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.271449165159659</v>
+        <v>1.145743084391865</v>
       </c>
       <c r="F1983" t="n">
         <v>0.05668845234224584</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.854333186457135</v>
+        <v>2.728627105689341</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47168,19 @@
         <v>3.838199629265651</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.818730115521035</v>
+        <v>2.693024034753241</v>
       </c>
       <c r="D1984" t="n">
         <v>-3.908265341609395</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.255067554563529</v>
+        <v>1.129361473795735</v>
       </c>
       <c r="F1984" t="n">
         <v>0.09366235413357638</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.874927528001181</v>
+        <v>2.749221447233387</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47191,19 @@
         <v>3.863895080284885</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.869977880704075</v>
+        <v>2.74427179993628</v>
       </c>
       <c r="D1985" t="n">
         <v>-3.928323420474235</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.298292088200633</v>
+        <v>1.172586007432838</v>
       </c>
       <c r="F1985" t="n">
         <v>0.09366235413357638</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.926175293184221</v>
+        <v>2.800469212416426</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47214,19 @@
         <v>3.865338681321028</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.868418585298328</v>
+        <v>2.742712504530533</v>
       </c>
       <c r="D1986" t="n">
         <v>-3.888392747296345</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.312705062066042</v>
+        <v>1.186998981298248</v>
       </c>
       <c r="F1986" t="n">
         <v>0.1335930273114667</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.948574401685208</v>
+        <v>2.822868320917414</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47237,19 @@
         <v>3.864489842475145</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.863366813536598</v>
+        <v>2.737660732768803</v>
       </c>
       <c r="D1987" t="n">
         <v>-3.837360654573817</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.328066127393323</v>
+        <v>1.202360046625529</v>
       </c>
       <c r="F1987" t="n">
         <v>0.1846251200339947</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.974141885556995</v>
+        <v>2.8484358047892</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47260,19 @@
         <v>3.84254736040486</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.880554217629303</v>
+        <v>2.754848136861508</v>
       </c>
       <c r="D1988" t="n">
         <v>-3.772136473446611</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.37134320393691</v>
+        <v>1.245637123169116</v>
       </c>
       <c r="F1988" t="n">
         <v>0.2498493011612003</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.030463798326023</v>
+        <v>2.904757717558229</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47283,19 @@
         <v>3.840061186882564</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.876515189928583</v>
+        <v>2.750809109160789</v>
       </c>
       <c r="D1989" t="n">
         <v>-3.734709453375478</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.382274984264644</v>
+        <v>1.25656890349685</v>
       </c>
       <c r="F1989" t="n">
         <v>0.255100839190382</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.029575693442812</v>
+        <v>2.903869612675018</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47306,19 @@
         <v>3.845169808992669</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.877771982259823</v>
+        <v>2.752065901492029</v>
       </c>
       <c r="D1990" t="n">
         <v>-3.754821109410186</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.375487114182001</v>
+        <v>1.249781033414207</v>
       </c>
       <c r="F1990" t="n">
         <v>0.2661281841878012</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.037448892772504</v>
+        <v>2.91174281200471</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47329,19 @@
         <v>3.828661445636294</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.038329753281034</v>
+        <v>2.91262367251324</v>
       </c>
       <c r="D1991" t="n">
         <v>-3.701076294982981</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.557542810974094</v>
+        <v>1.4318367302063</v>
       </c>
       <c r="F1991" t="n">
         <v>0.2761914936282631</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.204044649457992</v>
+        <v>3.078338568690198</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47352,19 @@
         <v>3.813222820957632</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.158442662498851</v>
+        <v>3.032736581731057</v>
       </c>
       <c r="D1992" t="n">
         <v>-3.677284726376839</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.687172347634368</v>
+        <v>1.561466266866574</v>
       </c>
       <c r="F1992" t="n">
         <v>0.2999830622344054</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.338432499839495</v>
+        <v>3.2127264190717</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47375,19 @@
         <v>3.814230727998758</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.15015063851271</v>
+        <v>3.024444557744916</v>
       </c>
       <c r="D1993" t="n">
         <v>-3.651200642113031</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.68931395735375</v>
+        <v>1.563607876585956</v>
       </c>
       <c r="F1993" t="n">
         <v>0.2999830622344054</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.330140475853354</v>
+        <v>3.204434395085559</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47398,19 @@
         <v>3.803397818896932</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.14834383409649</v>
+        <v>3.022637753328695</v>
       </c>
       <c r="D1994" t="n">
         <v>-3.573069461264084</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.718759625277108</v>
+        <v>1.593053544509314</v>
       </c>
       <c r="F1994" t="n">
         <v>0.37415987311809</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.372839757967344</v>
+        <v>3.24713367719955</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47421,19 @@
         <v>3.796264143959863</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.165898239823281</v>
+        <v>3.040192159055487</v>
       </c>
       <c r="D1995" t="n">
         <v>-3.564176999870801</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.739871015561213</v>
+        <v>1.614164934793419</v>
       </c>
       <c r="F1995" t="n">
         <v>0.37415987311809</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.390394163694135</v>
+        <v>3.264688082926341</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47444,19 @@
         <v>3.794424941945373</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.157753287227865</v>
+        <v>3.032047206460071</v>
       </c>
       <c r="D1996" t="n">
         <v>-3.732653116840679</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.664335616177846</v>
+        <v>1.538629535410052</v>
       </c>
       <c r="F1996" t="n">
         <v>0.3462120374015092</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.365480509668771</v>
+        <v>3.239774428900977</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47467,19 @@
         <v>3.795574066782715</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.139022984415727</v>
+        <v>3.013316903647933</v>
       </c>
       <c r="D1997" t="n">
         <v>-3.034853587979096</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.924725124910341</v>
+        <v>1.799019044142547</v>
       </c>
       <c r="F1997" t="n">
         <v>0.2758639780310985</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.304541371234386</v>
+        <v>3.178835290466592</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47490,19 @@
         <v>3.784671345632645</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.129687006912631</v>
+        <v>3.003980926144837</v>
       </c>
       <c r="D1998" t="n">
         <v>-3.012132484295943</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.924477588880507</v>
+        <v>1.798771508112712</v>
       </c>
       <c r="F1998" t="n">
         <v>0.2758639780310985</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.295205393731291</v>
+        <v>3.169499312963497</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47513,19 @@
         <v>3.783205696777682</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.2885931327638</v>
+        <v>3.162887051996006</v>
       </c>
       <c r="D1999" t="n">
         <v>-3.010407441005899</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.084073732047693</v>
+        <v>1.958367651279899</v>
       </c>
       <c r="F1999" t="n">
         <v>0.2775890213211422</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.455146545556486</v>
+        <v>3.329440464788692</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47536,19 @@
         <v>3.779933725644421</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.325670955257447</v>
+        <v>3.199964874489653</v>
       </c>
       <c r="D2000" t="n">
         <v>-3.165188447784154</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.059239151830038</v>
+        <v>1.933533071062243</v>
       </c>
       <c r="F2000" t="n">
         <v>0.2442213472666661</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.472203763617447</v>
+        <v>3.346497682849653</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47559,19 @@
         <v>3.769443619799968</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.322346311246992</v>
+        <v>3.196640230479198</v>
       </c>
       <c r="D2001" t="n">
         <v>-3.113753114399495</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.076488641173447</v>
+        <v>1.950782560405652</v>
       </c>
       <c r="F2001" t="n">
         <v>0.2956566806513258</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.499740319637788</v>
+        <v>3.374034238869994</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47582,19 @@
         <v>3.766673496331124</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.332352464891734</v>
+        <v>3.206646384123939</v>
       </c>
       <c r="D2002" t="n">
         <v>-3.086801890073007</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.097275284548783</v>
+        <v>1.971569203780989</v>
       </c>
       <c r="F2002" t="n">
         <v>0.3105370266790449</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.518674680899161</v>
+        <v>3.392968600131367</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47605,19 @@
         <v>3.768052067784117</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.516455597036694</v>
+        <v>3.390749516268899</v>
       </c>
       <c r="D2003" t="n">
         <v>-3.222754898129323</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.226997213471217</v>
+        <v>2.101291132703422</v>
       </c>
       <c r="F2003" t="n">
         <v>0.3105370266790449</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.702777813044121</v>
+        <v>3.577071732276326</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47628,19 @@
         <v>3.74392550571443</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.508572291939687</v>
+        <v>3.382866211171892</v>
       </c>
       <c r="D2004" t="n">
         <v>-3.245163015934195</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.210150661252261</v>
+        <v>2.084444580484467</v>
       </c>
       <c r="F2004" t="n">
         <v>0.3105370266790449</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.694894507947114</v>
+        <v>3.56918842717932</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47651,19 @@
         <v>3.719118627155041</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.510626291489324</v>
+        <v>3.38492021072153</v>
       </c>
       <c r="D2005" t="n">
         <v>-3.393168783413595</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.153002353810138</v>
+        <v>2.027296273042344</v>
       </c>
       <c r="F2005" t="n">
         <v>0.2238100178155035</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.644912302178626</v>
+        <v>3.519206221410832</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47674,19 @@
         <v>3.729452285161986</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.566880009211171</v>
+        <v>3.441173928443377</v>
       </c>
       <c r="D2006" t="n">
         <v>-3.402609709302125</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.205479701176574</v>
+        <v>2.079773620408779</v>
       </c>
       <c r="F2006" t="n">
         <v>0.3462371353588949</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.774622290426509</v>
+        <v>3.648916209658714</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47697,19 @@
         <v>3.714941193321643</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.569771103756472</v>
+        <v>3.444065022988678</v>
       </c>
       <c r="D2007" t="n">
         <v>-3.401322945762568</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.208885501137697</v>
+        <v>2.083179420369903</v>
       </c>
       <c r="F2007" t="n">
         <v>0.3475238988984515</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.778285443095543</v>
+        <v>3.652579362327749</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47720,19 @@
         <v>3.727898186347711</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.567882916650247</v>
+        <v>3.442176835882453</v>
       </c>
       <c r="D2008" t="n">
         <v>-3.40287999975186</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.206374492435756</v>
+        <v>2.080668411667961</v>
       </c>
       <c r="F2008" t="n">
         <v>0.3475238988984515</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.776397255989318</v>
+        <v>3.650691175221524</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47743,19 @@
         <v>3.710654104887755</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.56270314625311</v>
+        <v>3.436997065485315</v>
       </c>
       <c r="D2009" t="n">
         <v>-3.410151885275324</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.198285967829232</v>
+        <v>2.072579887061438</v>
       </c>
       <c r="F2009" t="n">
         <v>0.3402520133749867</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.766854354278102</v>
+        <v>3.641148273510308</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47766,19 @@
         <v>3.712897612343073</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.561137156463262</v>
+        <v>3.435431075695468</v>
       </c>
       <c r="D2010" t="n">
         <v>-3.408310866217073</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.197456385662685</v>
+        <v>2.071750304894891</v>
       </c>
       <c r="F2010" t="n">
         <v>0.3415202400464551</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.766049300491135</v>
+        <v>3.640343219723341</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47789,19 @@
         <v>3.754911907647114</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.574210563329181</v>
+        <v>3.448504482561386</v>
       </c>
       <c r="D2011" t="n">
         <v>-3.415219571716753</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.207766310328731</v>
+        <v>2.082060229560937</v>
       </c>
       <c r="F2011" t="n">
         <v>0.3415202400464551</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.779122707357054</v>
+        <v>3.65341662658926</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47812,19 @@
         <v>3.749896851763537</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.574210563329181</v>
+        <v>3.448504482561386</v>
       </c>
       <c r="D2012" t="n">
         <v>-3.416781214531613</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.207141653202788</v>
+        <v>2.081435572434994</v>
       </c>
       <c r="F2012" t="n">
         <v>0.3415202400464551</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.779122707357054</v>
+        <v>3.65341662658926</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47832,45 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.85064586963974</v>
+        <v>3.715834055392119</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.572734604456183</v>
+        <v>3.447028523688388</v>
       </c>
       <c r="D2013" t="n">
         <v>-3.444682001641086</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.194505379486</v>
+        <v>2.068799298718206</v>
       </c>
       <c r="F2013" t="n">
         <v>0.3069233159035203</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.756888593998295</v>
+        <v>3.631182513230501</v>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" s="2" t="n">
+        <v>45476</v>
+      </c>
+      <c r="B2014" t="n">
+        <v>3.815648773041493</v>
+      </c>
+      <c r="C2014" t="n">
+        <v>3.613405510609233</v>
+      </c>
+      <c r="D2014" t="n">
+        <v>-3.444682001641086</v>
+      </c>
+      <c r="E2014" t="n">
+        <v>2.068799298718206</v>
+      </c>
+      <c r="F2014" t="n">
+        <v>0.3069233159035203</v>
+      </c>
+      <c r="G2014" t="n">
+        <v>3.606469307595601</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240703.xlsx
+++ b/tame_output/ON/bt/strategyON_20240703.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -709,8 +709,10 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="Y2" t="n">
-        <v>1</v>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -744,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>15.9%</t>
         </is>
       </c>
     </row>
@@ -756,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>78.5%</t>
+          <t>71.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -817,22 +819,22 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-31.8%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -847,30 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
-      <c r="Y3" t="n">
-        <v>-0.0616172931916848</v>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>-5.9%</t>
+        </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>25.3%</t>
         </is>
       </c>
     </row>
@@ -912,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.9%</t>
+          <t>-74.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -945,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.5%</t>
+          <t>123.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>93.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,27 +977,27 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-658.8%</t>
+          <t>-680.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.7%</t>
+          <t>-50.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1003,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.2%</t>
+          <t>-70.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1021,12 +1025,14 @@
           <t>-0.1</t>
         </is>
       </c>
-      <c r="Y4" t="n">
-        <v>4.258812073042996</v>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>447.2%</t>
+        </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1056,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-506.0%</t>
+          <t>-551.3%</t>
         </is>
       </c>
     </row>
@@ -1068,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1101,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1129,17 +1135,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-263.9%</t>
+          <t>-272.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1149,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-36.6%</t>
+          <t>-37.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1159,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1177,12 +1183,14 @@
           <t>0.1</t>
         </is>
       </c>
-      <c r="Y5" t="n">
-        <v>102.5183581257701</v>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>-23.9%</t>
+        </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>-42.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1212,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-169.3%</t>
+          <t>-185.8%</t>
         </is>
       </c>
     </row>
@@ -1224,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-22.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1257,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1285,12 +1293,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-279.1%</t>
+          <t>-300.5%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1305,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-29.9%</t>
+          <t>-31.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1315,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1333,12 +1341,14 @@
           <t>-0.1</t>
         </is>
       </c>
-      <c r="Y6" t="n">
-        <v>1.097788583625984</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>82.1%</t>
+        </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-136.7%</t>
+          <t>-160.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1368,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-193.3%</t>
+          <t>-225.7%</t>
         </is>
       </c>
     </row>
@@ -1380,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1413,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.5%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1441,12 +1451,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-167.9%</t>
+          <t>-180.7%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1461,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-25.3%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1471,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1489,12 +1499,14 @@
           <t>0.1</t>
         </is>
       </c>
-      <c r="Y7" t="n">
-        <v>-0.1700699457340738</v>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>-16.5%</t>
+        </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1524,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-85.4%</t>
+          <t>-109.8%</t>
         </is>
       </c>
     </row>
@@ -43721,16 +43733,16 @@
         <v>3.13991794227561</v>
       </c>
       <c r="D1834" t="n">
-        <v>0.9638453345512126</v>
+        <v>0.7497961784502833</v>
       </c>
       <c r="E1834" t="n">
-        <v>3.525099651782348</v>
+        <v>3.439479989341976</v>
       </c>
       <c r="F1834" t="n">
-        <v>1.845813780780637</v>
+        <v>1.631764624679707</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.247406210743993</v>
+        <v>4.118976717083434</v>
       </c>
     </row>
     <row r="1835">
@@ -43744,16 +43756,16 @@
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.7672949234980071</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.44473732322341</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1835" t="n">
-        <v>1.88246794646914</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.267656546019438</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1836">
@@ -43767,16 +43779,16 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.6137755390125424</v>
+        <v>0.3997263829116132</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.363154842056671</v>
+        <v>3.2775351796163</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.919434420938664</v>
+        <v>1.705385264837735</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.2696617033286</v>
+        <v>4.141232209668043</v>
       </c>
     </row>
     <row r="1837">
@@ -43790,16 +43802,16 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.549401769195011</v>
+        <v>0.3353526130940819</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.337894472855533</v>
+        <v>3.252274810415162</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.919434420938664</v>
+        <v>1.705385264837735</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.270150842054475</v>
+        <v>4.141721348393917</v>
       </c>
     </row>
     <row r="1838">
@@ -43813,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.4129568789675984</v>
+        <v>0.1989077228666692</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.287396499386235</v>
+        <v>3.201776836945863</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.782989530711252</v>
+        <v>1.568940374610322</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.192363890539694</v>
+        <v>4.063934396879136</v>
       </c>
     </row>
     <row r="1839">
@@ -43836,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.1758253871178033</v>
+        <v>-0.03822376898312591</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.227484987143858</v>
+        <v>3.141865324703487</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.782989530711252</v>
+        <v>1.568940374610322</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.227304975037235</v>
+        <v>4.098875481376678</v>
       </c>
     </row>
     <row r="1840">
@@ -43859,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.1808629778453898</v>
+        <v>-0.03318617825553938</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.228077463620231</v>
+        <v>3.142457801179859</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.838633986977569</v>
+        <v>1.62458483087664</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.259269088982364</v>
+        <v>4.130839595321806</v>
       </c>
     </row>
     <row r="1841">
@@ -43882,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.07633105686266695</v>
+        <v>-0.2903802129635961</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.103946231360745</v>
+        <v>3.018326568920374</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.581439952269512</v>
+        <v>1.367390796168583</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.083699049781267</v>
+        <v>3.95526955612071</v>
       </c>
     </row>
     <row r="1842">
@@ -43905,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.142098446912079</v>
+        <v>-0.3561476030130082</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.078656884471451</v>
+        <v>2.993037222031079</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.581439952269512</v>
+        <v>1.367390796168583</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.084716658911737</v>
+        <v>3.95628716525118</v>
       </c>
     </row>
     <row r="1843">
@@ -43928,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.3473431239693236</v>
+        <v>-0.5613922800702528</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.987187045636309</v>
+        <v>2.901567383195937</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.581439952269512</v>
+        <v>1.367390796168583</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.075344690899493</v>
+        <v>3.946915197238935</v>
       </c>
     </row>
     <row r="1844">
@@ -43951,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.4291150243970753</v>
+        <v>-0.6431641804980044</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.944561011420446</v>
+        <v>2.858941348980074</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.608475525675649</v>
+        <v>1.394426369574719</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.081648760898413</v>
+        <v>3.953219267237856</v>
       </c>
     </row>
     <row r="1845">
@@ -43974,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.4963241322689529</v>
+        <v>-0.7103732883698821</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.922442685105398</v>
+        <v>2.836823022665026</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.608475525675649</v>
+        <v>1.394426369574719</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.086414077732115</v>
+        <v>3.957984584071558</v>
       </c>
     </row>
     <row r="1846">
@@ -43997,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.7038899166605648</v>
+        <v>-0.917939072761494</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.837241167467993</v>
+        <v>2.751621505027621</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.400909741284037</v>
+        <v>1.186860585183108</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.959699403216389</v>
+        <v>3.831269909555831</v>
       </c>
     </row>
     <row r="1847">
@@ -44020,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.121643940207402</v>
+        <v>-1.335693096308331</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.668066449554321</v>
+        <v>2.58244678711395</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.9831557177371998</v>
+        <v>0.7691065616362706</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.706973880593349</v>
+        <v>3.578544386932792</v>
       </c>
     </row>
     <row r="1848">
@@ -44043,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.411775606812833</v>
+        <v>-1.625824762913762</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.551879999511071</v>
+        <v>2.466260337070699</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.00723751247738</v>
+        <v>0.7931883563764505</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.721289174036379</v>
+        <v>3.592859680375822</v>
       </c>
     </row>
     <row r="1849">
@@ -44066,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.61977966516591</v>
+        <v>-1.83382882126684</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.473570520723765</v>
+        <v>2.387950858283393</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.00723751247738</v>
+        <v>0.7931883563764505</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.726181318590304</v>
+        <v>3.597751824929747</v>
       </c>
     </row>
     <row r="1850">
@@ -44089,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.831192086053886</v>
+        <v>-2.045241242154815</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.384087008706563</v>
+        <v>2.298467346266191</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.7958250915894045</v>
+        <v>0.5817759354884754</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.594415322395507</v>
+        <v>3.46598582873495</v>
       </c>
     </row>
     <row r="1851">
@@ -44112,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.197260813198538</v>
+        <v>-2.411309969299468</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.230743817155151</v>
+        <v>2.145124154714779</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.4297563644447518</v>
+        <v>0.2157072083438227</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.367858385415165</v>
+        <v>3.239428891754608</v>
       </c>
     </row>
     <row r="1852">
@@ -44135,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.405751594650222</v>
+        <v>-2.619800750751152</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.167685794313245</v>
+        <v>2.082066131872874</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.2212655829930674</v>
+        <v>0.007216426892138306</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.263102206282923</v>
+        <v>3.134672712622365</v>
       </c>
     </row>
     <row r="1853">
@@ -44158,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.652952779415444</v>
+        <v>-2.867001935516374</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.076904070815726</v>
+        <v>1.991284408375353</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.2414189364918798</v>
+        <v>0.02736978039095073</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.283292968790779</v>
+        <v>3.154863475130221</v>
       </c>
     </row>
     <row r="1854">
@@ -44181,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.145337807439541</v>
+        <v>-3.359386963540471</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.881056451649819</v>
+        <v>1.795436789209447</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.2509660915322169</v>
+        <v>-0.465015247633146</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.988968344020053</v>
+        <v>2.860538850359495</v>
       </c>
     </row>
     <row r="1855">
@@ -44204,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.530518198369613</v>
+        <v>-3.744567354470543</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.725526834090653</v>
+        <v>1.639907171650281</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.2509660915322169</v>
+        <v>-0.465015247633146</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.987510882832916</v>
+        <v>2.859081389172359</v>
       </c>
     </row>
     <row r="1856">
@@ -44227,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.780388878384195</v>
+        <v>-3.994438034485125</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.627347685539437</v>
+        <v>1.541728023099065</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.2147033717017536</v>
+        <v>-0.4287525278026827</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.01103763818581</v>
+        <v>2.882608144525252</v>
       </c>
     </row>
     <row r="1857">
@@ -44250,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.986900655271216</v>
+        <v>-4.200949811372146</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.540849033440886</v>
+        <v>1.455229371000514</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.4212151485887751</v>
+        <v>-0.6352643046897042</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.883236630709855</v>
+        <v>2.754807137049298</v>
       </c>
     </row>
     <row r="1858">
@@ -44273,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.306244730351718</v>
+        <v>-4.520293886452648</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.414884330108945</v>
+        <v>1.329264667668573</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.4212151485887751</v>
+        <v>-0.6352643046897042</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.885009557410115</v>
+        <v>2.756580063749557</v>
       </c>
     </row>
     <row r="1859">
@@ -44296,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.738050523501506</v>
+        <v>-4.952099679602435</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.228494900316434</v>
+        <v>1.142875237876062</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.5576326450300422</v>
+        <v>-0.7716818011309712</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.789491947012759</v>
+        <v>2.661062453352201</v>
       </c>
     </row>
     <row r="1860">
@@ -44319,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.972744517634058</v>
+        <v>-5.186793673734988</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.122902077665504</v>
+        <v>1.037282415225132</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.551296377800787</v>
+        <v>-0.765345533901716</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.781578482352403</v>
+        <v>2.653148988691845</v>
       </c>
     </row>
     <row r="1861">
@@ -44342,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.30840716486451</v>
+        <v>-5.52245632096544</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9872176104292882</v>
+        <v>0.9015979479889165</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.6192273632896919</v>
+        <v>-0.8332765193906209</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.739400482715025</v>
+        <v>2.610970989054468</v>
       </c>
     </row>
     <row r="1862">
@@ -44365,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.672033409764824</v>
+        <v>-5.886082565865753</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8482546727034044</v>
+        <v>0.7626350102630326</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.7174490001568177</v>
+        <v>-0.9314981562577467</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.686955060828991</v>
+        <v>2.558525567168433</v>
       </c>
     </row>
     <row r="1863">
@@ -44388,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.03716079240357</v>
+        <v>-6.2512099485045</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.701458234653737</v>
+        <v>0.6158385722133652</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.01375978445583</v>
+        <v>-1.227808940556759</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.508423105255415</v>
+        <v>2.379993611594857</v>
       </c>
     </row>
     <row r="1864">
@@ -44411,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.445749569584249</v>
+        <v>-6.659798725685178</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5367842677962247</v>
+        <v>0.4511646053558529</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.422348561636509</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.262031382961767</v>
+        <v>2.133601889301209</v>
       </c>
     </row>
     <row r="1865">
@@ -44434,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.722325669900082</v>
+        <v>-6.936374826001011</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.4213392601413521</v>
+        <v>0.3357195977009808</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.422348561636509</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.257216815433227</v>
+        <v>2.12878732177267</v>
       </c>
     </row>
     <row r="1866">
@@ -44457,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.138717544187079</v>
+        <v>-7.352766700288008</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2527765610354304</v>
+        <v>0.1671568985950591</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.422348561636509</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.255210866042105</v>
+        <v>2.126781372381547</v>
       </c>
     </row>
     <row r="1867">
@@ -44480,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.382988944914149</v>
+        <v>-7.597038101015078</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1653266914132816</v>
+        <v>0.07970702897291027</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.422348561636509</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.265469556710784</v>
+        <v>2.137040063050226</v>
       </c>
     </row>
     <row r="1868">
@@ -44503,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.588239964150909</v>
+        <v>-7.802289120251838</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.07932584886427296</v>
+        <v>-0.006293813576098817</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.422348561636509</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.261569121856479</v>
+        <v>2.133139628195922</v>
       </c>
     </row>
     <row r="1869">
@@ -44526,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.751819842335292</v>
+        <v>-7.965868998436221</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.01229881764552054</v>
+        <v>-0.07332084479485124</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.422348561636509</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.25997404191148</v>
+        <v>2.131544548250923</v>
       </c>
     </row>
     <row r="1870">
@@ -44549,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.048481184145491</v>
+        <v>-8.262530340246419</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.1025867431493506</v>
+        <v>-0.1882064055897223</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.491091697370387</v>
+        <v>-1.705140853471316</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.222507136400361</v>
+        <v>2.094077642739804</v>
       </c>
     </row>
     <row r="1871">
@@ -44572,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.235200892454793</v>
+        <v>-8.449250048555722</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.1813009310074749</v>
+        <v>-0.2669205934478462</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.491091697370387</v>
+        <v>-1.705140853471316</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.218480831865958</v>
+        <v>2.0900513382054</v>
       </c>
     </row>
     <row r="1872">
@@ -44595,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.618202281197425</v>
+        <v>-8.832251437298353</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.3346035878261113</v>
+        <v>-0.4202232502664831</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.491091697370387</v>
+        <v>-1.705140853471316</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.218378730544374</v>
+        <v>2.089949236883816</v>
       </c>
     </row>
     <row r="1873">
@@ -44618,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.800072072182459</v>
+        <v>-9.014121228283388</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4047799882486953</v>
+        <v>-0.4903996506890667</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.672961488355422</v>
+        <v>-1.887010644456351</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.111828371924783</v>
+        <v>1.983398878264226</v>
       </c>
     </row>
     <row r="1874">
@@ -44641,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.159602394686461</v>
+        <v>-9.37365155078739</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.5432418139522457</v>
+        <v>-0.628861476392617</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.672961488355422</v>
+        <v>-1.887010644456351</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.117178675222833</v>
+        <v>1.988749181562276</v>
       </c>
     </row>
     <row r="1875">
@@ -44664,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.209951458140683</v>
+        <v>-9.424000614241612</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.5554654193767568</v>
+        <v>-0.6410850818171285</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.723310551809644</v>
+        <v>-1.937359707910573</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.094885257107477</v>
+        <v>1.96645576344692</v>
       </c>
     </row>
     <row r="1876">
@@ -44687,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.307570735562079</v>
+        <v>-9.521619891663008</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.5914713797235467</v>
+        <v>-0.677091042163918</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.820929829231041</v>
+        <v>-2.03497898533197</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.039355441276408</v>
+        <v>1.91092594761585</v>
       </c>
     </row>
     <row r="1877">
@@ -44710,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.455096823567722</v>
+        <v>-9.669145979668651</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.6475882586042316</v>
+        <v>-0.733207921044603</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.968455917236684</v>
+        <v>-2.182505073337614</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.953733344794594</v>
+        <v>1.825303851134037</v>
       </c>
     </row>
     <row r="1878">
@@ -44733,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.659354998897586</v>
+        <v>-9.873404154998514</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7237783316175346</v>
+        <v>-0.8093979940579059</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.096094861850673</v>
+        <v>-2.310144017951603</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.882663175144843</v>
+        <v>1.754233681484286</v>
       </c>
     </row>
     <row r="1879">
@@ -44756,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.693007837406059</v>
+        <v>-9.907056993506988</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.7327569125364879</v>
+        <v>-0.8183765749768592</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.196508229767711</v>
+        <v>-2.41055738586864</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.826897708879057</v>
+        <v>1.698468215218499</v>
       </c>
     </row>
     <row r="1880">
@@ -44779,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.61953800573861</v>
+        <v>-9.891203652589249</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.6879972783760873</v>
+        <v>-0.7966635371163431</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.123038398100262</v>
+        <v>-2.394704044950902</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.886351309372947</v>
+        <v>1.723351921262563</v>
       </c>
     </row>
     <row r="1881">
@@ -44802,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.794662423125153</v>
+        <v>-10.06632806997579</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.7434918245831876</v>
+        <v>-0.8521580833234434</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.298162815486806</v>
+        <v>-2.569828462337446</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.795831879688538</v>
+        <v>1.632832491578154</v>
       </c>
     </row>
     <row r="1882">
@@ -44825,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.02911451713964</v>
+        <v>-10.30078016399028</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.8444918270905792</v>
+        <v>-0.9531580858308355</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.298162815486806</v>
+        <v>-2.569828462337446</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.788612714786942</v>
+        <v>1.625613326676558</v>
       </c>
     </row>
     <row r="1883">
@@ -44848,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.13348924816609</v>
+        <v>-10.40515489501673</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.892913910275134</v>
+        <v>-1.00158016901539</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.402537546513252</v>
+        <v>-2.674203193363892</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.719315685397098</v>
+        <v>1.556316297286714</v>
       </c>
     </row>
     <row r="1884">
@@ -44871,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.18627540376642</v>
+        <v>-10.45794105061706</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.9129125826767091</v>
+        <v>-1.021578841416964</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.498213033095649</v>
+        <v>-2.769878679946289</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.663026183286216</v>
+        <v>1.500026795175832</v>
       </c>
     </row>
     <row r="1885">
@@ -44894,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.31231219713471</v>
+        <v>-10.58397784398534</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.9606335713949101</v>
+        <v>-1.069299830135165</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.472961410285906</v>
+        <v>-2.744627057136547</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.680870885601176</v>
+        <v>1.517871497490792</v>
       </c>
     </row>
     <row r="1886">
@@ -44917,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.26029668316589</v>
+        <v>-10.53196233001653</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.9358370301209833</v>
+        <v>-1.04450328886124</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.472961410285906</v>
+        <v>-2.744627057136547</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.684861221287577</v>
+        <v>1.521861833177193</v>
       </c>
     </row>
     <row r="1887">
@@ -44940,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.40196852489001</v>
+        <v>-10.67363417174065</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.9939809937093731</v>
+        <v>-1.102647252449629</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.472961410285906</v>
+        <v>-2.744627057136547</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.683385994388835</v>
+        <v>1.520386606278451</v>
       </c>
     </row>
     <row r="1888">
@@ -44963,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.35237768046518</v>
+        <v>-10.62404332731582</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.9590912457745673</v>
+        <v>-1.067757504514824</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.423370565861072</v>
+        <v>-2.695036212711713</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.728193911208608</v>
+        <v>1.565194523098224</v>
       </c>
     </row>
     <row r="1889">
@@ -44986,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.3395702874604</v>
+        <v>-10.61123593431104</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.9670194222193405</v>
+        <v>-1.075685680959597</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.472226340869974</v>
+        <v>-2.743891987720614</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.685829312556584</v>
+        <v>1.5228299244462</v>
       </c>
     </row>
     <row r="1890">
@@ -45009,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.11372513474099</v>
+        <v>-10.38539078159163</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.8671022880953676</v>
+        <v>-0.975768546835623</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.43029966528281</v>
+        <v>-2.70196531213345</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.720564390945091</v>
+        <v>1.557565002834707</v>
       </c>
     </row>
     <row r="1891">
@@ -45032,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.9891464784034</v>
+        <v>-10.26081212525404</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.8161316810042716</v>
+        <v>-0.9247979397445278</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.43029966528281</v>
+        <v>-2.70196531213345</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.72170353550115</v>
+        <v>1.558704147390766</v>
       </c>
     </row>
     <row r="1892">
@@ -45055,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.04204176644769</v>
+        <v>-10.31370741329833</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.8346560220598791</v>
+        <v>-0.9433222808001345</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.425344319194364</v>
+        <v>-2.697009966045004</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.727310517316325</v>
+        <v>1.564311129205941</v>
       </c>
     </row>
     <row r="1893">
@@ -45078,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.969908591159806</v>
+        <v>-10.24157423801045</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8000690477060899</v>
+        <v>-0.9087353064463457</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.425344319194364</v>
+        <v>-2.697009966045004</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.733044221554962</v>
+        <v>1.570044833444578</v>
       </c>
     </row>
     <row r="1894">
@@ -45101,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.898542198550158</v>
+        <v>-10.1702078454008</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.7812597530560961</v>
+        <v>-0.8899260117963514</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.353977926584716</v>
+        <v>-2.625643573435356</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.766126794726886</v>
+        <v>1.603127406616502</v>
       </c>
     </row>
     <row r="1895">
@@ -45124,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.805083164564934</v>
+        <v>-10.07674881141557</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7537596207749138</v>
+        <v>-0.8624258795151696</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.353977926584716</v>
+        <v>-2.625643573435356</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.756243313413978</v>
+        <v>1.593243925303594</v>
       </c>
     </row>
     <row r="1896">
@@ -45147,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.537841363696536</v>
+        <v>-9.809507010547176</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6486974609269285</v>
+        <v>-0.7573637196671843</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.353977926584716</v>
+        <v>-2.625643573435356</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.754408752914604</v>
+        <v>1.59140936480422</v>
       </c>
     </row>
     <row r="1897">
@@ -45170,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.439934325020046</v>
+        <v>-9.711599971870685</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6098349604297932</v>
+        <v>-0.7185012191700486</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.285992176724159</v>
+        <v>-2.557657823574799</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.794899887857477</v>
+        <v>1.631900499747093</v>
       </c>
     </row>
     <row r="1898">
@@ -45193,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.415980784044088</v>
+        <v>-9.687646430894727</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.5995850378939163</v>
+        <v>-0.7082512966341721</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.262038635748202</v>
+        <v>-2.533704282598842</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.809940518588546</v>
+        <v>1.646941130478161</v>
       </c>
     </row>
     <row r="1899">
@@ -45216,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.151920845721291</v>
+        <v>-9.42358649257193</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5072213787265496</v>
+        <v>-0.6158876374668054</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.997978697425405</v>
+        <v>-2.269644344276046</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.955116165420471</v>
+        <v>1.792116777310087</v>
       </c>
     </row>
     <row r="1900">
@@ -45239,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.444841222216454</v>
+        <v>-8.716506869067093</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2271765629849156</v>
+        <v>-0.3358428217251714</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.997978697425405</v>
+        <v>-2.269644344276046</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.95232913176017</v>
+        <v>1.789329743649786</v>
       </c>
     </row>
     <row r="1901">
@@ -45262,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.404656923850263</v>
+        <v>-8.676322570700902</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2107592197505981</v>
+        <v>-0.3194254784908539</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.957794399059215</v>
+        <v>-2.229460045909855</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.976783334667726</v>
+        <v>1.813783946557342</v>
       </c>
     </row>
     <row r="1902">
@@ -45285,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.2412570529109</v>
+        <v>-8.512922699761539</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1460324501540957</v>
+        <v>-0.2546987088943515</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.794394528119852</v>
+        <v>-2.066060174970493</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.074190078452101</v>
+        <v>1.911190690341716</v>
       </c>
     </row>
     <row r="1903">
@@ -45308,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.0077758306813</v>
+        <v>-8.27944147753194</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.04471553242440418</v>
+        <v>-0.1533817911646596</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.560913305890254</v>
+        <v>-1.832578952740894</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.222203240627712</v>
+        <v>2.059203852517328</v>
       </c>
     </row>
     <row r="1904">
@@ -45325,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785792</v>
+        <v>3.801637122785793</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.858109439673785</v>
+        <v>-8.129775086524425</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.01225881366564296</v>
+        <v>-0.09640744507461285</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.468009814647718</v>
+        <v>-1.739675461498358</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.275053125060274</v>
+        <v>2.11205373694989</v>
       </c>
     </row>
     <row r="1905">
@@ -45351,19 +45363,19 @@
         <v>3.763182248390432</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.025520419828138</v>
+        <v>3.041974488500182</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.725833966042899</v>
+        <v>-8.012368361931848</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.06516959090276941</v>
+        <v>-0.1633292805863045</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.335734341016831</v>
+        <v>-1.622268736905782</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.224079815218039</v>
+        <v>2.068613246356714</v>
       </c>
     </row>
     <row r="1906">
@@ -45374,19 +45386,19 @@
         <v>3.784718794105956</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.028335480515775</v>
+        <v>3.044789549187819</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.570095633483157</v>
+        <v>-7.856630029372107</v>
       </c>
       <c r="E1906" t="n">
-        <v>-5.919719123603784e-05</v>
+        <v>-0.09821888687477109</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.17999600845709</v>
+        <v>-1.46653040434604</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.320337875441521</v>
+        <v>2.164871306580195</v>
       </c>
     </row>
     <row r="1907">
@@ -45397,19 +45409,19 @@
         <v>3.753882571960991</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.041241821739433</v>
+        <v>3.057695890411478</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.321095834799576</v>
+        <v>-7.607630230688526</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1124470635058552</v>
+        <v>0.01428737382232015</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.17999600845709</v>
+        <v>-1.46653040434604</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.33324421666518</v>
+        <v>2.177777647803854</v>
       </c>
     </row>
     <row r="1908">
@@ -45420,19 +45432,19 @@
         <v>3.69293185560765</v>
       </c>
       <c r="C1908" t="n">
-        <v>2.913265892140214</v>
+        <v>2.929719960812259</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.42668582457268</v>
+        <v>-7.71322022046163</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.05776486200260589</v>
+        <v>-0.1559245516861409</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.285585998230194</v>
+        <v>-1.572120394119145</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.141914293202098</v>
+        <v>1.986447724340772</v>
       </c>
     </row>
     <row r="1909">
@@ -45443,19 +45455,19 @@
         <v>3.770422583987909</v>
       </c>
       <c r="C1909" t="n">
-        <v>2.9618102340173</v>
+        <v>2.978264302689345</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.445420726691277</v>
+        <v>-7.731955122580227</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.01671448097295825</v>
+        <v>-0.1148741706564933</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.291182007890325</v>
+        <v>-1.577716403779276</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.187101029283105</v>
+        <v>2.03163446042178</v>
       </c>
     </row>
     <row r="1910">
@@ -45466,19 +45478,19 @@
         <v>3.760333686710817</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.841931311329133</v>
+        <v>2.858385380001177</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.297480685283678</v>
+        <v>-7.584015081172628</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.0774173870980861</v>
+        <v>-0.1755770767816212</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.270861091981768</v>
+        <v>-1.557395487870718</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.079414656140072</v>
+        <v>1.923948087278747</v>
       </c>
     </row>
     <row r="1911">
@@ -45489,19 +45501,19 @@
         <v>3.72356622940921</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.833217325075655</v>
+        <v>2.849671393747699</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.244511163029689</v>
+        <v>-7.531045558918639</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.06494356444996896</v>
+        <v>-0.163103254133504</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.217891569727779</v>
+        <v>-1.50442596561673</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.102482383238987</v>
+        <v>1.947015814377662</v>
       </c>
     </row>
     <row r="1912">
@@ -45512,19 +45524,19 @@
         <v>3.729969716098114</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.826256712980562</v>
+        <v>2.842710781652606</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.200962756258999</v>
+        <v>-7.487497152147949</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.05448481383678594</v>
+        <v>-0.152644503520321</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.217891569727779</v>
+        <v>-1.50442596561673</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.095521771143894</v>
+        <v>1.940055202282569</v>
       </c>
     </row>
     <row r="1913">
@@ -45535,19 +45547,19 @@
         <v>3.782922533493425</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.840719067361705</v>
+        <v>2.857173136033749</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.958814362805141</v>
+        <v>-7.245348758694091</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.05683689792590041</v>
+        <v>-0.04132279175763465</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.217891569727779</v>
+        <v>-1.50442596561673</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.109984125525037</v>
+        <v>1.954517556663712</v>
       </c>
     </row>
     <row r="1914">
@@ -45558,19 +45570,19 @@
         <v>3.828551486722821</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.8352511878209</v>
+        <v>2.851705256492944</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.850555225682619</v>
+        <v>-7.137089621571569</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.09467267323410411</v>
+        <v>-0.003487016449430946</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.217891569727779</v>
+        <v>-1.50442596561673</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.104516245984232</v>
+        <v>1.949049677122907</v>
       </c>
     </row>
     <row r="1915">
@@ -45581,19 +45593,19 @@
         <v>3.82805292879205</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.832749281831477</v>
+        <v>2.849203350503521</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.727264090865488</v>
+        <v>-7.013798486754438</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1414872211715337</v>
+        <v>0.04332753148799862</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.094600434910649</v>
+        <v>-1.381134830799599</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.175989020885088</v>
+        <v>2.020522452023762</v>
       </c>
     </row>
     <row r="1916">
@@ -45604,19 +45616,19 @@
         <v>3.812453678919912</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.840450260068802</v>
+        <v>2.856904328740846</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.706114891962045</v>
+        <v>-6.992649287850995</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.157647878970236</v>
+        <v>0.05948818928670097</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.073451236007205</v>
+        <v>-1.359985631896156</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.196379518464479</v>
+        <v>2.040912949603153</v>
       </c>
     </row>
     <row r="1917">
@@ -45627,19 +45639,19 @@
         <v>3.748328408318098</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.836230968415852</v>
+        <v>2.852685037087897</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.462349449978601</v>
+        <v>-6.74888384586755</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2509347641106645</v>
+        <v>0.1527750744271295</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.073451236007205</v>
+        <v>-1.359985631896156</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.192160226811529</v>
+        <v>2.036693657950204</v>
       </c>
     </row>
     <row r="1918">
@@ -45650,19 +45662,19 @@
         <v>3.824311233057531</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.838355282335868</v>
+        <v>2.854809351007913</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.360586629701306</v>
+        <v>-6.647121025590256</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2937642061415984</v>
+        <v>0.1956045164580633</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.060232167614777</v>
+        <v>-1.346766563503727</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.202215981767003</v>
+        <v>2.046749412905677</v>
       </c>
     </row>
     <row r="1919">
@@ -45673,19 +45685,19 @@
         <v>3.826354974279191</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.831097357319571</v>
+        <v>2.847551425991615</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.110736235752231</v>
+        <v>-6.397270631641181</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3864464387049305</v>
+        <v>0.2882867490213954</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.060232167614777</v>
+        <v>-1.346766563503727</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.194958056750705</v>
+        <v>2.039491487889379</v>
       </c>
     </row>
     <row r="1920">
@@ -45696,19 +45708,19 @@
         <v>3.835957987011504</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.834696480840219</v>
+        <v>2.851150549512264</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.934844143284798</v>
+        <v>-6.221378539173749</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4604023992125525</v>
+        <v>0.362242709529017</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.060232167614777</v>
+        <v>-1.346766563503727</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.198557180271353</v>
+        <v>2.043090611410028</v>
       </c>
     </row>
     <row r="1921">
@@ -45719,19 +45731,19 @@
         <v>3.780933911392992</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.848023986894773</v>
+        <v>2.864478055566817</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.763397680262335</v>
+        <v>-6.049932076151285</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5423084904760915</v>
+        <v>0.444148800792556</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.8887857045923134</v>
+        <v>-1.175320100481264</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.314752564139385</v>
+        <v>2.15928599527806</v>
       </c>
     </row>
     <row r="1922">
@@ -45742,19 +45754,19 @@
         <v>3.773765222632787</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.84704446451107</v>
+        <v>2.863498533183114</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.689108114523996</v>
+        <v>-5.975642510412946</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5710447943877242</v>
+        <v>0.4728851047041887</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8144961388539742</v>
+        <v>-1.101030534742925</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.358346781198686</v>
+        <v>2.20288021233736</v>
       </c>
     </row>
     <row r="1923">
@@ -45765,19 +45777,19 @@
         <v>3.76461787988308</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.851739265565387</v>
+        <v>2.868193334237432</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.625472372290061</v>
+        <v>-5.912006768179012</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.601193892335615</v>
+        <v>0.5030342026520795</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.7508603966200397</v>
+        <v>-1.03739479250899</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.401223027593364</v>
+        <v>2.245756458732038</v>
       </c>
     </row>
     <row r="1924">
@@ -45788,19 +45800,19 @@
         <v>3.79881477107479</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.832933524349183</v>
+        <v>2.849387593021227</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.514045612964141</v>
+        <v>-5.800580008853092</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6269588548497786</v>
+        <v>0.5287991651662436</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.7508603966200397</v>
+        <v>-1.03739479250899</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.38241728637716</v>
+        <v>2.226950717515834</v>
       </c>
     </row>
     <row r="1925">
@@ -45811,19 +45823,19 @@
         <v>3.797694884242302</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.83467660097406</v>
+        <v>2.851130669646105</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.273615116159281</v>
+        <v>-5.560149512048231</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7248741301966004</v>
+        <v>0.6267144405130649</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5104298998151794</v>
+        <v>-0.7969642957041296</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.528418661084953</v>
+        <v>2.372952092223627</v>
       </c>
     </row>
     <row r="1926">
@@ -45834,19 +45846,19 @@
         <v>3.821593509367692</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.83860591480888</v>
+        <v>2.855059983480925</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.201372547988086</v>
+        <v>-5.487906943877037</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7577004712998985</v>
+        <v>0.659540781616363</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5104298998151794</v>
+        <v>-0.7969642957041296</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.532347974919773</v>
+        <v>2.376881406058447</v>
       </c>
     </row>
     <row r="1927">
@@ -45857,19 +45869,19 @@
         <v>3.822326997879973</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.83928449872622</v>
+        <v>2.855738567398265</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.148374225706698</v>
+        <v>-5.434908621595649</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7795783841297936</v>
+        <v>0.6814186944462581</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.4550936408132406</v>
+        <v>-0.7416280367021908</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.566228314238276</v>
+        <v>2.410761745376951</v>
       </c>
     </row>
     <row r="1928">
@@ -45880,19 +45892,19 @@
         <v>3.848616626502345</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.836282569946214</v>
+        <v>2.852736638618258</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.039569340226971</v>
+        <v>-5.326103736115922</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8200984095416777</v>
+        <v>0.7219387198581426</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.4550936408132406</v>
+        <v>-0.7416280367021908</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.56322638545827</v>
+        <v>2.407759816596944</v>
       </c>
     </row>
     <row r="1929">
@@ -45903,19 +45915,19 @@
         <v>3.818668951675947</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.837861606956828</v>
+        <v>2.854315675628873</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.819548542189961</v>
+        <v>-5.106082938078911</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9096857657670963</v>
+        <v>0.811526076083561</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.3138737957452603</v>
+        <v>-0.6004081916342106</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.649537329509672</v>
+        <v>2.494070760648346</v>
       </c>
     </row>
     <row r="1930">
@@ -45926,19 +45938,19 @@
         <v>3.843274527539958</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.853755789758651</v>
+        <v>2.870209858430696</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.686680853126683</v>
+        <v>-4.973215249015634</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9787270241942305</v>
+        <v>0.8805673345106952</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.3138737957452603</v>
+        <v>-0.6004081916342106</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.665431512311495</v>
+        <v>2.50996494345017</v>
       </c>
     </row>
     <row r="1931">
@@ -45949,19 +45961,19 @@
         <v>3.845047386496265</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.854901634198953</v>
+        <v>2.871355702870998</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.566507769762184</v>
+        <v>-4.853042165651135</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.027942101980332</v>
+        <v>0.9297824122967966</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.1937007123807614</v>
+        <v>-0.4802351082697116</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.738681206770497</v>
+        <v>2.583214637909171</v>
       </c>
     </row>
     <row r="1932">
@@ -45972,19 +45984,19 @@
         <v>3.791273551577001</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.864989736760393</v>
+        <v>2.881443805432438</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.421835624662447</v>
+        <v>-4.708370020551397</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.095899062581667</v>
+        <v>0.9977393728981314</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.04902856728102395</v>
+        <v>-0.3355629631699742</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.835572596391779</v>
+        <v>2.680106027530453</v>
       </c>
     </row>
     <row r="1933">
@@ -45995,19 +46007,19 @@
         <v>3.735839222942107</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.851027228161819</v>
+        <v>2.867481296833863</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.481710452020139</v>
+        <v>-4.76824484790909</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.057986623040016</v>
+        <v>0.9598269333564802</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1089033946387161</v>
+        <v>-0.3954377905276663</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.785685191378589</v>
+        <v>2.630218622517264</v>
       </c>
     </row>
     <row r="1934">
@@ -46018,19 +46030,19 @@
         <v>3.762647477674519</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.873427721484385</v>
+        <v>2.88988179015643</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.394910954241131</v>
+        <v>-4.681445350130081</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.115106915474185</v>
+        <v>1.01694722579065</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1089033946387161</v>
+        <v>-0.3954377905276663</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.808085684701155</v>
+        <v>2.65261911583983</v>
       </c>
     </row>
     <row r="1935">
@@ -46041,19 +46053,19 @@
         <v>3.729146398430698</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.873500122857797</v>
+        <v>2.889954191529842</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.397380660702937</v>
+        <v>-4.683915056591887</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.114191434262875</v>
+        <v>1.016031744579339</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1113731011005222</v>
+        <v>-0.3979074969894725</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.806676262197484</v>
+        <v>2.651209693336158</v>
       </c>
     </row>
     <row r="1936">
@@ -46064,19 +46076,19 @@
         <v>3.743220196003607</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.884507045332499</v>
+        <v>2.900961114004544</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.465750847026947</v>
+        <v>-4.752285242915898</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.097850282207973</v>
+        <v>0.9996905925244373</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1020974020643073</v>
+        <v>-0.3886317979532575</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.823248604093915</v>
+        <v>2.66778203523259</v>
       </c>
     </row>
     <row r="1937">
@@ -46087,19 +46099,19 @@
         <v>3.714179139508375</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.874943753964391</v>
+        <v>2.891397822636435</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.479538899873994</v>
+        <v>-4.766073295762944</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.082771769701045</v>
+        <v>0.98461208001751</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1020974020643073</v>
+        <v>-0.3886317979532575</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.813685312725807</v>
+        <v>2.658218743864481</v>
       </c>
     </row>
     <row r="1938">
@@ -46110,19 +46122,19 @@
         <v>3.71090673141771</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.699653319004777</v>
+        <v>2.716107387676822</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.510532059202699</v>
+        <v>-4.79706645509165</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8950840710099501</v>
+        <v>0.7969243813264146</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1020974020643073</v>
+        <v>-0.3886317979532575</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.638394877766193</v>
+        <v>2.482928308904868</v>
       </c>
     </row>
     <row r="1939">
@@ -46133,19 +46145,19 @@
         <v>3.746042526205906</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.704220550996565</v>
+        <v>2.72067461966861</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.33505779941023</v>
+        <v>-4.621592195299181</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9698410069187253</v>
+        <v>0.8716813172351898</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1020974020643073</v>
+        <v>-0.3886317979532575</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.642962109757981</v>
+        <v>2.487495540896655</v>
       </c>
     </row>
     <row r="1940">
@@ -46156,19 +46168,19 @@
         <v>3.765024323225451</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.679962579757772</v>
+        <v>2.696416648429817</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.445994052051479</v>
+        <v>-4.73252844794043</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9012085346234329</v>
+        <v>0.8030488449398974</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1020974020643073</v>
+        <v>-0.3886317979532575</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.618704138519188</v>
+        <v>2.463237569657863</v>
       </c>
     </row>
     <row r="1941">
@@ -46179,19 +46191,19 @@
         <v>3.7732102971113</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.683093964977678</v>
+        <v>2.699548033649722</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.412330506579197</v>
+        <v>-4.698864902468148</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9178053380322513</v>
+        <v>0.8196456483487158</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.06843385659202544</v>
+        <v>-0.3549682524809757</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.642033651022463</v>
+        <v>2.486567082161137</v>
       </c>
     </row>
     <row r="1942">
@@ -46202,19 +46214,19 @@
         <v>3.78434395226417</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.69326635140981</v>
+        <v>2.709720420081855</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.352477887375474</v>
+        <v>-4.639012283264424</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9519187721458728</v>
+        <v>0.8537590824623376</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.06843385659202544</v>
+        <v>-0.3549682524809757</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.652206037454595</v>
+        <v>2.496739468593269</v>
       </c>
     </row>
     <row r="1943">
@@ -46225,19 +46237,19 @@
         <v>3.786949957742306</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.68821262198367</v>
+        <v>2.704666690655715</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.266234424349096</v>
+        <v>-4.552768820238047</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9813624279302844</v>
+        <v>0.8832027382467489</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.06843385659202544</v>
+        <v>-0.3549682524809757</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.647152308028455</v>
+        <v>2.49168573916713</v>
       </c>
     </row>
     <row r="1944">
@@ -46248,19 +46260,19 @@
         <v>3.752027499316052</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.679988397428196</v>
+        <v>2.69644246610024</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.311541243748076</v>
+        <v>-4.598075639637027</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9550154756152178</v>
+        <v>0.8568557859316825</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1092440196012562</v>
+        <v>-0.3957784154902065</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.614441985667443</v>
+        <v>2.458975416806117</v>
       </c>
     </row>
     <row r="1945">
@@ -46271,19 +46283,19 @@
         <v>3.753571165803196</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.680540270461298</v>
+        <v>2.696994339133342</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.340574348450377</v>
+        <v>-4.627108744339328</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9439541067673991</v>
+        <v>0.8457944170838636</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1092440196012562</v>
+        <v>-0.3957784154902065</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.614993858700544</v>
+        <v>2.459527289839218</v>
       </c>
     </row>
     <row r="1946">
@@ -46294,19 +46306,19 @@
         <v>3.733390600809503</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.609812962352663</v>
+        <v>2.626267031024708</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.247763866999517</v>
+        <v>-4.534298262888468</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9103509912391086</v>
+        <v>0.8121913015555731</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.01643353815039689</v>
+        <v>-0.3029679340393471</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.599952839462425</v>
+        <v>2.4444862706011</v>
       </c>
     </row>
     <row r="1947">
@@ -46317,19 +46329,19 @@
         <v>3.74828581656043</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.611686438277264</v>
+        <v>2.628140506949308</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.292153336328945</v>
+        <v>-4.578687732217896</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8944686794319383</v>
+        <v>0.796308989748403</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.06082300747982455</v>
+        <v>-0.3473574033687748</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.575192633789369</v>
+        <v>2.419726064928044</v>
       </c>
     </row>
     <row r="1948">
@@ -46340,19 +46352,19 @@
         <v>3.721077195472743</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.606762146788987</v>
+        <v>2.623216215461031</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.179482118092695</v>
+        <v>-4.466016513981645</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9346128752381615</v>
+        <v>0.836453185554626</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.05184821075642565</v>
+        <v>-0.2346861851325246</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.637871073242843</v>
+        <v>2.482404504381517</v>
       </c>
     </row>
     <row r="1949">
@@ -46363,19 +46375,19 @@
         <v>3.743047603798543</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.612253442619654</v>
+        <v>2.628707511291699</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.067105116910022</v>
+        <v>-4.353639512798972</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9850549715418979</v>
+        <v>0.8868952818583624</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.05184821075642565</v>
+        <v>-0.2346861851325246</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.64336236907351</v>
+        <v>2.487895800212184</v>
       </c>
     </row>
     <row r="1950">
@@ -46386,19 +46398,19 @@
         <v>3.689597840498871</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.623750644388193</v>
+        <v>2.640204713060238</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.094885514811375</v>
+        <v>-4.381419910700325</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9854400141498958</v>
+        <v>0.8872803244663605</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.02406781285507259</v>
+        <v>-0.2624665830338777</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.638191332101237</v>
+        <v>2.482724763239911</v>
       </c>
     </row>
     <row r="1951">
@@ -46409,19 +46421,19 @@
         <v>3.643069621705331</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.462106364388847</v>
+        <v>2.478560433060891</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.177886795836653</v>
+        <v>-4.464421191725604</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7905952217404375</v>
+        <v>0.6924355320569022</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.005496928327898831</v>
+        <v>-0.2810374675610514</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.465404521385586</v>
+        <v>2.30993795252426</v>
       </c>
     </row>
     <row r="1952">
@@ -46432,19 +46444,19 @@
         <v>3.682716310729276</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.582256025108052</v>
+        <v>2.598710093780097</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.286500874279985</v>
+        <v>-4.573035270168935</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8672992510823108</v>
+        <v>0.7691395613987753</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.005496928327898831</v>
+        <v>-0.2810374675610514</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.585554182104792</v>
+        <v>2.430087613243466</v>
       </c>
     </row>
     <row r="1953">
@@ -46455,19 +46467,19 @@
         <v>3.733012441190775</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.596769051210375</v>
+        <v>2.61322311988242</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.251091836031842</v>
+        <v>-4.537626231920792</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8959758924838908</v>
+        <v>0.7978162028003555</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.005496928327898831</v>
+        <v>-0.2810374675610514</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.600067208207115</v>
+        <v>2.444600639345789</v>
       </c>
     </row>
     <row r="1954">
@@ -46478,19 +46490,19 @@
         <v>3.741174069913432</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.594188492552744</v>
+        <v>2.610642561224788</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.212708173473691</v>
+        <v>-4.499242569362641</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.90874879884952</v>
+        <v>0.8105891091659845</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.04388059088605001</v>
+        <v>-0.2426538050029002</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.620516847084374</v>
+        <v>2.465050278223048</v>
       </c>
     </row>
     <row r="1955">
@@ -46501,19 +46513,19 @@
         <v>3.751147197532493</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.590917521398046</v>
+        <v>2.60737159007009</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.035591843438525</v>
+        <v>-4.322126239327475</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9763243597088884</v>
+        <v>0.8781646700253529</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.04388059088605001</v>
+        <v>-0.2426538050029002</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.617245875929676</v>
+        <v>2.46177930706835</v>
       </c>
     </row>
     <row r="1956">
@@ -46524,19 +46536,19 @@
         <v>3.741328448793911</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.591600913159959</v>
+        <v>2.608054981832003</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.08068408827207</v>
+        <v>-4.367218484161021</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9589708535373831</v>
+        <v>0.8608111638538478</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.01801545228333978</v>
+        <v>-0.30454984817229</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.580791641789955</v>
+        <v>2.42532507292863</v>
       </c>
     </row>
     <row r="1957">
@@ -46547,19 +46559,19 @@
         <v>3.750729377011243</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.585387888466373</v>
+        <v>2.601841957138418</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.901308667033303</v>
+        <v>-4.187843062922253</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.024507997339305</v>
+        <v>0.9263483076557693</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.1387613058873789</v>
+        <v>-0.1477730900015713</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.668644671998801</v>
+        <v>2.513178103137475</v>
       </c>
     </row>
     <row r="1958">
@@ -46570,19 +46582,19 @@
         <v>3.716991718982237</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.566195343797963</v>
+        <v>2.582649412470007</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.946322880553909</v>
+        <v>-4.232857276442859</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9873097672626518</v>
+        <v>0.8891500775791166</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.1084124105727743</v>
+        <v>-0.178121985316176</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.631242790141628</v>
+        <v>2.475776221280302</v>
       </c>
     </row>
     <row r="1959">
@@ -46593,19 +46605,19 @@
         <v>3.737026608509546</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.571886906136909</v>
+        <v>2.588340974808953</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.213327390826344</v>
+        <v>-4.499861786715294</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8861995254926234</v>
+        <v>0.7880398358090883</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.08595062747017429</v>
+        <v>-0.3724850233591245</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.520316529654804</v>
+        <v>2.364849960793479</v>
       </c>
     </row>
     <row r="1960">
@@ -46616,19 +46628,19 @@
         <v>3.702309454760817</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.57109082803341</v>
+        <v>2.587544896705455</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.314525172263517</v>
+        <v>-4.601059568152467</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8449243348142557</v>
+        <v>0.7467646451307206</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.1543594410154935</v>
+        <v>-0.4408938369044437</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.478475163424114</v>
+        <v>2.323008594562789</v>
       </c>
     </row>
     <row r="1961">
@@ -46639,19 +46651,19 @@
         <v>3.705571661815461</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.568690789587727</v>
+        <v>2.585144858259771</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.308014205649204</v>
+        <v>-4.594548601538154</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8451286830142974</v>
+        <v>0.7469689933307624</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.1543594410154935</v>
+        <v>-0.4408938369044437</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.476075124978431</v>
+        <v>2.320608556117105</v>
       </c>
     </row>
     <row r="1962">
@@ -46662,19 +46674,19 @@
         <v>3.709510443378106</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.565215508795972</v>
+        <v>2.581669577468016</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.288976077941907</v>
+        <v>-4.575510473830857</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8492686533054614</v>
+        <v>0.7511089636219264</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.212543052346688</v>
+        <v>-0.4990774482356383</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.437689677387959</v>
+        <v>2.282223108526634</v>
       </c>
     </row>
     <row r="1963">
@@ -46685,19 +46697,19 @@
         <v>3.731064473131257</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.742797377734652</v>
+        <v>2.759251446406697</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.320102709092525</v>
+        <v>-4.606637104981475</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.014399869783895</v>
+        <v>0.9162401801003595</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.212543052346688</v>
+        <v>-0.4990774482356383</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.61527154632664</v>
+        <v>2.459804977465314</v>
       </c>
     </row>
     <row r="1964">
@@ -46708,19 +46720,19 @@
         <v>3.722447362067873</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.743630706720786</v>
+        <v>2.76008477539283</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.333969470426443</v>
+        <v>-4.620503866315393</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.009686494236461</v>
+        <v>0.9115268045529259</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.250400969080511</v>
+        <v>-0.5369353649694613</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.59339012527248</v>
+        <v>2.437923556411154</v>
       </c>
     </row>
     <row r="1965">
@@ -46731,19 +46743,19 @@
         <v>3.787425580789129</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.749639237117712</v>
+        <v>2.766093305789756</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.289165298886513</v>
+        <v>-4.575699694775463</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.033616693249359</v>
+        <v>0.9354570035658238</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.250400969080511</v>
+        <v>-0.5369353649694613</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.599398655669406</v>
+        <v>2.44393208680808</v>
       </c>
     </row>
     <row r="1966">
@@ -46754,19 +46766,19 @@
         <v>3.781501250519916</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.828791884909734</v>
+        <v>2.845245953581778</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.141422328651511</v>
+        <v>-4.427956724540461</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.171866529135382</v>
+        <v>1.073706839451847</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.0825936118456278</v>
+        <v>-0.3691280077345781</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.779235717802357</v>
+        <v>2.623769148941032</v>
       </c>
     </row>
     <row r="1967">
@@ -46777,19 +46789,19 @@
         <v>3.802245929181178</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.831585506441215</v>
+        <v>2.848039575113259</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.243437011182732</v>
+        <v>-4.529971407071682</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.133854277654374</v>
+        <v>1.035694587970839</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.0825936118456278</v>
+        <v>-0.3691280077345781</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.782029339333838</v>
+        <v>2.626562770472513</v>
       </c>
     </row>
     <row r="1968">
@@ -46800,19 +46812,19 @@
         <v>3.805608985394739</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.832247854832873</v>
+        <v>2.848701923504918</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.237284305129948</v>
+        <v>-4.523818701018897</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.136977708467146</v>
+        <v>1.038818018783611</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.07644090579284352</v>
+        <v>-0.3629753016817938</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.786383311357167</v>
+        <v>2.630916742495842</v>
       </c>
     </row>
     <row r="1969">
@@ -46823,19 +46835,19 @@
         <v>3.798239794890615</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.831328331572983</v>
+        <v>2.847782400245028</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.25409360328045</v>
+        <v>-4.540627999169399</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.129334465947056</v>
+        <v>1.031174776263521</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.09325020394334516</v>
+        <v>-0.3797845998322955</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.775378209206977</v>
+        <v>2.619911640345651</v>
       </c>
     </row>
     <row r="1970">
@@ -46846,19 +46858,19 @@
         <v>3.867362636798433</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.897663885369804</v>
+        <v>2.914117954041849</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.191795604504327</v>
+        <v>-4.478330000393277</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.220589219254326</v>
+        <v>1.122429529570791</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.09325020394334516</v>
+        <v>-0.3797845998322955</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.841713763003797</v>
+        <v>2.686247194142472</v>
       </c>
     </row>
     <row r="1971">
@@ -46869,19 +46881,19 @@
         <v>3.8487291399922</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.606244757759202</v>
+        <v>2.622698826431247</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.990005406839169</v>
+        <v>-4.276539802728119</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.009886170709787</v>
+        <v>0.9117264810262518</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.1047679882258092</v>
+        <v>-0.1817664076631411</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.669105550694688</v>
+        <v>2.513638981833362</v>
       </c>
     </row>
     <row r="1972">
@@ -46892,19 +46904,19 @@
         <v>3.841444817852429</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.676534990081378</v>
+        <v>2.692989058753422</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.916627309750433</v>
+        <v>-4.203161705639383</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.109527641867457</v>
+        <v>1.011367952183921</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.1781460853145458</v>
+        <v>-0.1083883105744045</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.783422641270105</v>
+        <v>2.62795607240878</v>
       </c>
     </row>
     <row r="1973">
@@ -46915,19 +46927,19 @@
         <v>3.819063300319554</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.691162726197421</v>
+        <v>2.707616794869466</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.014367854375407</v>
+        <v>-4.300902250264357</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.085059160133511</v>
+        <v>0.9868994704499754</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.1622568071815656</v>
+        <v>-0.1242775887073847</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.788516810506361</v>
+        <v>2.633050241645035</v>
       </c>
     </row>
     <row r="1974">
@@ -46938,19 +46950,19 @@
         <v>3.831819032489393</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.689698707022093</v>
+        <v>2.706152775694137</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.190705614498336</v>
+        <v>-4.477240010387287</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.013060036909011</v>
+        <v>0.9149003472254753</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.0140809529413638</v>
+        <v>-0.3006153488303141</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.681250135257275</v>
+        <v>2.525783566395949</v>
       </c>
     </row>
     <row r="1975">
@@ -46961,19 +46973,19 @@
         <v>3.836411672397802</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.688190325062021</v>
+        <v>2.704644393734066</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.114283568066409</v>
+        <v>-4.40081796395536</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.04212047352171</v>
+        <v>0.9439607838381745</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.0140809529413638</v>
+        <v>-0.3006153488303141</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.679741753297203</v>
+        <v>2.524275184435878</v>
       </c>
     </row>
     <row r="1976">
@@ -46984,19 +46996,19 @@
         <v>3.833513460316257</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.688053192497458</v>
+        <v>2.704507261169502</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.069910436427841</v>
+        <v>-4.356444832316791</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.059732593612574</v>
+        <v>0.9615729039290382</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.0302921786972048</v>
+        <v>-0.2562422171917455</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.706228499715781</v>
+        <v>2.550761930854455</v>
       </c>
     </row>
     <row r="1977">
@@ -47007,19 +47019,19 @@
         <v>3.821562117105971</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.682446986636048</v>
+        <v>2.698901055308093</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.947076215540673</v>
+        <v>-4.233610611429624</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.103260076106031</v>
+        <v>1.005100386422496</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.0302921786972048</v>
+        <v>-0.2562422171917455</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.700622293854371</v>
+        <v>2.545155724993045</v>
       </c>
     </row>
     <row r="1978">
@@ -47030,19 +47042,19 @@
         <v>3.833011148190328</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.688828743663852</v>
+        <v>2.705282812335897</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.899420484979617</v>
+        <v>-4.185954880868568</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.128704125358258</v>
+        <v>1.030544435674722</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.07794790925826045</v>
+        <v>-0.2085864866306898</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.735597489218809</v>
+        <v>2.580130920357483</v>
       </c>
     </row>
     <row r="1979">
@@ -47053,19 +47065,19 @@
         <v>3.822678210569621</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.693721117038577</v>
+        <v>2.710175185710622</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.798902326480863</v>
+        <v>-4.085436722369813</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.173803762132484</v>
+        <v>1.075644072448949</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.178466067757015</v>
+        <v>-0.1080683281319353</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.800800757692786</v>
+        <v>2.645334188831461</v>
       </c>
     </row>
     <row r="1980">
@@ -47076,19 +47088,19 @@
         <v>3.828808877557297</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.680475789514449</v>
+        <v>2.696929858186494</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.859568916883252</v>
+        <v>-4.146103312772203</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.136291798447401</v>
+        <v>1.038132108763865</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.09676775103848134</v>
+        <v>-0.189766644850469</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.738536440137538</v>
+        <v>2.583069871276213</v>
       </c>
     </row>
     <row r="1981">
@@ -47099,19 +47111,19 @@
         <v>3.816837033932772</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.684573492125078</v>
+        <v>2.701027560797122</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.814730515274854</v>
+        <v>-4.101264911163804</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.158324861701389</v>
+        <v>1.060165172017853</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.1013111839833508</v>
+        <v>-0.1852232119055995</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.745360202515088</v>
+        <v>2.589893633653763</v>
       </c>
     </row>
     <row r="1982">
@@ -47122,19 +47134,19 @@
         <v>3.817932354917057</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.688734431756156</v>
+        <v>2.7051885004282</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.915489151031852</v>
+        <v>-4.202023546920802</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.122182347029667</v>
+        <v>1.024022657346132</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.01248561525634539</v>
+        <v>-0.2740487806326049</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.696225800909963</v>
+        <v>2.540759232048638</v>
       </c>
     </row>
     <row r="1983">
@@ -47145,19 +47157,19 @@
         <v>3.826684745405966</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.694614034283993</v>
+        <v>2.711068102956038</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.871286313945952</v>
+        <v>-4.157820709834902</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.145743084391865</v>
+        <v>1.04758339470833</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.05668845234224584</v>
+        <v>-0.2298459435467045</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.728627105689341</v>
+        <v>2.573160536828015</v>
       </c>
     </row>
     <row r="1984">
@@ -47168,19 +47180,19 @@
         <v>3.838199629265651</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.693024034753241</v>
+        <v>2.709478103425285</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.908265341609395</v>
+        <v>-4.194799737498345</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.129361473795735</v>
+        <v>1.0312017841122</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.09366235413357638</v>
+        <v>-0.1928720417553739</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.749221447233387</v>
+        <v>2.593754878372061</v>
       </c>
     </row>
     <row r="1985">
@@ -47191,19 +47203,19 @@
         <v>3.863895080284885</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.74427179993628</v>
+        <v>2.760725868608325</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.928323420474235</v>
+        <v>-4.214857816363185</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.172586007432838</v>
+        <v>1.074426317749303</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.09366235413357638</v>
+        <v>-0.1928720417553739</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.800469212416426</v>
+        <v>2.645002643555101</v>
       </c>
     </row>
     <row r="1986">
@@ -47214,19 +47226,19 @@
         <v>3.865338681321028</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.742712504530533</v>
+        <v>2.759166573202578</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.888392747296345</v>
+        <v>-4.174927143185295</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.186998981298248</v>
+        <v>1.088839291614712</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.1335930273114667</v>
+        <v>-0.1529413685774836</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.822868320917414</v>
+        <v>2.667401752056088</v>
       </c>
     </row>
     <row r="1987">
@@ -47237,19 +47249,19 @@
         <v>3.864489842475145</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.737660732768803</v>
+        <v>2.754114801440848</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.837360654573817</v>
+        <v>-4.123895050462767</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.202360046625529</v>
+        <v>1.104200356941994</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.1846251200339947</v>
+        <v>-0.1019092758549556</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.8484358047892</v>
+        <v>2.692969235927875</v>
       </c>
     </row>
     <row r="1988">
@@ -47260,19 +47272,19 @@
         <v>3.84254736040486</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.754848136861508</v>
+        <v>2.771302205533553</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.772136473446611</v>
+        <v>-4.058670869335562</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.245637123169116</v>
+        <v>1.147477433485581</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.2498493011612003</v>
+        <v>-0.03668509472775</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.904757717558229</v>
+        <v>2.749291148696903</v>
       </c>
     </row>
     <row r="1989">
@@ -47283,19 +47295,19 @@
         <v>3.840061186882564</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.750809109160789</v>
+        <v>2.767263177832833</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.734709453375478</v>
+        <v>-4.021243849264428</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.25656890349685</v>
+        <v>1.158409213813315</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.255100839190382</v>
+        <v>-0.03143355669856834</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.903869612675018</v>
+        <v>2.748403043813692</v>
       </c>
     </row>
     <row r="1990">
@@ -47306,19 +47318,19 @@
         <v>3.845169808992669</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.752065901492029</v>
+        <v>2.768519970164073</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.754821109410186</v>
+        <v>-4.041355505299136</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.249781033414207</v>
+        <v>1.151621343730672</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.2661281841878012</v>
+        <v>-0.02040621170114915</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.91174281200471</v>
+        <v>2.756276243143384</v>
       </c>
     </row>
     <row r="1991">
@@ -47329,19 +47341,19 @@
         <v>3.828661445636294</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.91262367251324</v>
+        <v>2.929077741185284</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.701076294982981</v>
+        <v>-3.987610690871931</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.4318367302063</v>
+        <v>1.333677040522764</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.2761914936282631</v>
+        <v>-0.01034290226068718</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.078338568690198</v>
+        <v>2.922871999828872</v>
       </c>
     </row>
     <row r="1992">
@@ -47352,19 +47364,19 @@
         <v>3.813222820957632</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.032736581731057</v>
+        <v>3.049190650403101</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.677284726376839</v>
+        <v>-3.963819122265789</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.561466266866574</v>
+        <v>1.463306577183038</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.2999830622344054</v>
+        <v>0.01344866634545511</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.2127264190717</v>
+        <v>3.057259850210375</v>
       </c>
     </row>
     <row r="1993">
@@ -47375,19 +47387,19 @@
         <v>3.814230727998758</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.024444557744916</v>
+        <v>3.04089862641696</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.651200642113031</v>
+        <v>-3.937735038001981</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.563607876585956</v>
+        <v>1.465448186902421</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.2999830622344054</v>
+        <v>0.01344866634545511</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.204434395085559</v>
+        <v>3.048967826224234</v>
       </c>
     </row>
     <row r="1994">
@@ -47398,19 +47410,19 @@
         <v>3.803397818896932</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.022637753328695</v>
+        <v>3.03909182200074</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.573069461264084</v>
+        <v>-3.859603857153035</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.593053544509314</v>
+        <v>1.494893854825779</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.37415987311809</v>
+        <v>0.08762547722913966</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.24713367719955</v>
+        <v>3.091667108338224</v>
       </c>
     </row>
     <row r="1995">
@@ -47421,19 +47433,19 @@
         <v>3.796264143959863</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.040192159055487</v>
+        <v>3.056646227727531</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.564176999870801</v>
+        <v>-3.850711395759752</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.614164934793419</v>
+        <v>1.516005245109883</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.37415987311809</v>
+        <v>0.08762547722913966</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.264688082926341</v>
+        <v>3.109221514065015</v>
       </c>
     </row>
     <row r="1996">
@@ -47444,19 +47456,19 @@
         <v>3.794424941945373</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.032047206460071</v>
+        <v>3.048501275132115</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.732653116840679</v>
+        <v>-4.019187512729629</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.538629535410052</v>
+        <v>1.440469845726516</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.3462120374015092</v>
+        <v>0.05967764151255889</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.239774428900977</v>
+        <v>3.084307860039651</v>
       </c>
     </row>
     <row r="1997">
@@ -47467,19 +47479,19 @@
         <v>3.795574066782715</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.013316903647933</v>
+        <v>3.029770972319977</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.034853587979096</v>
+        <v>-3.321387983868046</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.799019044142547</v>
+        <v>1.700859354459011</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.2758639780310985</v>
+        <v>-0.01067041785785183</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.178835290466592</v>
+        <v>3.023368721605266</v>
       </c>
     </row>
     <row r="1998">
@@ -47490,19 +47502,19 @@
         <v>3.784671345632645</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.003980926144837</v>
+        <v>3.020434994816882</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.012132484295943</v>
+        <v>-3.298666880184893</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.798771508112712</v>
+        <v>1.700611818429177</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.2758639780310985</v>
+        <v>-0.01067041785785183</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.169499312963497</v>
+        <v>3.014032744102171</v>
       </c>
     </row>
     <row r="1999">
@@ -47513,19 +47525,19 @@
         <v>3.783205696777682</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.162887051996006</v>
+        <v>3.179341120668051</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.010407441005899</v>
+        <v>-3.29694183689485</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.958367651279899</v>
+        <v>1.860207961596363</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.2775890213211422</v>
+        <v>-0.008945374567808084</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.329440464788692</v>
+        <v>3.173973895927366</v>
       </c>
     </row>
     <row r="2000">
@@ -47536,19 +47548,19 @@
         <v>3.779933725644421</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.199964874489653</v>
+        <v>3.216418943161697</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.165188447784154</v>
+        <v>-3.451722843673105</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.933533071062243</v>
+        <v>1.835373381378708</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.2442213472666661</v>
+        <v>-0.04231304862228419</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.346497682849653</v>
+        <v>3.191031113988327</v>
       </c>
     </row>
     <row r="2001">
@@ -47559,19 +47571,19 @@
         <v>3.769443619799968</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.196640230479198</v>
+        <v>3.213094299151242</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.113753114399495</v>
+        <v>-3.400287510288445</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.950782560405652</v>
+        <v>1.852622870722117</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.2956566806513258</v>
+        <v>0.009122284762375477</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.374034238869994</v>
+        <v>3.218567670008668</v>
       </c>
     </row>
     <row r="2002">
@@ -47582,19 +47594,19 @@
         <v>3.766673496331124</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.206646384123939</v>
+        <v>3.223100452795984</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.086801890073007</v>
+        <v>-3.373336285961957</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.971569203780989</v>
+        <v>1.873409514097454</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.3105370266790449</v>
+        <v>0.02400263079009463</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.392968600131367</v>
+        <v>3.237502031270041</v>
       </c>
     </row>
     <row r="2003">
@@ -47605,19 +47617,19 @@
         <v>3.768052067784117</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.390749516268899</v>
+        <v>3.407203584940944</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.222754898129323</v>
+        <v>-3.509289294018274</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.101291132703422</v>
+        <v>2.003131443019887</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.3105370266790449</v>
+        <v>0.02400263079009463</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.577071732276326</v>
+        <v>3.421605163415001</v>
       </c>
     </row>
     <row r="2004">
@@ -47628,19 +47640,19 @@
         <v>3.74392550571443</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.382866211171892</v>
+        <v>3.399320279843937</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.245163015934195</v>
+        <v>-3.531697411823146</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.084444580484467</v>
+        <v>1.986284890800931</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.3105370266790449</v>
+        <v>0.02400263079009463</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.56918842717932</v>
+        <v>3.413721858317994</v>
       </c>
     </row>
     <row r="2005">
@@ -47651,19 +47663,19 @@
         <v>3.719118627155041</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.38492021072153</v>
+        <v>3.401374279393574</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.393168783413595</v>
+        <v>-3.679703179302545</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.027296273042344</v>
+        <v>1.929136583358809</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.2238100178155035</v>
+        <v>-0.06272437807344683</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.519206221410832</v>
+        <v>3.363739652549506</v>
       </c>
     </row>
     <row r="2006">
@@ -47674,19 +47686,19 @@
         <v>3.729452285161986</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.441173928443377</v>
+        <v>3.457627997115421</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.402609709302125</v>
+        <v>-3.689144105191075</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.079773620408779</v>
+        <v>1.981613930725244</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.3462371353588949</v>
+        <v>0.05970273946994459</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.648916209658714</v>
+        <v>3.493449640797389</v>
       </c>
     </row>
     <row r="2007">
@@ -47697,19 +47709,19 @@
         <v>3.714941193321643</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.444065022988678</v>
+        <v>3.460519091660722</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.401322945762568</v>
+        <v>-3.687857341651519</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.083179420369903</v>
+        <v>1.985019730686368</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.3475238988984515</v>
+        <v>0.06098950300950118</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.652579362327749</v>
+        <v>3.497112793466423</v>
       </c>
     </row>
     <row r="2008">
@@ -47720,19 +47732,19 @@
         <v>3.727898186347711</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.442176835882453</v>
+        <v>3.458630904554497</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.40287999975186</v>
+        <v>-3.68941439564081</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.080668411667961</v>
+        <v>1.982508721984426</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.3475238988984515</v>
+        <v>0.06098950300950118</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.650691175221524</v>
+        <v>3.495224606360198</v>
       </c>
     </row>
     <row r="2009">
@@ -47743,19 +47755,19 @@
         <v>3.710654104887755</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.436997065485315</v>
+        <v>3.45345113415736</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.410151885275324</v>
+        <v>-3.696686281164275</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.072579887061438</v>
+        <v>1.974420197377903</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.3402520133749867</v>
+        <v>0.05371761748603643</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.641148273510308</v>
+        <v>3.485681704648982</v>
       </c>
     </row>
     <row r="2010">
@@ -47766,19 +47778,19 @@
         <v>3.712897612343073</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.435431075695468</v>
+        <v>3.451885144367512</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.408310866217073</v>
+        <v>-3.694845262106023</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.071750304894891</v>
+        <v>1.973590615211355</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.3415202400464551</v>
+        <v>0.05498584415750485</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.640343219723341</v>
+        <v>3.484876650862015</v>
       </c>
     </row>
     <row r="2011">
@@ -47789,19 +47801,19 @@
         <v>3.754911907647114</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.448504482561386</v>
+        <v>3.464958551233431</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.415219571716753</v>
+        <v>-3.701753967605704</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.082060229560937</v>
+        <v>1.983900539877402</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.3415202400464551</v>
+        <v>0.05498584415750485</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.65341662658926</v>
+        <v>3.497950057727934</v>
       </c>
     </row>
     <row r="2012">
@@ -47812,19 +47824,19 @@
         <v>3.749896851763537</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.448504482561386</v>
+        <v>3.464958551233431</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.416781214531613</v>
+        <v>-3.703315610420564</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.081435572434994</v>
+        <v>1.983275882751458</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.3415202400464551</v>
+        <v>0.05498584415750485</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.65341662658926</v>
+        <v>3.497950057727934</v>
       </c>
     </row>
     <row r="2013">
@@ -47832,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392119</v>
+        <v>3.71583405539212</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.447028523688388</v>
+        <v>3.463482592360433</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.444682001641086</v>
+        <v>-3.896813942095191</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.068799298718206</v>
+        <v>1.904400591208609</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.3069233159035203</v>
+        <v>-0.01689285728290507</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.631182513230501</v>
+        <v>3.45334687799069</v>
       </c>
     </row>
     <row r="2014">
@@ -47855,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.815648773041493</v>
+        <v>3.439666940549856</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.613405510609233</v>
+        <v>3.369159911614337</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.444682001641086</v>
+        <v>-3.896813942095191</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.068799298718206</v>
+        <v>1.904400591208609</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.3069233159035203</v>
+        <v>-0.01689285728290507</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.606469307595601</v>
+        <v>3.362223708600705</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240703.xlsx
+++ b/tame_output/ON/bt/strategyON_20240703.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>55.7%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>82.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,27 +819,27 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-31.8%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,22 +859,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>59.7%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.5%</t>
+          <t>-72.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>108.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.6%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>94.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.3%</t>
+          <t>-49.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.8%</t>
+          <t>-68.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>447.2%</t>
+          <t>452.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-551.3%</t>
+          <t>-518.4%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>-37.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-39.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-42.8%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-185.8%</t>
+          <t>-161.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.8%</t>
+          <t>-21.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.7%</t>
+          <t>-31.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-14.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-160.0%</t>
+          <t>-173.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-225.7%</t>
+          <t>-214.7%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-28.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-109.8%</t>
+          <t>-75.4%</t>
         </is>
       </c>
     </row>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355689</v>
+        <v>3.311888301355688</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279813</v>
+        <v>3.385382209279812</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511404</v>
+        <v>3.367379938511403</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082123</v>
+        <v>3.299560092082122</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757921</v>
+        <v>3.29349053375792</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760739</v>
+        <v>3.293766719760738</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296836</v>
+        <v>3.299918119296835</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201487</v>
+        <v>3.295507330201486</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153006</v>
+        <v>3.258791981153005</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207813</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191737</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.30502326510864</v>
+        <v>3.305023265108639</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097821</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094117</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199287</v>
+        <v>3.405960511199286</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969594</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297749</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539466</v>
+        <v>3.501052558539465</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937501</v>
+        <v>3.4924487119375</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141704</v>
+        <v>3.502790399141703</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440635</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.891203652589249</v>
+        <v>-9.833587161839539</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7966635371163431</v>
+        <v>-0.7736169408164586</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.394704044950902</v>
+        <v>-2.337087554201192</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.723351921262563</v>
+        <v>1.757921815712389</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608602</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.06632806997579</v>
+        <v>-10.00871157922608</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8521580833234434</v>
+        <v>-0.8291114870235594</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.569828462337446</v>
+        <v>-2.512211971587735</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.632832491578154</v>
+        <v>1.66740238602798</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.30078016399028</v>
+        <v>-10.24316367324057</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9531580858308355</v>
+        <v>-0.9301114895309515</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.569828462337446</v>
+        <v>-2.512211971587735</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.625613326676558</v>
+        <v>1.660183221126384</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.40515489501673</v>
+        <v>-10.34753840426702</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.00158016901539</v>
+        <v>-0.9785335727155062</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.674203193363892</v>
+        <v>-2.616586702614181</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.556316297286714</v>
+        <v>1.59088619173654</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.45794105061706</v>
+        <v>-10.40032455986734</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.021578841416964</v>
+        <v>-0.9985322451170804</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.769878679946289</v>
+        <v>-2.712262189196578</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.500026795175832</v>
+        <v>1.534596689625658</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297401</v>
+        <v>3.4921016412974</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.58397784398534</v>
+        <v>-10.52636135323563</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.069299830135165</v>
+        <v>-1.046253233835281</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.744627057136547</v>
+        <v>-2.687010566386836</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.517871497490792</v>
+        <v>1.552441391940618</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322546</v>
+        <v>3.573674025322545</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.53196233001653</v>
+        <v>-10.47434583926682</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.04450328886124</v>
+        <v>-1.021456692561356</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.744627057136547</v>
+        <v>-2.687010566386836</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.521861833177193</v>
+        <v>1.556431727627019</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158924</v>
+        <v>3.600038265158923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.67363417174065</v>
+        <v>-10.61601768099094</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.102647252449629</v>
+        <v>-1.079600656149745</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.744627057136547</v>
+        <v>-2.687010566386836</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.520386606278451</v>
+        <v>1.554956500728278</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940722</v>
+        <v>3.691571733940721</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.62404332731582</v>
+        <v>-10.56642683656611</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.067757504514824</v>
+        <v>-1.044710908214939</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.695036212711713</v>
+        <v>-2.637419721962002</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.565194523098224</v>
+        <v>1.59976441754805</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770583</v>
+        <v>3.676841549770582</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.61123593431104</v>
+        <v>-10.55361944356133</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.075685680959597</v>
+        <v>-1.052639084659713</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.743891987720614</v>
+        <v>-2.686275496970903</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.5228299244462</v>
+        <v>1.557399818896027</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615287</v>
+        <v>3.685161381615286</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.38539078159163</v>
+        <v>-10.32777429084192</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.975768546835623</v>
+        <v>-0.9527219505357398</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.70196531213345</v>
+        <v>-2.64434882138374</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.557565002834707</v>
+        <v>1.592134897284533</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.26081212525404</v>
+        <v>-10.20319563450433</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9247979397445278</v>
+        <v>-0.9017513434446438</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.70196531213345</v>
+        <v>-2.64434882138374</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.558704147390766</v>
+        <v>1.593274041840592</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646221</v>
+        <v>3.71093553364622</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.31370741329833</v>
+        <v>-10.25609092254862</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9433222808001345</v>
+        <v>-0.9202756845002513</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.697009966045004</v>
+        <v>-2.639393475295293</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.564311129205941</v>
+        <v>1.598881023655768</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611572</v>
+        <v>3.768951674611571</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.24157423801045</v>
+        <v>-10.18395774726074</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9087353064463457</v>
+        <v>-0.8856887101464617</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.697009966045004</v>
+        <v>-2.639393475295293</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.570044833444578</v>
+        <v>1.604614727894404</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955332</v>
+        <v>3.728577929955331</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.1702078454008</v>
+        <v>-10.11259135465109</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8899260117963514</v>
+        <v>-0.8668794154964683</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.625643573435356</v>
+        <v>-2.568027082685645</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.603127406616502</v>
+        <v>1.637697301066328</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.07674881141557</v>
+        <v>-10.01913232066586</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8624258795151696</v>
+        <v>-0.8393792832152864</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.625643573435356</v>
+        <v>-2.568027082685645</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.593243925303594</v>
+        <v>1.62781381975342</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436234</v>
+        <v>3.766317079436233</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.809507010547176</v>
+        <v>-9.751890519797467</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7573637196671843</v>
+        <v>-0.7343171233673007</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.625643573435356</v>
+        <v>-2.568027082685645</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.59140936480422</v>
+        <v>1.625979259254047</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311954</v>
+        <v>3.784684521311953</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.711599971870685</v>
+        <v>-9.653983481120976</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7185012191700486</v>
+        <v>-0.6954546228701655</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.557657823574799</v>
+        <v>-2.500041332825089</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.631900499747093</v>
+        <v>1.66647039419692</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.80082935409725</v>
+        <v>3.800829354097249</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.687646430894727</v>
+        <v>-9.630029940145018</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7082512966341721</v>
+        <v>-0.6852047003342885</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.533704282598842</v>
+        <v>-2.476087791849131</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.646941130478161</v>
+        <v>1.681511024927988</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017778</v>
+        <v>3.789311112017777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.42358649257193</v>
+        <v>-9.365970001822221</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6158876374668054</v>
+        <v>-0.5928410411669218</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.269644344276046</v>
+        <v>-2.212027853526335</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.792116777310087</v>
+        <v>1.826686671759913</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.716506869067093</v>
+        <v>-8.658890378317384</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3358428217251714</v>
+        <v>-0.3127962254252878</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.269644344276046</v>
+        <v>-2.212027853526335</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.789329743649786</v>
+        <v>1.823899638099612</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388735</v>
+        <v>3.839374447388733</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.676322570700902</v>
+        <v>-8.618706079951194</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3194254784908539</v>
+        <v>-0.2963788821909703</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.229460045909855</v>
+        <v>-2.171843555160144</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.813783946557342</v>
+        <v>1.848353841007168</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626481</v>
+        <v>3.856161751626479</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.512922699761539</v>
+        <v>-8.45530620901183</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2546987088943515</v>
+        <v>-0.2316521125944679</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.066060174970493</v>
+        <v>-2.008443684220782</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.911190690341716</v>
+        <v>1.945760584791542</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291817</v>
+        <v>3.787330429291815</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.27944147753194</v>
+        <v>-8.221824986782231</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1533817911646596</v>
+        <v>-0.130335194864776</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.832578952740894</v>
+        <v>-1.774962461991183</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.059203852517328</v>
+        <v>2.093773746967154</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785793</v>
+        <v>3.801637122785791</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.129775086524425</v>
+        <v>-8.072158595774717</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.09640744507461285</v>
+        <v>-0.07336084877472926</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.739675461498358</v>
+        <v>-1.682058970748648</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.11205373694989</v>
+        <v>2.146623631399716</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390432</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.041974488500182</v>
+        <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.012368361931848</v>
+        <v>-7.93988312214383</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1633292805863045</v>
+        <v>-0.02508317257534776</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.622268736905782</v>
+        <v>-1.549783497117761</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.068613246356714</v>
+        <v>2.221356402325275</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105956</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.044789549187819</v>
+        <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.856630029372107</v>
+        <v>-7.784144789584088</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.09821888687477109</v>
+        <v>0.04002722113618562</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.46653040434604</v>
+        <v>-1.394045164558019</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.164871306580195</v>
+        <v>2.317614462548757</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960991</v>
+        <v>3.75388257196099</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.057695890411478</v>
+        <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.607630230688526</v>
+        <v>-7.535144990900507</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.01428737382232015</v>
+        <v>0.1525334818332769</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.46653040434604</v>
+        <v>-1.394045164558019</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.177777647803854</v>
+        <v>2.330520803772416</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.69293185560765</v>
+        <v>3.692931855607648</v>
       </c>
       <c r="C1908" t="n">
-        <v>2.929719960812259</v>
+        <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.71322022046163</v>
+        <v>-7.640734980673612</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1559245516861409</v>
+        <v>-0.01767844367518379</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.572120394119145</v>
+        <v>-1.499635154331124</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.986447724340772</v>
+        <v>2.139190880309334</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987909</v>
+        <v>3.770422583987907</v>
       </c>
       <c r="C1909" t="n">
-        <v>2.978264302689345</v>
+        <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.731955122580227</v>
+        <v>-7.659469882792209</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1148741706564933</v>
+        <v>0.02337193735446386</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.577716403779276</v>
+        <v>-1.505231163991255</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.03163446042178</v>
+        <v>2.184377616390342</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710817</v>
+        <v>3.760333686710815</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.858385380001177</v>
+        <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.584015081172628</v>
+        <v>-7.511529841384609</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1755770767816212</v>
+        <v>-0.037330968770664</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.557395487870718</v>
+        <v>-1.484910248082697</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.923948087278747</v>
+        <v>2.076691243247309</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.72356622940921</v>
+        <v>3.723566229409208</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.849671393747699</v>
+        <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.531045558918639</v>
+        <v>-7.458560319130621</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.163103254133504</v>
+        <v>-0.02485714612254686</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.50442596561673</v>
+        <v>-1.431940725828709</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.947015814377662</v>
+        <v>2.099758970346224</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098114</v>
+        <v>3.729969716098112</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.842710781652606</v>
+        <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.487497152147949</v>
+        <v>-7.415011912359931</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.152644503520321</v>
+        <v>-0.01439839550936384</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.50442596561673</v>
+        <v>-1.431940725828709</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.940055202282569</v>
+        <v>2.092798358251131</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493425</v>
+        <v>3.782922533493423</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.857173136033749</v>
+        <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.245348758694091</v>
+        <v>-7.172863518906072</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.04132279175763465</v>
+        <v>0.09692331625332251</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.50442596561673</v>
+        <v>-1.431940725828709</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.954517556663712</v>
+        <v>2.107260712632274</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722821</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.851705256492944</v>
+        <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.137089621571569</v>
+        <v>-7.064604381783551</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.003487016449430946</v>
+        <v>0.1347590915615262</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.50442596561673</v>
+        <v>-1.431940725828709</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.949049677122907</v>
+        <v>2.101792833091469</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.82805292879205</v>
+        <v>3.828052928792048</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.849203350503521</v>
+        <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.013798486754438</v>
+        <v>-6.94131324696642</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.04332753148799862</v>
+        <v>0.1815736394989558</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.381134830799599</v>
+        <v>-1.308649591011578</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.020522452023762</v>
+        <v>2.173265607992324</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919912</v>
+        <v>3.81245367891991</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.856904328740846</v>
+        <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.992649287850995</v>
+        <v>-6.920164048062976</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.05948818928670097</v>
+        <v>0.1977342972976581</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.359985631896156</v>
+        <v>-1.287500392108135</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.040912949603153</v>
+        <v>2.193656105571716</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318098</v>
+        <v>3.748328408318097</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.852685037087897</v>
+        <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.74888384586755</v>
+        <v>-6.676398606079532</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1527750744271295</v>
+        <v>0.2910211824380866</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.359985631896156</v>
+        <v>-1.287500392108135</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.036693657950204</v>
+        <v>2.189436813918766</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057531</v>
+        <v>3.82431123305753</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.854809351007913</v>
+        <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.647121025590256</v>
+        <v>-6.574635785802237</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1956045164580633</v>
+        <v>0.3338506244690205</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.346766563503727</v>
+        <v>-1.274281323715706</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.046749412905677</v>
+        <v>2.199492568874239</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279191</v>
+        <v>3.826354974279189</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.847551425991615</v>
+        <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.397270631641181</v>
+        <v>-6.324785391853163</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2882867490213954</v>
+        <v>0.4265328570323526</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.346766563503727</v>
+        <v>-1.274281323715706</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.039491487889379</v>
+        <v>2.192234643857941</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011504</v>
+        <v>3.835957987011502</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.851150549512264</v>
+        <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.221378539173749</v>
+        <v>-6.14889329938573</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.362242709529017</v>
+        <v>0.5004888175399742</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.346766563503727</v>
+        <v>-1.274281323715706</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.043090611410028</v>
+        <v>2.19583376737859</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392992</v>
+        <v>3.780933911392991</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.864478055566817</v>
+        <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.049932076151285</v>
+        <v>-5.977446836363266</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.444148800792556</v>
+        <v>0.5823949088035136</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.175320100481264</v>
+        <v>-1.102834860693243</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.15928599527806</v>
+        <v>2.312029151246622</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632787</v>
+        <v>3.773765222632785</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.863498533183114</v>
+        <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.975642510412946</v>
+        <v>-5.903157270624927</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4728851047041887</v>
+        <v>0.6111312127151463</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.101030534742925</v>
+        <v>-1.028545294954904</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.20288021233736</v>
+        <v>2.355623368305922</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461787988308</v>
+        <v>3.764617879883078</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.868193334237432</v>
+        <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.912006768179012</v>
+        <v>-5.839521528390993</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5030342026520795</v>
+        <v>0.6412803106630371</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.03739479250899</v>
+        <v>-0.9649095527209691</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.245756458732038</v>
+        <v>2.3984996147006</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107479</v>
+        <v>3.798814771074788</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.849387593021227</v>
+        <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.800580008853092</v>
+        <v>-5.728094769065073</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5287991651662436</v>
+        <v>0.6670452731772007</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.03739479250899</v>
+        <v>-0.9649095527209691</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.226950717515834</v>
+        <v>2.379693873484396</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242302</v>
+        <v>3.7976948842423</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.851130669646105</v>
+        <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.560149512048231</v>
+        <v>-5.487664272260212</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6267144405130649</v>
+        <v>0.7649605485240225</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7969642957041296</v>
+        <v>-0.7244790559161088</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.372952092223627</v>
+        <v>2.52569524819219</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367692</v>
+        <v>3.82159350936769</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.855059983480925</v>
+        <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.487906943877037</v>
+        <v>-5.415421704089018</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.659540781616363</v>
+        <v>0.7977868896273206</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7969642957041296</v>
+        <v>-0.7244790559161088</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.376881406058447</v>
+        <v>2.52962456202701</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879973</v>
+        <v>3.822326997879971</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.855738567398265</v>
+        <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.434908621595649</v>
+        <v>-5.36242338180763</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6814186944462581</v>
+        <v>0.8196648024572157</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7416280367021908</v>
+        <v>-0.66914279691417</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.410761745376951</v>
+        <v>2.563504901345513</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502345</v>
+        <v>3.848616626502343</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.852736638618258</v>
+        <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.326103736115922</v>
+        <v>-5.253618496327903</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7219387198581426</v>
+        <v>0.8601848278690998</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7416280367021908</v>
+        <v>-0.66914279691417</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.407759816596944</v>
+        <v>2.560502972565506</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675947</v>
+        <v>3.818668951675945</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.854315675628873</v>
+        <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.106082938078911</v>
+        <v>-5.033597698290892</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.811526076083561</v>
+        <v>0.9497721840945181</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6004081916342106</v>
+        <v>-0.5279229518461898</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.494070760648346</v>
+        <v>2.646813916616909</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539958</v>
+        <v>3.843274527539956</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.870209858430696</v>
+        <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.973215249015634</v>
+        <v>-4.900730009227614</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8805673345106952</v>
+        <v>1.018813442521653</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6004081916342106</v>
+        <v>-0.5279229518461898</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.50996494345017</v>
+        <v>2.662708099418732</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496265</v>
+        <v>3.845047386496264</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.871355702870998</v>
+        <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.853042165651135</v>
+        <v>-4.780556925863116</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9297824122967966</v>
+        <v>1.068028520307754</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4802351082697116</v>
+        <v>-0.4077498684816908</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.583214637909171</v>
+        <v>2.735957793877733</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577001</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.881443805432438</v>
+        <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.708370020551397</v>
+        <v>-4.635884780763378</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9977393728981314</v>
+        <v>1.135985480909089</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3355629631699742</v>
+        <v>-0.2630777233819534</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.680106027530453</v>
+        <v>2.832849183499015</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942107</v>
+        <v>3.735839222942105</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.867481296833863</v>
+        <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.76824484790909</v>
+        <v>-4.695759608121071</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9598269333564802</v>
+        <v>1.098073041367438</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3954377905276663</v>
+        <v>-0.3229525507396455</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.630218622517264</v>
+        <v>2.782961778485826</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674519</v>
+        <v>3.762647477674517</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.88988179015643</v>
+        <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.681445350130081</v>
+        <v>-4.608960110342062</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.01694722579065</v>
+        <v>1.155193333801607</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3954377905276663</v>
+        <v>-0.3229525507396455</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.65261911583983</v>
+        <v>2.805362271808392</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430698</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.889954191529842</v>
+        <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.683915056591887</v>
+        <v>-4.611429816803868</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.016031744579339</v>
+        <v>1.154277852590297</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3979074969894725</v>
+        <v>-0.3254222572014517</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.651209693336158</v>
+        <v>2.803952849304721</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003607</v>
+        <v>3.743220196003605</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.900961114004544</v>
+        <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.752285242915898</v>
+        <v>-4.679800003127879</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9996905925244373</v>
+        <v>1.137936700535395</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3886317979532575</v>
+        <v>-0.3161465581652367</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.66778203523259</v>
+        <v>2.820525191201152</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508375</v>
+        <v>3.714179139508373</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.891397822636435</v>
+        <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.766073295762944</v>
+        <v>-4.693588055974925</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.98461208001751</v>
+        <v>1.122858188028467</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3886317979532575</v>
+        <v>-0.3161465581652367</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.658218743864481</v>
+        <v>2.810961899833043</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.71090673141771</v>
+        <v>3.710906731417708</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.716107387676822</v>
+        <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.79706645509165</v>
+        <v>-4.724581215303631</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7969243813264146</v>
+        <v>0.9351704893373722</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3886317979532575</v>
+        <v>-0.3161465581652367</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.482928308904868</v>
+        <v>2.63567146487343</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205906</v>
+        <v>3.746042526205905</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.72067461966861</v>
+        <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.621592195299181</v>
+        <v>-4.549106955511162</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8716813172351898</v>
+        <v>1.009927425246147</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3886317979532575</v>
+        <v>-0.3161465581652367</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.487495540896655</v>
+        <v>2.640238696865218</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225451</v>
+        <v>3.765024323225449</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.696416648429817</v>
+        <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.73252844794043</v>
+        <v>-4.660043208152411</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8030488449398974</v>
+        <v>0.941294952950855</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3886317979532575</v>
+        <v>-0.3161465581652367</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.463237569657863</v>
+        <v>2.615980725626425</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.7732102971113</v>
+        <v>3.773210297111298</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.699548033649722</v>
+        <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.698864902468148</v>
+        <v>-4.626379662680129</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8196456483487158</v>
+        <v>0.9578917563596734</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3549682524809757</v>
+        <v>-0.2824830126929549</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.486567082161137</v>
+        <v>2.6393102381297</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.78434395226417</v>
+        <v>3.784343952264168</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.709720420081855</v>
+        <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.639012283264424</v>
+        <v>-4.566527043476405</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8537590824623376</v>
+        <v>0.9920051904732949</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3549682524809757</v>
+        <v>-0.2824830126929549</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.496739468593269</v>
+        <v>2.649482624561832</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742306</v>
+        <v>3.786949957742304</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.704666690655715</v>
+        <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.552768820238047</v>
+        <v>-4.480283580450028</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8832027382467489</v>
+        <v>1.021448846257706</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3549682524809757</v>
+        <v>-0.2824830126929549</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.49168573916713</v>
+        <v>2.644428895135692</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316052</v>
+        <v>3.752027499316051</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.69644246610024</v>
+        <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.598075639637027</v>
+        <v>-4.525590399849007</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8568557859316825</v>
+        <v>0.9951018939426399</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3957784154902065</v>
+        <v>-0.3232931757021857</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.458975416806117</v>
+        <v>2.611718572774679</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803196</v>
+        <v>3.753571165803195</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.696994339133342</v>
+        <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.627108744339328</v>
+        <v>-4.464336575850562</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8457944170838636</v>
+        <v>1.02015529657512</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3957784154902065</v>
+        <v>-0.3232931757021857</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.459527289839218</v>
+        <v>2.612270445807781</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809503</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.626267031024708</v>
+        <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.534298262888468</v>
+        <v>-4.371526094399703</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8121913015555731</v>
+        <v>0.9865521810468292</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3029679340393471</v>
+        <v>-0.2304826942513263</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.4444862706011</v>
+        <v>2.597229426569662</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.74828581656043</v>
+        <v>3.748285816560429</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.628140506949308</v>
+        <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.578687732217896</v>
+        <v>-4.41591556372913</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.796308989748403</v>
+        <v>0.9706698692396589</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.3473574033687748</v>
+        <v>-0.274872163580754</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.419726064928044</v>
+        <v>2.572469220896606</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472743</v>
+        <v>3.721077195472742</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.623216215461031</v>
+        <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.466016513981645</v>
+        <v>-4.30324434549288</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.836453185554626</v>
+        <v>1.010814065045882</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2346861851325246</v>
+        <v>-0.1622009453445038</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.482404504381517</v>
+        <v>2.635147660350079</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798543</v>
+        <v>3.743047603798542</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.628707511291699</v>
+        <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.353639512798972</v>
+        <v>-4.190867344310207</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8868952818583624</v>
+        <v>1.061256161349619</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2346861851325246</v>
+        <v>-0.1622009453445038</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.487895800212184</v>
+        <v>2.640638956180747</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498871</v>
+        <v>3.68959784049887</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.640204713060238</v>
+        <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.381419910700325</v>
+        <v>-4.21864774221156</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8872803244663605</v>
+        <v>1.061641203957616</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2624665830338777</v>
+        <v>-0.1899813432458569</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.482724763239911</v>
+        <v>2.635467919208474</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705331</v>
+        <v>3.64306962170533</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.478560433060891</v>
+        <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.464421191725604</v>
+        <v>-4.301649023236839</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6924355320569022</v>
+        <v>0.8667964115481581</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2810374675610514</v>
+        <v>-0.2085522277730306</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.30993795252426</v>
+        <v>2.462681108492823</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729276</v>
+        <v>3.682716310729275</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.598710093780097</v>
+        <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.573035270168935</v>
+        <v>-4.41026310168017</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7691395613987753</v>
+        <v>0.9435004408900314</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2810374675610514</v>
+        <v>-0.2085522277730306</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.430087613243466</v>
+        <v>2.582830769212028</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190775</v>
+        <v>3.733012441190774</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.61322311988242</v>
+        <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.537626231920792</v>
+        <v>-4.374854063432027</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7978162028003555</v>
+        <v>0.9721770822916116</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2810374675610514</v>
+        <v>-0.2085522277730306</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.444600639345789</v>
+        <v>2.597343795314351</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913432</v>
+        <v>3.741174069913431</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.610642561224788</v>
+        <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.499242569362641</v>
+        <v>-4.336470400873876</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8105891091659845</v>
+        <v>0.9849499886572406</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2426538050029002</v>
+        <v>-0.1701685652148794</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.465050278223048</v>
+        <v>2.617793434191611</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532493</v>
+        <v>3.751147197532492</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.60737159007009</v>
+        <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.322126239327475</v>
+        <v>-4.15935407083871</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8781646700253529</v>
+        <v>1.052525549516609</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2426538050029002</v>
+        <v>-0.1701685652148794</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.46177930706835</v>
+        <v>2.614522463036913</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793911</v>
+        <v>3.74132844879391</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.608054981832003</v>
+        <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.367218484161021</v>
+        <v>-4.204446315672255</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8608111638538478</v>
+        <v>1.035172043345104</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.30454984817229</v>
+        <v>-0.2320646083842692</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.42532507292863</v>
+        <v>2.578068228897192</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011243</v>
+        <v>3.750729377011242</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.601841957138418</v>
+        <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.187843062922253</v>
+        <v>-4.025070894433488</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9263483076557693</v>
+        <v>1.100709187147025</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.1477730900015713</v>
+        <v>-0.07528785021355056</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.513178103137475</v>
+        <v>2.665921259106037</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716991718982237</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.582649412470007</v>
+        <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.232857276442859</v>
+        <v>-4.070085107954094</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8891500775791166</v>
+        <v>1.063510957070372</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.178121985316176</v>
+        <v>-0.1056367455281552</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.475776221280302</v>
+        <v>2.628519377248864</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509546</v>
+        <v>3.737026608509545</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.588340974808953</v>
+        <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.499861786715294</v>
+        <v>-4.337089618226529</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7880398358090883</v>
+        <v>0.962400715300344</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3724850233591245</v>
+        <v>-0.2999997835711037</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.364849960793479</v>
+        <v>2.517593116762041</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760817</v>
+        <v>3.702309454760816</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.587544896705455</v>
+        <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.601059568152467</v>
+        <v>-4.438287399663702</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7467646451307206</v>
+        <v>0.9211255246219765</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4408938369044437</v>
+        <v>-0.3684085971164229</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.323008594562789</v>
+        <v>2.475751750531351</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815461</v>
+        <v>3.70557166181546</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.585144858259771</v>
+        <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.594548601538154</v>
+        <v>-4.431776433049389</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7469689933307624</v>
+        <v>0.9213298728220183</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4408938369044437</v>
+        <v>-0.3684085971164229</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.320608556117105</v>
+        <v>2.473351712085668</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378106</v>
+        <v>3.709510443378105</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.581669577468016</v>
+        <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.575510473830857</v>
+        <v>-4.412738305342092</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7511089636219264</v>
+        <v>0.925469843113182</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4990774482356383</v>
+        <v>-0.4265922084476175</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.282223108526634</v>
+        <v>2.434966264495196</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131257</v>
+        <v>3.731064473131256</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.759251446406697</v>
+        <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.606637104981475</v>
+        <v>-4.443864936492711</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9162401801003595</v>
+        <v>1.090601059591615</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4990774482356383</v>
+        <v>-0.4265922084476175</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.459804977465314</v>
+        <v>2.612548133433877</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067873</v>
+        <v>3.722447362067872</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.76008477539283</v>
+        <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.620503866315393</v>
+        <v>-4.457731697826628</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9115268045529259</v>
+        <v>1.085887684044182</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.5369353649694613</v>
+        <v>-0.4644501251814404</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.437923556411154</v>
+        <v>2.590666712379716</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789129</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.766093305789756</v>
+        <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.575699694775463</v>
+        <v>-4.412927526286698</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9354570035658238</v>
+        <v>1.10981788305708</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.5369353649694613</v>
+        <v>-0.4644501251814404</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.44393208680808</v>
+        <v>2.596675242776642</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519916</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.845245953581778</v>
+        <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.427956724540461</v>
+        <v>-4.265184556051696</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.073706839451847</v>
+        <v>1.248067718943102</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3691280077345781</v>
+        <v>-0.2966427679465573</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.623769148941032</v>
+        <v>2.776512304909594</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181178</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.848039575113259</v>
+        <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.529971407071682</v>
+        <v>-4.367199238582917</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.035694587970839</v>
+        <v>1.210055467462095</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3691280077345781</v>
+        <v>-0.2966427679465573</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.626562770472513</v>
+        <v>2.779305926441075</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394739</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.848701923504918</v>
+        <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.523818701018897</v>
+        <v>-4.361046532530133</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.038818018783611</v>
+        <v>1.213178898274867</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.3629753016817938</v>
+        <v>-0.290490061893773</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.630916742495842</v>
+        <v>2.783659898464404</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890615</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.847782400245028</v>
+        <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.540627999169399</v>
+        <v>-4.377855830680635</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.031174776263521</v>
+        <v>1.205535655754777</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3797845998322955</v>
+        <v>-0.3072993600442746</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.619911640345651</v>
+        <v>2.772654796314213</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798433</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.914117954041849</v>
+        <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.478330000393277</v>
+        <v>-4.315557831904512</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.122429529570791</v>
+        <v>1.296790409062046</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3797845998322955</v>
+        <v>-0.3072993600442746</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.686247194142472</v>
+        <v>2.838990350111034</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.8487291399922</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.622698826431247</v>
+        <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.276539802728119</v>
+        <v>-4.113767634239355</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9117264810262518</v>
+        <v>1.086087360517507</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1817664076631411</v>
+        <v>-0.1092811678751202</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.513638981833362</v>
+        <v>2.666382137801925</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852429</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.692989058753422</v>
+        <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.203161705639383</v>
+        <v>-4.040389537150618</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.011367952183921</v>
+        <v>1.185728831675177</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.1083883105744045</v>
+        <v>-0.03590307078638366</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.62795607240878</v>
+        <v>2.780699228377342</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319554</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.707616794869466</v>
+        <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.300902250264357</v>
+        <v>-4.138130081775593</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9868994704499754</v>
+        <v>1.161260349941231</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.1242775887073847</v>
+        <v>-0.05179234891936385</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.633050241645035</v>
+        <v>2.785793397613598</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489393</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.706152775694137</v>
+        <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.477240010387287</v>
+        <v>-4.314467841898522</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9149003472254753</v>
+        <v>1.089261226716731</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.3006153488303141</v>
+        <v>-0.2281301090422932</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.525783566395949</v>
+        <v>2.678526722364512</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397802</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.704644393734066</v>
+        <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.40081796395536</v>
+        <v>-4.238045795466595</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9439607838381745</v>
+        <v>1.11832166332943</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.3006153488303141</v>
+        <v>-0.2281301090422932</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.524275184435878</v>
+        <v>2.67701834040444</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316257</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.704507261169502</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.356444832316791</v>
+        <v>-4.193672663828027</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9615729039290382</v>
+        <v>1.135933783420294</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2562422171917455</v>
+        <v>-0.1837569774037247</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.550761930854455</v>
+        <v>2.703505086823017</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105971</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.698901055308093</v>
+        <v>2.808153067403842</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.233610611429624</v>
+        <v>-4.070838442940859</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.005100386422496</v>
+        <v>1.179461265913751</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2562422171917455</v>
+        <v>-0.1837569774037247</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.545155724993045</v>
+        <v>2.697898880961608</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190328</v>
+        <v>3.833011148190329</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.705282812335897</v>
+        <v>2.814534824431647</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.185954880868568</v>
+        <v>-4.023182712379803</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.030544435674722</v>
+        <v>1.204905315165978</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.2085864866306898</v>
+        <v>-0.136101246842669</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.580130920357483</v>
+        <v>2.732874076326045</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569621</v>
+        <v>3.822678210569622</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.710175185710622</v>
+        <v>2.819427197806371</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.085436722369813</v>
+        <v>-3.922664553881049</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.075644072448949</v>
+        <v>1.250004951940205</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.1080683281319353</v>
+        <v>-0.03558308834391444</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.645334188831461</v>
+        <v>2.798077344800023</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557297</v>
+        <v>3.828808877557298</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.696929858186494</v>
+        <v>2.806181870282244</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.146103312772203</v>
+        <v>-3.983331144283438</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.038132108763865</v>
+        <v>1.212492988255121</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.189766644850469</v>
+        <v>-0.1172814050624481</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.583069871276213</v>
+        <v>2.735813027244775</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932772</v>
+        <v>3.816837033932774</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.701027560797122</v>
+        <v>2.810279572892872</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.101264911163804</v>
+        <v>-3.93849274267504</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.060165172017853</v>
+        <v>1.234526051509109</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.1852232119055995</v>
+        <v>-0.1127379721175786</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.589893633653763</v>
+        <v>2.742636789622325</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917057</v>
+        <v>3.817932354917058</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.7051885004282</v>
+        <v>2.81444051252395</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.202023546920802</v>
+        <v>-4.039251378432038</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.024022657346132</v>
+        <v>1.198383536837388</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.2740487806326049</v>
+        <v>-0.2015635408445841</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.540759232048638</v>
+        <v>2.6935023880172</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405966</v>
+        <v>3.826684745405967</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.711068102956038</v>
+        <v>2.820320115051787</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.157820709834902</v>
+        <v>-3.995048541346137</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.04758339470833</v>
+        <v>1.221944274199585</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.2298459435467045</v>
+        <v>-0.1573607037586836</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.573160536828015</v>
+        <v>2.725903692796578</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265651</v>
+        <v>3.838199629265652</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.709478103425285</v>
+        <v>2.818730115521035</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.194799737498345</v>
+        <v>-4.03202756900958</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.0312017841122</v>
+        <v>1.205562663603456</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.1928720417553739</v>
+        <v>-0.1203868019673531</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.593754878372061</v>
+        <v>2.746498034340624</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284885</v>
+        <v>3.863895080284887</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.760725868608325</v>
+        <v>2.869977880704075</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.214857816363185</v>
+        <v>-4.052085647874421</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.074426317749303</v>
+        <v>1.248787197240559</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.1928720417553739</v>
+        <v>-0.1203868019673531</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.645002643555101</v>
+        <v>2.797745799523663</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321028</v>
+        <v>3.865338681321029</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.759166573202578</v>
+        <v>2.868418585298328</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.174927143185295</v>
+        <v>-4.01215497469653</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.088839291614712</v>
+        <v>1.263200171105968</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.1529413685774836</v>
+        <v>-0.08045612878946273</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.667401752056088</v>
+        <v>2.82014490802465</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475145</v>
+        <v>3.864489842475146</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.754114801440848</v>
+        <v>2.863366813536598</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.123895050462767</v>
+        <v>-3.961122881974002</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.104200356941994</v>
+        <v>1.278561236433249</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.1019092758549556</v>
+        <v>-0.02942403606693478</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.692969235927875</v>
+        <v>2.845712391896437</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84254736040486</v>
+        <v>3.842547360404862</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.771302205533553</v>
+        <v>2.880554217629303</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.058670869335562</v>
+        <v>-3.895898700846796</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.147477433485581</v>
+        <v>1.321838312976837</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.03668509472775</v>
+        <v>0.03580014506027085</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.749291148696903</v>
+        <v>2.902034304665465</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882564</v>
+        <v>3.840061186882566</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.767263177832833</v>
+        <v>2.876515189928583</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.021243849264428</v>
+        <v>-3.858471680775663</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.158409213813315</v>
+        <v>1.332770093304571</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.03143355669856834</v>
+        <v>0.04105168308945251</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.748403043813692</v>
+        <v>2.901146199782255</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992669</v>
+        <v>3.84516980899267</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.768519970164073</v>
+        <v>2.877771982259823</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.041355505299136</v>
+        <v>-3.878583336810371</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.151621343730672</v>
+        <v>1.325982223221928</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.02040621170114915</v>
+        <v>0.0520790280868717</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.756276243143384</v>
+        <v>2.909019399111947</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636294</v>
+        <v>3.828661445636296</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.929077741185284</v>
+        <v>3.038329753281034</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.987610690871931</v>
+        <v>-3.824838522383166</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.333677040522764</v>
+        <v>1.50803792001402</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.01034290226068718</v>
+        <v>0.06214233752733367</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.922871999828872</v>
+        <v>3.075615155797434</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957632</v>
+        <v>3.813222820957634</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.049190650403101</v>
+        <v>3.158442662498851</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.963819122265789</v>
+        <v>-3.801046953777024</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.463306577183038</v>
+        <v>1.637667456674294</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.01344866634545511</v>
+        <v>0.08593390613347596</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.057259850210375</v>
+        <v>3.210003006178937</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998758</v>
+        <v>3.81423072799876</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.04089862641696</v>
+        <v>3.15015063851271</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.937735038001981</v>
+        <v>-3.774962869513216</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.465448186902421</v>
+        <v>1.639809066393677</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.01344866634545511</v>
+        <v>0.08593390613347596</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.048967826224234</v>
+        <v>3.201710982192796</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896932</v>
+        <v>3.803397818896934</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.03909182200074</v>
+        <v>3.14834383409649</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.859603857153035</v>
+        <v>-3.696831688664269</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.494893854825779</v>
+        <v>1.669254734317035</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.08762547722913966</v>
+        <v>0.1601107170171605</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.091667108338224</v>
+        <v>3.244410264306786</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959863</v>
+        <v>3.796264143959864</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.056646227727531</v>
+        <v>3.165898239823281</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.850711395759752</v>
+        <v>-3.687939227270986</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.516005245109883</v>
+        <v>1.690366124601139</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.08762547722913966</v>
+        <v>0.1601107170171605</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.109221514065015</v>
+        <v>3.261964670033578</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945373</v>
+        <v>3.794424941945374</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.048501275132115</v>
+        <v>3.157753287227865</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.019187512729629</v>
+        <v>-3.856415344240864</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.440469845726516</v>
+        <v>1.614830725217772</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.05967764151255889</v>
+        <v>0.1321628813005797</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.084307860039651</v>
+        <v>3.237051016008213</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782715</v>
+        <v>3.795574066782716</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.029770972319977</v>
+        <v>3.139022984415727</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.321387983868046</v>
+        <v>-3.158615815379281</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.700859354459011</v>
+        <v>1.875220233950267</v>
       </c>
       <c r="F1997" t="n">
-        <v>-0.01067041785785183</v>
+        <v>0.06181482193016902</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.023368721605266</v>
+        <v>3.176111877573828</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632645</v>
+        <v>3.784671345632646</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.020434994816882</v>
+        <v>3.129687006912631</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.298666880184893</v>
+        <v>-3.135894711696128</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.700611818429177</v>
+        <v>1.874972697920433</v>
       </c>
       <c r="F1998" t="n">
-        <v>-0.01067041785785183</v>
+        <v>0.06181482193016902</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.014032744102171</v>
+        <v>3.166775900070733</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777682</v>
+        <v>3.783205696777684</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.179341120668051</v>
+        <v>3.2885931327638</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.29694183689485</v>
+        <v>-3.134169668406084</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.860207961596363</v>
+        <v>2.034568841087619</v>
       </c>
       <c r="F1999" t="n">
-        <v>-0.008945374567808084</v>
+        <v>0.06353986522021277</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.173973895927366</v>
+        <v>3.326717051895928</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644421</v>
+        <v>3.779933725644423</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.216418943161697</v>
+        <v>3.325670955257447</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.451722843673105</v>
+        <v>-3.288950675184339</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.835373381378708</v>
+        <v>2.009734260869964</v>
       </c>
       <c r="F2000" t="n">
-        <v>-0.04231304862228419</v>
+        <v>0.03017219116573666</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.191031113988327</v>
+        <v>3.34377426995689</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799968</v>
+        <v>3.769443619799969</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.213094299151242</v>
+        <v>3.322346311246992</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.400287510288445</v>
+        <v>-3.23751534179968</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.852622870722117</v>
+        <v>2.026983750213373</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.009122284762375477</v>
+        <v>0.08160752455039633</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.218567670008668</v>
+        <v>3.37131082597723</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331124</v>
+        <v>3.766673496331125</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.223100452795984</v>
+        <v>3.332352464891734</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.373336285961957</v>
+        <v>-3.210564117473192</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.873409514097454</v>
+        <v>2.04777039358871</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.02400263079009463</v>
+        <v>0.09648787057811548</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.237502031270041</v>
+        <v>3.390245187238603</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784117</v>
+        <v>3.768052067784119</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.407203584940944</v>
+        <v>3.516455597036694</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.509289294018274</v>
+        <v>-3.346517125529508</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.003131443019887</v>
+        <v>2.177492322511143</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.02400263079009463</v>
+        <v>0.09648787057811548</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.421605163415001</v>
+        <v>3.574348319383563</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.74392550571443</v>
+        <v>3.743925505714432</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.399320279843937</v>
+        <v>3.508572291939687</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.531697411823146</v>
+        <v>-3.36892524333438</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.986284890800931</v>
+        <v>2.160645770292187</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.02400263079009463</v>
+        <v>0.09648787057811548</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.413721858317994</v>
+        <v>3.566465014286556</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155041</v>
+        <v>3.719118627155042</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.401374279393574</v>
+        <v>3.510626291489324</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.679703179302545</v>
+        <v>-3.51693101081378</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.929136583358809</v>
+        <v>2.103497462850065</v>
       </c>
       <c r="F2005" t="n">
-        <v>-0.06272437807344683</v>
+        <v>0.009760861714574021</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.363739652549506</v>
+        <v>3.516482808518069</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161986</v>
+        <v>3.729452285161988</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.457627997115421</v>
+        <v>3.566880009211171</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.689144105191075</v>
+        <v>-3.52637193670231</v>
       </c>
       <c r="E2006" t="n">
-        <v>1.981613930725244</v>
+        <v>2.1559748102165</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.05970273946994459</v>
+        <v>0.1321879792579654</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.493449640797389</v>
+        <v>3.646192796765951</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321643</v>
+        <v>3.714941193321645</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.460519091660722</v>
+        <v>3.569771103756472</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.687857341651519</v>
+        <v>-3.525085173162753</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.985019730686368</v>
+        <v>2.159380610177624</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.06098950300950118</v>
+        <v>0.133474742797522</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.497112793466423</v>
+        <v>3.649855949434985</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347711</v>
+        <v>3.727898186347713</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.458630904554497</v>
+        <v>3.567882916650247</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.68941439564081</v>
+        <v>-3.526642227152045</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.982508721984426</v>
+        <v>2.156869601475682</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.06098950300950118</v>
+        <v>0.133474742797522</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.495224606360198</v>
+        <v>3.647967762328761</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887755</v>
+        <v>3.710654104887757</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.45345113415736</v>
+        <v>3.56270314625311</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.696686281164275</v>
+        <v>-3.533914112675509</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.974420197377903</v>
+        <v>2.148781076869159</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.05371761748603643</v>
+        <v>0.1262028572740573</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.485681704648982</v>
+        <v>3.638424860617544</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343073</v>
+        <v>3.712897612343075</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.451885144367512</v>
+        <v>3.561137156463262</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.694845262106023</v>
+        <v>-3.532073093617258</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.973590615211355</v>
+        <v>2.147951494702611</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.05498584415750485</v>
+        <v>0.1274710839455257</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.484876650862015</v>
+        <v>3.637619806830577</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647114</v>
+        <v>3.754911907647116</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.464958551233431</v>
+        <v>3.574210563329181</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.701753967605704</v>
+        <v>-3.538981799116939</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.983900539877402</v>
+        <v>2.158261419368658</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.05498584415750485</v>
+        <v>0.1274710839455257</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.497950057727934</v>
+        <v>3.650693213696496</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763537</v>
+        <v>3.749896851763538</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.464958551233431</v>
+        <v>3.574210563329181</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.703315610420564</v>
+        <v>-3.540543441931798</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.983275882751458</v>
+        <v>2.157636762242714</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.05498584415750485</v>
+        <v>0.1274710839455257</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.497950057727934</v>
+        <v>3.650693213696496</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.71583405539212</v>
+        <v>3.715834055392121</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.463482592360433</v>
+        <v>3.572734604456183</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.896813942095191</v>
+        <v>-3.568444229041271</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.904400591208609</v>
+        <v>2.145000488525927</v>
       </c>
       <c r="F2013" t="n">
-        <v>-0.01689285728290507</v>
+        <v>0.09287415980259089</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.45334687799069</v>
+        <v>3.628459100337737</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.439666940549856</v>
+        <v>3.837339925399336</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.369159911614337</v>
+        <v>3.713380098448614</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.896813942095191</v>
+        <v>-3.568444229041271</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.904400591208609</v>
+        <v>2.145000488525927</v>
       </c>
       <c r="F2014" t="n">
-        <v>-0.01689285728290507</v>
+        <v>0.09287415980259089</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.362223708600705</v>
+        <v>3.706443895434982</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240703.xlsx
+++ b/tame_output/ON/bt/strategyON_20240703.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>15.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>82.2%</t>
+          <t>73.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -824,22 +824,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>32.9%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.9%</t>
+          <t>-73.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.8%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>93.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.3%</t>
+          <t>-69.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.2%</t>
+          <t>447.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-518.4%</t>
+          <t>-530.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-39.4%</t>
+          <t>-38.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-161.7%</t>
+          <t>-166.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.2%</t>
+          <t>-23.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.5%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-173.5%</t>
+          <t>-182.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-214.7%</t>
+          <t>-229.4%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.4%</t>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-102.2%</t>
         </is>
       </c>
     </row>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355688</v>
+        <v>3.311888301355689</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279812</v>
+        <v>3.385382209279813</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082122</v>
+        <v>3.299560092082123</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.29349053375792</v>
+        <v>3.293490533757921</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760738</v>
+        <v>3.293766719760739</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296835</v>
+        <v>3.299918119296836</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201486</v>
+        <v>3.295507330201487</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153005</v>
+        <v>3.258791981153006</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207813</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191737</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108639</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097821</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094117</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199286</v>
+        <v>3.405960511199287</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.424633354969594</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297749</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539465</v>
+        <v>3.501052558539466</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.4924487119375</v>
+        <v>3.492448711937501</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141703</v>
+        <v>3.502790399141704</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729892</v>
+        <v>3.496851904729893</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440636</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.490059241608602</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4921016412974</v>
+        <v>3.492101641297401</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322545</v>
+        <v>3.573674025322546</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158923</v>
+        <v>3.600038265158924</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940721</v>
+        <v>3.691571733940722</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770582</v>
+        <v>3.676841549770583</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615286</v>
+        <v>3.685161381615287</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.71093553364622</v>
+        <v>3.710935533646221</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611571</v>
+        <v>3.768951674611572</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955331</v>
+        <v>3.728577929955332</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436233</v>
+        <v>3.766317079436234</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311953</v>
+        <v>3.784684521311954</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097249</v>
+        <v>3.80082935409725</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017777</v>
+        <v>3.789311112017778</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388733</v>
+        <v>3.839374447388735</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626479</v>
+        <v>3.856161751626481</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291815</v>
+        <v>3.787330429291817</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785791</v>
+        <v>3.801637122785793</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390432</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105956</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.75388257196099</v>
+        <v>3.753882571960991</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607648</v>
+        <v>3.69293185560765</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987907</v>
+        <v>3.770422583987909</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710815</v>
+        <v>3.760333686710817</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409208</v>
+        <v>3.72356622940921</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098112</v>
+        <v>3.729969716098115</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493423</v>
+        <v>3.782922533493426</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722822</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792048</v>
+        <v>3.828052928792051</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.81245367891991</v>
+        <v>3.812453678919913</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318097</v>
+        <v>3.748328408318099</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.82431123305753</v>
+        <v>3.824311233057532</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279189</v>
+        <v>3.826354974279192</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011502</v>
+        <v>3.835957987011505</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392991</v>
+        <v>3.780933911392994</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632785</v>
+        <v>3.773765222632789</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883078</v>
+        <v>3.764617879883081</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074788</v>
+        <v>3.798814771074792</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.7976948842423</v>
+        <v>3.797694884242303</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936769</v>
+        <v>3.821593509367694</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879971</v>
+        <v>3.822326997879975</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502343</v>
+        <v>3.848616626502347</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675945</v>
+        <v>3.818668951675948</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539956</v>
+        <v>3.843274527539959</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496264</v>
+        <v>3.845047386496267</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551577004</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942105</v>
+        <v>3.735839222942109</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674517</v>
+        <v>3.762647477674521</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430697</v>
+        <v>3.7291463984307</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003605</v>
+        <v>3.743220196003609</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508373</v>
+        <v>3.714179139508377</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417708</v>
+        <v>3.710906731417712</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205905</v>
+        <v>3.746042526205908</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225449</v>
+        <v>3.765024323225453</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111298</v>
+        <v>3.773210297111302</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264168</v>
+        <v>3.784343952264171</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742304</v>
+        <v>3.786949957742308</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316051</v>
+        <v>3.752027499316054</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803195</v>
+        <v>3.753571165803199</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.464336575850562</v>
+        <v>-4.554623504551309</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.02015529657512</v>
+        <v>0.9840405250948212</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3232931757021857</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809503</v>
+        <v>3.733390600809506</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.371526094399703</v>
+        <v>-4.461813023100449</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9865521810468292</v>
+        <v>0.9504374095665307</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.2304826942513263</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560429</v>
+        <v>3.748285816560433</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.41591556372913</v>
+        <v>-4.506202492429876</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9706698692396589</v>
+        <v>0.9345550977593604</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.274872163580754</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472742</v>
+        <v>3.721077195472746</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.30324434549288</v>
+        <v>-4.393531274193626</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.010814065045882</v>
+        <v>0.9746992935655836</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.1622009453445038</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798542</v>
+        <v>3.743047603798545</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.190867344310207</v>
+        <v>-4.281154273010953</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.061256161349619</v>
+        <v>1.02514138986932</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.1622009453445038</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959784049887</v>
+        <v>3.689597840498873</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.21864774221156</v>
+        <v>-4.308934670912306</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.061641203957616</v>
+        <v>1.025526432477318</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.1899813432458569</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306962170533</v>
+        <v>3.643069621705334</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.301649023236839</v>
+        <v>-4.391935951937585</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8667964115481581</v>
+        <v>0.8306816400678596</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2085522277730306</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729275</v>
+        <v>3.682716310729278</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.41026310168017</v>
+        <v>-4.500550030380916</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9435004408900314</v>
+        <v>0.9073856694097329</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2085522277730306</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190774</v>
+        <v>3.733012441190778</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.374854063432027</v>
+        <v>-4.465140992132773</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9721770822916116</v>
+        <v>0.9360623108113129</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2085522277730306</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913431</v>
+        <v>3.741174069913435</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.336470400873876</v>
+        <v>-4.426757329574622</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9849499886572406</v>
+        <v>0.9488352171769421</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.1701685652148794</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532492</v>
+        <v>3.751147197532496</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.15935407083871</v>
+        <v>-4.249640999539456</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.052525549516609</v>
+        <v>1.016410778036311</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.1701685652148794</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.74132844879391</v>
+        <v>3.741328448793913</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.204446315672255</v>
+        <v>-4.294733244373002</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.035172043345104</v>
+        <v>0.9990572718648052</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.2320646083842692</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011242</v>
+        <v>3.750729377011246</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.025070894433488</v>
+        <v>-4.115357823134234</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.100709187147025</v>
+        <v>1.064594415666727</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.07528785021355056</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982237</v>
+        <v>3.71699171898224</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.070085107954094</v>
+        <v>-4.16037203665484</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.063510957070372</v>
+        <v>1.027396185590074</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.1056367455281552</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509545</v>
+        <v>3.737026608509549</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.337089618226529</v>
+        <v>-4.427376546927275</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.962400715300344</v>
+        <v>0.9262859438200459</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.2999997835711037</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760816</v>
+        <v>3.70230945476082</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.438287399663702</v>
+        <v>-4.528574328364448</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9211255246219765</v>
+        <v>0.8850107531416782</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.3684085971164229</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.70557166181546</v>
+        <v>3.705571661815464</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.431776433049389</v>
+        <v>-4.522063361750135</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9213298728220183</v>
+        <v>0.88521510134172</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.3684085971164229</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378105</v>
+        <v>3.709510443378108</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.412738305342092</v>
+        <v>-4.503025234042838</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.925469843113182</v>
+        <v>0.8893550716328837</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.4265922084476175</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131256</v>
+        <v>3.731064473131259</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.443864936492711</v>
+        <v>-4.534151865193456</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.090601059591615</v>
+        <v>1.054486288111317</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.4265922084476175</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067872</v>
+        <v>3.722447362067876</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.457731697826628</v>
+        <v>-4.548018626527374</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.085887684044182</v>
+        <v>1.049772912563883</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.4644501251814404</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789129</v>
+        <v>3.787425580789133</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.412927526286698</v>
+        <v>-4.503214454987444</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.10981788305708</v>
+        <v>1.073703111576781</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.4644501251814404</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519916</v>
+        <v>3.78150125051992</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.265184556051696</v>
+        <v>-4.355471484752441</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.248067718943102</v>
+        <v>1.211952947462804</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.2966427679465573</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181178</v>
+        <v>3.802245929181182</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.367199238582917</v>
+        <v>-4.457486167283663</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.210055467462095</v>
+        <v>1.173940695981797</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.2966427679465573</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394739</v>
+        <v>3.805608985394742</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.361046532530133</v>
+        <v>-4.451333461230878</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.213178898274867</v>
+        <v>1.177064126794569</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.290490061893773</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890615</v>
+        <v>3.798239794890619</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.377855830680635</v>
+        <v>-4.46814275938138</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.205535655754777</v>
+        <v>1.169420884274478</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.3072993600442746</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798433</v>
+        <v>3.867362636798436</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.315557831904512</v>
+        <v>-4.405844760605258</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.296790409062046</v>
+        <v>1.260675637581748</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.3072993600442746</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.8487291399922</v>
+        <v>3.848729139992203</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.113767634239355</v>
+        <v>-4.2040545629401</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.086087360517507</v>
+        <v>1.049972589037209</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.1092811678751202</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852429</v>
+        <v>3.841444817852433</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.040389537150618</v>
+        <v>-4.130676465851364</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.185728831675177</v>
+        <v>1.149614060194879</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.03590307078638366</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319554</v>
+        <v>3.819063300319558</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.138130081775593</v>
+        <v>-4.228417010476338</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.161260349941231</v>
+        <v>1.125145578460933</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.05179234891936385</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489393</v>
+        <v>3.831819032489396</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.314467841898522</v>
+        <v>-4.404754770599268</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.089261226716731</v>
+        <v>1.053146455236433</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.2281301090422932</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397802</v>
+        <v>3.836411672397806</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.238045795466595</v>
+        <v>-4.328332724167341</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.11832166332943</v>
+        <v>1.082206891849132</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.2281301090422932</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316257</v>
+        <v>3.833513460316261</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.193672663828027</v>
+        <v>-4.283959592528772</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.135933783420294</v>
+        <v>1.099819011939996</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.1837569774037247</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105971</v>
+        <v>3.821562117105975</v>
       </c>
       <c r="C1977" t="n">
         <v>2.808153067403842</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.070838442940859</v>
+        <v>-4.161125371641605</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.179461265913751</v>
+        <v>1.143346494433453</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.1837569774037247</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190329</v>
+        <v>3.833011148190333</v>
       </c>
       <c r="C1978" t="n">
         <v>2.814534824431647</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.023182712379803</v>
+        <v>-4.113469641080549</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.204905315165978</v>
+        <v>1.16879054368568</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.136101246842669</v>
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569622</v>
+        <v>3.822678210569625</v>
       </c>
       <c r="C1979" t="n">
         <v>2.819427197806371</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.922664553881049</v>
+        <v>-4.040603768773277</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.250004951940205</v>
+        <v>1.202829265983313</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.03558308834391444</v>
+        <v>-0.06323537453539663</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.798077344800023</v>
+        <v>2.781485973085134</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557298</v>
+        <v>3.8288088775573</v>
       </c>
       <c r="C1980" t="n">
         <v>2.806181870282244</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.983331144283438</v>
+        <v>-4.101270359175667</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.212492988255121</v>
+        <v>1.16531730229823</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.1172814050624481</v>
+        <v>-0.1449336912539303</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.735813027244775</v>
+        <v>2.719221655529886</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932774</v>
+        <v>3.816837033932775</v>
       </c>
       <c r="C1981" t="n">
         <v>2.810279572892872</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.93849274267504</v>
+        <v>-4.056431957567268</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.234526051509109</v>
+        <v>1.187350365552218</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.1127379721175786</v>
+        <v>-0.1403902583090608</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.742636789622325</v>
+        <v>2.726045417907436</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917058</v>
+        <v>3.81793235491706</v>
       </c>
       <c r="C1982" t="n">
         <v>2.81444051252395</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.039251378432038</v>
+        <v>-4.157190593324266</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.198383536837388</v>
+        <v>1.151207850880497</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.2015635408445841</v>
+        <v>-0.2292158270360662</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.6935023880172</v>
+        <v>2.676911016302311</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405967</v>
+        <v>3.826684745405969</v>
       </c>
       <c r="C1983" t="n">
         <v>2.820320115051787</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.995048541346137</v>
+        <v>-4.112987756238366</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.221944274199585</v>
+        <v>1.174768588242694</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1573607037586836</v>
+        <v>-0.1850129899501658</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.725903692796578</v>
+        <v>2.709312321081688</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265652</v>
+        <v>3.838199629265654</v>
       </c>
       <c r="C1984" t="n">
         <v>2.818730115521035</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.03202756900958</v>
+        <v>-4.149966783901808</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.205562663603456</v>
+        <v>1.158386977646564</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.1203868019673531</v>
+        <v>-0.1480390881588353</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.746498034340624</v>
+        <v>2.729906662625734</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284887</v>
+        <v>3.863895080284888</v>
       </c>
       <c r="C1985" t="n">
         <v>2.869977880704075</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.052085647874421</v>
+        <v>-4.170024862766649</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.248787197240559</v>
+        <v>1.201611511283668</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.1203868019673531</v>
+        <v>-0.1480390881588353</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.797745799523663</v>
+        <v>2.781154427808774</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321029</v>
+        <v>3.865338681321031</v>
       </c>
       <c r="C1986" t="n">
         <v>2.868418585298328</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.01215497469653</v>
+        <v>-4.130094189588759</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.263200171105968</v>
+        <v>1.216024485149077</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.08045612878946273</v>
+        <v>-0.1081084149809449</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.82014490802465</v>
+        <v>2.803553536309761</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475146</v>
+        <v>3.864489842475148</v>
       </c>
       <c r="C1987" t="n">
         <v>2.863366813536598</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.961122881974002</v>
+        <v>-4.079062096866231</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.278561236433249</v>
+        <v>1.231385550476358</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.02942403606693478</v>
+        <v>-0.05707632225841697</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.845712391896437</v>
+        <v>2.829121020181548</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404862</v>
+        <v>3.842547360404864</v>
       </c>
       <c r="C1988" t="n">
         <v>2.880554217629303</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.895898700846796</v>
+        <v>-4.013837915739026</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.321838312976837</v>
+        <v>1.274662627019945</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.03580014506027085</v>
+        <v>0.00814785886878866</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.902034304665465</v>
+        <v>2.885442932950576</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882566</v>
+        <v>3.840061186882568</v>
       </c>
       <c r="C1989" t="n">
         <v>2.876515189928583</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.858471680775663</v>
+        <v>-3.976410895667892</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.332770093304571</v>
+        <v>1.285594407347679</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.04105168308945251</v>
+        <v>0.01339939689797032</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.901146199782255</v>
+        <v>2.884554828067365</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899267</v>
+        <v>3.845169808992672</v>
       </c>
       <c r="C1990" t="n">
         <v>2.877771982259823</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.878583336810371</v>
+        <v>-3.9965225517026</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.325982223221928</v>
+        <v>1.278806537265036</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.0520790280868717</v>
+        <v>0.02442674189538951</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.909019399111947</v>
+        <v>2.892428027397057</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636296</v>
+        <v>3.828661445636298</v>
       </c>
       <c r="C1991" t="n">
         <v>3.038329753281034</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.824838522383166</v>
+        <v>-3.942777737275395</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.50803792001402</v>
+        <v>1.460862234057129</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.06214233752733367</v>
+        <v>0.03449005133585148</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.075615155797434</v>
+        <v>3.059023784082545</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957634</v>
+        <v>3.813222820957636</v>
       </c>
       <c r="C1992" t="n">
         <v>3.158442662498851</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.801046953777024</v>
+        <v>-3.918986168669253</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.637667456674294</v>
+        <v>1.590491770717403</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.08593390613347596</v>
+        <v>0.05828161994199377</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.210003006178937</v>
+        <v>3.193411634464048</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799876</v>
+        <v>3.814230727998762</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15015063851271</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.774962869513216</v>
+        <v>-3.892902084405445</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.639809066393677</v>
+        <v>1.592633380436785</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.08593390613347596</v>
+        <v>0.05828161994199377</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.201710982192796</v>
+        <v>3.185119610477907</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896934</v>
+        <v>3.803397818896936</v>
       </c>
       <c r="C1994" t="n">
         <v>3.14834383409649</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.696831688664269</v>
+        <v>-3.814770903556498</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.669254734317035</v>
+        <v>1.622079048360143</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.1601107170171605</v>
+        <v>0.1324584308256783</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.244410264306786</v>
+        <v>3.227818892591897</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959864</v>
+        <v>3.796264143959866</v>
       </c>
       <c r="C1995" t="n">
         <v>3.165898239823281</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.687939227270986</v>
+        <v>-3.805878442163215</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.690366124601139</v>
+        <v>1.643190438644248</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.1601107170171605</v>
+        <v>0.1324584308256783</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.261964670033578</v>
+        <v>3.245373298318688</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945374</v>
+        <v>3.794424941945376</v>
       </c>
       <c r="C1996" t="n">
         <v>3.157753287227865</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.856415344240864</v>
+        <v>-3.974354559133093</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.614830725217772</v>
+        <v>1.567655039260881</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1321628813005797</v>
+        <v>0.1045105951090975</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.237051016008213</v>
+        <v>3.220459644293324</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782716</v>
+        <v>3.795574066782718</v>
       </c>
       <c r="C1997" t="n">
         <v>3.139022984415727</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.158615815379281</v>
+        <v>-3.27655503027151</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.875220233950267</v>
+        <v>1.828044547993376</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.06181482193016902</v>
+        <v>0.03416253573868683</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.176111877573828</v>
+        <v>3.159520505858939</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632646</v>
+        <v>3.784671345632648</v>
       </c>
       <c r="C1998" t="n">
         <v>3.129687006912631</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.135894711696128</v>
+        <v>-3.253833926588357</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.874972697920433</v>
+        <v>1.827797011963541</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.06181482193016902</v>
+        <v>0.03416253573868683</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.166775900070733</v>
+        <v>3.150184528355844</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777684</v>
+        <v>3.783205696777686</v>
       </c>
       <c r="C1999" t="n">
         <v>3.2885931327638</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.134169668406084</v>
+        <v>-3.252108883298313</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.034568841087619</v>
+        <v>1.987393155130728</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.06353986522021277</v>
+        <v>0.03588757902873058</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.326717051895928</v>
+        <v>3.310125680181039</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644423</v>
+        <v>3.779933725644424</v>
       </c>
       <c r="C2000" t="n">
         <v>3.325670955257447</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.288950675184339</v>
+        <v>-3.406889890076569</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.009734260869964</v>
+        <v>1.962558574913072</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.03017219116573666</v>
+        <v>0.002519904974254472</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.34377426995689</v>
+        <v>3.327182898242</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799969</v>
+        <v>3.769443619799972</v>
       </c>
       <c r="C2001" t="n">
         <v>3.322346311246992</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.23751534179968</v>
+        <v>-3.355454556691909</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.026983750213373</v>
+        <v>1.979808064256481</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.08160752455039633</v>
+        <v>0.05395523835891414</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.37131082597723</v>
+        <v>3.354719454262341</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331125</v>
+        <v>3.766673496331127</v>
       </c>
       <c r="C2002" t="n">
         <v>3.332352464891734</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.210564117473192</v>
+        <v>-3.328503332365421</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.04777039358871</v>
+        <v>2.000594707631818</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.09648787057811548</v>
+        <v>0.06883558438663329</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.390245187238603</v>
+        <v>3.373653815523714</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784119</v>
+        <v>3.76805206778412</v>
       </c>
       <c r="C2003" t="n">
         <v>3.516455597036694</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.346517125529508</v>
+        <v>-3.464456340421737</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.177492322511143</v>
+        <v>2.130316636554252</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.09648787057811548</v>
+        <v>0.06883558438663329</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.574348319383563</v>
+        <v>3.557756947668674</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714432</v>
+        <v>3.743925505714434</v>
       </c>
       <c r="C2004" t="n">
         <v>3.508572291939687</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.36892524333438</v>
+        <v>-3.486864458226609</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.160645770292187</v>
+        <v>2.113470084335296</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.09648787057811548</v>
+        <v>0.06883558438663329</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.566465014286556</v>
+        <v>3.549873642571667</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155042</v>
+        <v>3.719118627155044</v>
       </c>
       <c r="C2005" t="n">
         <v>3.510626291489324</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.51693101081378</v>
+        <v>-3.639707735642976</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.103497462850065</v>
+        <v>2.054386772918386</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.009760861714574021</v>
+        <v>-0.01491952897283605</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.516482808518069</v>
+        <v>3.501674574105623</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161988</v>
+        <v>3.729452285161989</v>
       </c>
       <c r="C2006" t="n">
         <v>3.566880009211171</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.52637193670231</v>
+        <v>-3.649148661531506</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.1559748102165</v>
+        <v>2.106864120284822</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.1321879792579654</v>
+        <v>-0.01491952897283605</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.646192796765951</v>
+        <v>3.55792829182747</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321645</v>
+        <v>3.714941193321646</v>
       </c>
       <c r="C2007" t="n">
         <v>3.569771103756472</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.525085173162753</v>
+        <v>-3.64786189799195</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.159380610177624</v>
+        <v>2.110269920245945</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.133474742797522</v>
+        <v>-0.01363276543327946</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.649855949434985</v>
+        <v>3.561591444496505</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347713</v>
+        <v>3.727898186347715</v>
       </c>
       <c r="C2008" t="n">
         <v>3.567882916650247</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.526642227152045</v>
+        <v>-3.649418951981241</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.156869601475682</v>
+        <v>2.107758911544003</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.133474742797522</v>
+        <v>-0.01363276543327946</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.647967762328761</v>
+        <v>3.55970325739028</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887757</v>
+        <v>3.710654104887759</v>
       </c>
       <c r="C2009" t="n">
         <v>3.56270314625311</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.533914112675509</v>
+        <v>-3.656690837504706</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.148781076869159</v>
+        <v>2.09967038693748</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.1262028572740573</v>
+        <v>-0.02090465095674421</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.638424860617544</v>
+        <v>3.550160355679064</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343075</v>
+        <v>3.712897612343077</v>
       </c>
       <c r="C2010" t="n">
         <v>3.561137156463262</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.532073093617258</v>
+        <v>-3.654849818446455</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.147951494702611</v>
+        <v>2.098840804770933</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.1274710839455257</v>
+        <v>-0.01963642428527579</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.637619806830577</v>
+        <v>3.549355301892096</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647116</v>
+        <v>3.754911907647117</v>
       </c>
       <c r="C2011" t="n">
         <v>3.574210563329181</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.538981799116939</v>
+        <v>-3.661758523946135</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.158261419368658</v>
+        <v>2.109150729436979</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.1274710839455257</v>
+        <v>-0.01963642428527579</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.650693213696496</v>
+        <v>3.562428708758016</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763538</v>
+        <v>3.74989685176354</v>
       </c>
       <c r="C2012" t="n">
         <v>3.574210563329181</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.540543441931798</v>
+        <v>-3.663320166760995</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.157636762242714</v>
+        <v>2.108526072311035</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.1274710839455257</v>
+        <v>-0.01963642428527579</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.650693213696496</v>
+        <v>3.562428708758016</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392121</v>
+        <v>3.715834055392123</v>
       </c>
       <c r="C2013" t="n">
         <v>3.572734604456183</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.568444229041271</v>
+        <v>-3.691220953870468</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.145000488525927</v>
+        <v>2.095889798594248</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.09287415980259089</v>
+        <v>-0.05423334842821059</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.628459100337737</v>
+        <v>3.540194595399257</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.837339925399336</v>
+        <v>3.436768009612625</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.713380098448614</v>
+        <v>3.444833860021118</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.568444229041271</v>
+        <v>-3.691220953870468</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.145000488525927</v>
+        <v>2.095889798594248</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.09287415980259089</v>
+        <v>-0.05423334842821059</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.706443895434982</v>
+        <v>3.437897657007486</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240703.xlsx
+++ b/tame_output/ON/bt/strategyON_20240703.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>15.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,27 +849,27 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>45.3%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.5%</t>
+          <t>-73.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>108.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.9%</t>
+          <t>93.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.5%</t>
+          <t>-51.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.5%</t>
+          <t>-69.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-530.7%</t>
+          <t>-530.0%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.2%</t>
+          <t>-40.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-38.6%</t>
+          <t>-32.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>77.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-166.6%</t>
+          <t>-166.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.2%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.2%</t>
+          <t>-32.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-182.6%</t>
+          <t>-171.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-229.4%</t>
+          <t>-201.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-28.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-102.2%</t>
+          <t>-75.4%</t>
         </is>
       </c>
     </row>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355689</v>
+        <v>3.311888301355688</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279813</v>
+        <v>3.385382209279812</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440636</v>
+        <v>3.499971739440635</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608602</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105956</v>
+        <v>3.784718794105957</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960991</v>
+        <v>3.753882571960992</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.69293185560765</v>
+        <v>3.692931855607651</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987909</v>
+        <v>3.77042258398791</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098115</v>
+        <v>3.729969716098114</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493426</v>
+        <v>3.782922533493425</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.172863518906072</v>
+        <v>-7.243067615442058</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.09692331625332251</v>
+        <v>0.06884167763892846</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.431940725828709</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722822</v>
+        <v>3.828551486722821</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.064604381783551</v>
+        <v>-7.134808478319536</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1347590915615262</v>
+        <v>0.1066774529471322</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.431940725828709</v>
@@ -45596,10 +45596,10 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.94131324696642</v>
+        <v>-7.011517343502406</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1815736394989558</v>
+        <v>0.1534920008845613</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.308649591011578</v>
@@ -45619,10 +45619,10 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.920164048062976</v>
+        <v>-6.990368144598962</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1977342972976581</v>
+        <v>0.1696526586832636</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.287500392108135</v>
@@ -45642,10 +45642,10 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.676398606079532</v>
+        <v>-6.746602702615518</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2910211824380866</v>
+        <v>0.2629395438236921</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.287500392108135</v>
@@ -45665,10 +45665,10 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.574635785802237</v>
+        <v>-6.644839882338223</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3338506244690205</v>
+        <v>0.305768985854626</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.274281323715706</v>
@@ -45688,10 +45688,10 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.324785391853163</v>
+        <v>-6.394989488389148</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4265328570323526</v>
+        <v>0.3984512184179581</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.274281323715706</v>
@@ -45711,10 +45711,10 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.14889329938573</v>
+        <v>-6.219097395921716</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5004888175399742</v>
+        <v>0.4724071789255797</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.274281323715706</v>
@@ -45734,10 +45734,10 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.977446836363266</v>
+        <v>-6.047650932899253</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5823949088035136</v>
+        <v>0.5543132701891187</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.102834860693243</v>
@@ -45757,10 +45757,10 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.903157270624927</v>
+        <v>-5.973361367160914</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6111312127151463</v>
+        <v>0.5830495741007513</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.028545294954904</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.839521528390993</v>
+        <v>-5.909725624926979</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6412803106630371</v>
+        <v>0.6131986720486426</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.9649095527209691</v>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.728094769065073</v>
+        <v>-5.798298865601059</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6670452731772007</v>
+        <v>0.6389636345628062</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.9649095527209691</v>
@@ -45826,10 +45826,10 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.487664272260212</v>
+        <v>-5.557868368796199</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7649605485240225</v>
+        <v>0.7368789099096276</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.7244790559161088</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.415421704089018</v>
+        <v>-5.485625800625004</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7977868896273206</v>
+        <v>0.7697052510129256</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.7244790559161088</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.36242338180763</v>
+        <v>-5.432627478343616</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8196648024572157</v>
+        <v>0.7915831638428208</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.66914279691417</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.253618496327903</v>
+        <v>-5.323822592863889</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8601848278690998</v>
+        <v>0.8321031892547053</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.66914279691417</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.033597698290892</v>
+        <v>-5.103801794826879</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9497721840945181</v>
+        <v>0.9216905454801236</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.5279229518461898</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.900730009227614</v>
+        <v>-4.970934105763601</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.018813442521653</v>
+        <v>0.9907318039072579</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.5279229518461898</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.780556925863116</v>
+        <v>-4.850761022399102</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.068028520307754</v>
+        <v>1.039946881693359</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4077498684816908</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577004</v>
+        <v>3.791273551577003</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.635884780763378</v>
+        <v>-4.706088877299365</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.135985480909089</v>
+        <v>1.107903842294694</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.2630777233819534</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.695759608121071</v>
+        <v>-4.765963704657057</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.098073041367438</v>
+        <v>1.069991402753043</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.3229525507396455</v>
@@ -46033,10 +46033,10 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.608960110342062</v>
+        <v>-4.679164206878049</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.155193333801607</v>
+        <v>1.127111695187212</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.3229525507396455</v>
@@ -46056,10 +46056,10 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.611429816803868</v>
+        <v>-4.681633913339855</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.154277852590297</v>
+        <v>1.126196213975902</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.3254222572014517</v>
@@ -46079,10 +46079,10 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.679800003127879</v>
+        <v>-4.750004099663865</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.137936700535395</v>
+        <v>1.109855061921</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.3161465581652367</v>
@@ -46102,10 +46102,10 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.693588055974925</v>
+        <v>-4.763792152510912</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.122858188028467</v>
+        <v>1.094776549414073</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.3161465581652367</v>
@@ -46125,10 +46125,10 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.724581215303631</v>
+        <v>-4.794785311839617</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9351704893373722</v>
+        <v>0.9070888507229775</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.3161465581652367</v>
@@ -46148,10 +46148,10 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.549106955511162</v>
+        <v>-4.619311052047149</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.009927425246147</v>
+        <v>0.9818457866317527</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.3161465581652367</v>
@@ -46171,10 +46171,10 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.660043208152411</v>
+        <v>-4.730247304688397</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.941294952950855</v>
+        <v>0.9132133143364602</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.3161465581652367</v>
@@ -46194,10 +46194,10 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.626379662680129</v>
+        <v>-4.696583759216115</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9578917563596734</v>
+        <v>0.9298101177452787</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.2824830126929549</v>
@@ -46217,10 +46217,10 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.566527043476405</v>
+        <v>-4.636731140012392</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9920051904732949</v>
+        <v>0.9639235518589002</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.2824830126929549</v>
@@ -46240,10 +46240,10 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.480283580450028</v>
+        <v>-4.550487676986014</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.021448846257706</v>
+        <v>0.9933672076433118</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.2824830126929549</v>
@@ -46263,10 +46263,10 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.525590399849007</v>
+        <v>-4.595794496384994</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9951018939426399</v>
+        <v>0.9670202553282454</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.3232931757021857</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803199</v>
+        <v>3.753571165803198</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.554623504551309</v>
+        <v>-4.624827601087295</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9840405250948212</v>
+        <v>0.9559588864804265</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3232931757021857</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809506</v>
+        <v>3.733390600809505</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.461813023100449</v>
+        <v>-4.532017119636436</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9504374095665307</v>
+        <v>0.9223557709521359</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.2304826942513263</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560433</v>
+        <v>3.748285816560432</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.506202492429876</v>
+        <v>-4.576406588965863</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9345550977593604</v>
+        <v>0.9064734591449657</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.274872163580754</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472746</v>
+        <v>3.721077195472745</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.393531274193626</v>
+        <v>-4.463735370729613</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9746992935655836</v>
+        <v>0.9466176549511889</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.1622009453445038</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798545</v>
+        <v>3.743047603798544</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.281154273010953</v>
+        <v>-4.35135836954694</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.02514138986932</v>
+        <v>0.9970597512549253</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.1622009453445038</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498873</v>
+        <v>3.689597840498872</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.308934670912306</v>
+        <v>-4.379138767448293</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.025526432477318</v>
+        <v>0.9974447938629232</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.1899813432458569</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705334</v>
+        <v>3.643069621705333</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.391935951937585</v>
+        <v>-4.462140048473572</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8306816400678596</v>
+        <v>0.8026000014534649</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2085522277730306</v>
@@ -46447,10 +46447,10 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.500550030380916</v>
+        <v>-4.570754126916903</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9073856694097329</v>
+        <v>0.8793040307953381</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2085522277730306</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190778</v>
+        <v>3.733012441190777</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.465140992132773</v>
+        <v>-4.53534508866876</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9360623108113129</v>
+        <v>0.9079806721969184</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2085522277730306</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913435</v>
+        <v>3.741174069913434</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.426757329574622</v>
+        <v>-4.496961426110609</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9488352171769421</v>
+        <v>0.9207535785625474</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.1701685652148794</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532496</v>
+        <v>3.751147197532495</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.249640999539456</v>
+        <v>-4.319845096075443</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.016410778036311</v>
+        <v>0.9883291394219158</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.1701685652148794</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793913</v>
+        <v>3.741328448793912</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.294733244373002</v>
+        <v>-4.364937340908988</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9990572718648052</v>
+        <v>0.9709756332504105</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.2320646083842692</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011246</v>
+        <v>3.750729377011245</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.115357823134234</v>
+        <v>-4.185561919670221</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.064594415666727</v>
+        <v>1.036512777052332</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.07528785021355056</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898224</v>
+        <v>3.716991718982239</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.16037203665484</v>
+        <v>-4.230576133190826</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.027396185590074</v>
+        <v>0.9993145469756795</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.1056367455281552</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509549</v>
+        <v>3.737026608509548</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.427376546927275</v>
+        <v>-4.497580643463261</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9262859438200459</v>
+        <v>0.8982043052056512</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.2999997835711037</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476082</v>
+        <v>3.702309454760819</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.528574328364448</v>
+        <v>-4.598778424900434</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8850107531416782</v>
+        <v>0.8569291145272835</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.3684085971164229</v>
@@ -46654,10 +46654,10 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.522063361750135</v>
+        <v>-4.592267458286122</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.88521510134172</v>
+        <v>0.8571334627273253</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.3684085971164229</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378108</v>
+        <v>3.709510443378107</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.503025234042838</v>
+        <v>-4.573229330578824</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8893550716328837</v>
+        <v>0.8612734330184892</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.4265922084476175</v>
@@ -46700,10 +46700,10 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.534151865193456</v>
+        <v>-4.604355961729443</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.054486288111317</v>
+        <v>1.026404649496922</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.4265922084476175</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067876</v>
+        <v>3.722447362067875</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.548018626527374</v>
+        <v>-4.618222723063361</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.049772912563883</v>
+        <v>1.021691273949489</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.4644501251814404</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789133</v>
+        <v>3.787425580789131</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.503214454987444</v>
+        <v>-4.573418551523431</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.073703111576781</v>
+        <v>1.045621472962387</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.4644501251814404</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.78150125051992</v>
+        <v>3.781501250519918</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.355471484752441</v>
+        <v>-4.425675581288428</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.211952947462804</v>
+        <v>1.18387130884841</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.2966427679465573</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181182</v>
+        <v>3.80224592918118</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.457486167283663</v>
+        <v>-4.527690263819649</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.173940695981797</v>
+        <v>1.145859057367402</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.2966427679465573</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394742</v>
+        <v>3.80560898539474</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.451333461230878</v>
+        <v>-4.521537557766865</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.177064126794569</v>
+        <v>1.148982488180174</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.290490061893773</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890619</v>
+        <v>3.798239794890617</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.46814275938138</v>
+        <v>-4.538346855917367</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.169420884274478</v>
+        <v>1.141339245660084</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.3072993600442746</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798436</v>
+        <v>3.867362636798434</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.405844760605258</v>
+        <v>-4.476048857141245</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.260675637581748</v>
+        <v>1.232593998967353</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.3072993600442746</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992203</v>
+        <v>3.848729139992201</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.2040545629401</v>
+        <v>-4.274258659476087</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.049972589037209</v>
+        <v>1.021890950422815</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.1092811678751202</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852433</v>
+        <v>3.841444817852431</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.130676465851364</v>
+        <v>-4.200880562387351</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.149614060194879</v>
+        <v>1.121532421580484</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.03590307078638366</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319558</v>
+        <v>3.819063300319556</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.228417010476338</v>
+        <v>-4.298621107012325</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.125145578460933</v>
+        <v>1.097063939846538</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.05179234891936385</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489396</v>
+        <v>3.831819032489395</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.404754770599268</v>
+        <v>-4.474958867135254</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.053146455236433</v>
+        <v>1.025064816622038</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.2281301090422932</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397806</v>
+        <v>3.836411672397804</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.328332724167341</v>
+        <v>-4.398536820703328</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.082206891849132</v>
+        <v>1.054125253234737</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.2281301090422932</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316261</v>
+        <v>3.833513460316259</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.283959592528772</v>
+        <v>-4.354163689064759</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.099819011939996</v>
+        <v>1.071737373325601</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.1837569774037247</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105975</v>
+        <v>3.821562117105973</v>
       </c>
       <c r="C1977" t="n">
         <v>2.808153067403842</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.161125371641605</v>
+        <v>-4.231329468177591</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.143346494433453</v>
+        <v>1.115264855819059</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.1837569774037247</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190333</v>
+        <v>3.833011148190331</v>
       </c>
       <c r="C1978" t="n">
         <v>2.814534824431647</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.113469641080549</v>
+        <v>-4.183673737616536</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.16879054368568</v>
+        <v>1.140708905071285</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.136101246842669</v>
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569625</v>
+        <v>3.822678210569622</v>
       </c>
       <c r="C1979" t="n">
         <v>2.819427197806371</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.040603768773277</v>
+        <v>-4.083155579117781</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.202829265983313</v>
+        <v>1.185808541845512</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.06323537453539663</v>
+        <v>-0.03558308834391444</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.781485973085134</v>
+        <v>2.798077344800023</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.8288088775573</v>
+        <v>3.828808877557298</v>
       </c>
       <c r="C1980" t="n">
         <v>2.806181870282244</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.101270359175667</v>
+        <v>-4.14382216952017</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.16531730229823</v>
+        <v>1.148296578160428</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.1449336912539303</v>
+        <v>-0.1172814050624481</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.719221655529886</v>
+        <v>2.735813027244775</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932775</v>
+        <v>3.816837033932774</v>
       </c>
       <c r="C1981" t="n">
         <v>2.810279572892872</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.056431957567268</v>
+        <v>-4.098983767911772</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.187350365552218</v>
+        <v>1.170329641414416</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.1403902583090608</v>
+        <v>-0.1127379721175786</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.726045417907436</v>
+        <v>2.742636789622325</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.81793235491706</v>
+        <v>3.817932354917058</v>
       </c>
       <c r="C1982" t="n">
         <v>2.81444051252395</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.157190593324266</v>
+        <v>-4.19974240366877</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.151207850880497</v>
+        <v>1.134187126742695</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.2292158270360662</v>
+        <v>-0.2015635408445841</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.676911016302311</v>
+        <v>2.6935023880172</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405969</v>
+        <v>3.826684745405967</v>
       </c>
       <c r="C1983" t="n">
         <v>2.820320115051787</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.112987756238366</v>
+        <v>-4.15553956658287</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.174768588242694</v>
+        <v>1.157747864104892</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1850129899501658</v>
+        <v>-0.1573607037586836</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.709312321081688</v>
+        <v>2.725903692796578</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265654</v>
+        <v>3.838199629265652</v>
       </c>
       <c r="C1984" t="n">
         <v>2.818730115521035</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.149966783901808</v>
+        <v>-4.192518594246312</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.158386977646564</v>
+        <v>1.141366253508763</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.1480390881588353</v>
+        <v>-0.1203868019673531</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.729906662625734</v>
+        <v>2.746498034340624</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284888</v>
+        <v>3.863895080284887</v>
       </c>
       <c r="C1985" t="n">
         <v>2.869977880704075</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.170024862766649</v>
+        <v>-4.212576673111153</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.201611511283668</v>
+        <v>1.184590787145866</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.1480390881588353</v>
+        <v>-0.1203868019673531</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.781154427808774</v>
+        <v>2.797745799523663</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321031</v>
+        <v>3.865338681321029</v>
       </c>
       <c r="C1986" t="n">
         <v>2.868418585298328</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.130094189588759</v>
+        <v>-4.172645999933263</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.216024485149077</v>
+        <v>1.199003761011275</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.1081084149809449</v>
+        <v>-0.08045612878946273</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.803553536309761</v>
+        <v>2.82014490802465</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475148</v>
+        <v>3.864489842475146</v>
       </c>
       <c r="C1987" t="n">
         <v>2.863366813536598</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.079062096866231</v>
+        <v>-4.121613907210735</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.231385550476358</v>
+        <v>1.214364826338556</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.05707632225841697</v>
+        <v>-0.02942403606693478</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.829121020181548</v>
+        <v>2.845712391896437</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404864</v>
+        <v>3.842547360404862</v>
       </c>
       <c r="C1988" t="n">
         <v>2.880554217629303</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.013837915739026</v>
+        <v>-4.05638972608353</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.274662627019945</v>
+        <v>1.257641902882144</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.00814785886878866</v>
+        <v>0.03580014506027085</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.885442932950576</v>
+        <v>2.902034304665465</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882568</v>
+        <v>3.840061186882566</v>
       </c>
       <c r="C1989" t="n">
         <v>2.876515189928583</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.976410895667892</v>
+        <v>-4.018962706012395</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.285594407347679</v>
+        <v>1.268573683209878</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.01339939689797032</v>
+        <v>0.04105168308945251</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.884554828067365</v>
+        <v>2.901146199782255</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992672</v>
+        <v>3.84516980899267</v>
       </c>
       <c r="C1990" t="n">
         <v>2.877771982259823</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.9965225517026</v>
+        <v>-4.039074362047104</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.278806537265036</v>
+        <v>1.261785813127235</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.02442674189538951</v>
+        <v>0.0520790280868717</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.892428027397057</v>
+        <v>2.909019399111947</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636298</v>
+        <v>3.828661445636296</v>
       </c>
       <c r="C1991" t="n">
         <v>3.038329753281034</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.942777737275395</v>
+        <v>-3.985329547619899</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.460862234057129</v>
+        <v>1.443841509919327</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.03449005133585148</v>
+        <v>0.06214233752733367</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.059023784082545</v>
+        <v>3.075615155797434</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957636</v>
+        <v>3.813222820957634</v>
       </c>
       <c r="C1992" t="n">
         <v>3.158442662498851</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.918986168669253</v>
+        <v>-3.961537979013757</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.590491770717403</v>
+        <v>1.573471046579601</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.05828161994199377</v>
+        <v>0.08593390613347596</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.193411634464048</v>
+        <v>3.210003006178937</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998762</v>
+        <v>3.81423072799876</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15015063851271</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.892902084405445</v>
+        <v>-3.935453894749949</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.592633380436785</v>
+        <v>1.575612656298984</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.05828161994199377</v>
+        <v>0.08593390613347596</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.185119610477907</v>
+        <v>3.201710982192796</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896936</v>
+        <v>3.803397818896933</v>
       </c>
       <c r="C1994" t="n">
         <v>3.14834383409649</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.814770903556498</v>
+        <v>-3.857322713901002</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.622079048360143</v>
+        <v>1.605058324222342</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.1324584308256783</v>
+        <v>0.1601107170171605</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.227818892591897</v>
+        <v>3.244410264306786</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959866</v>
+        <v>3.796264143959863</v>
       </c>
       <c r="C1995" t="n">
         <v>3.165898239823281</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.805878442163215</v>
+        <v>-3.848430252507719</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.643190438644248</v>
+        <v>1.626169714506446</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.1324584308256783</v>
+        <v>0.1601107170171605</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.245373298318688</v>
+        <v>3.261964670033578</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945376</v>
+        <v>3.794424941945373</v>
       </c>
       <c r="C1996" t="n">
         <v>3.157753287227865</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.974354559133093</v>
+        <v>-4.016906369477597</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.567655039260881</v>
+        <v>1.550634315123079</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1045105951090975</v>
+        <v>0.1321628813005797</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.220459644293324</v>
+        <v>3.237051016008213</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782718</v>
+        <v>3.795574066782715</v>
       </c>
       <c r="C1997" t="n">
         <v>3.139022984415727</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.27655503027151</v>
+        <v>-3.319106840616013</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.828044547993376</v>
+        <v>1.811023823855574</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.03416253573868683</v>
+        <v>0.06181482193016902</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.159520505858939</v>
+        <v>3.176111877573828</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632648</v>
+        <v>3.784671345632645</v>
       </c>
       <c r="C1998" t="n">
         <v>3.129687006912631</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.253833926588357</v>
+        <v>-3.296385736932861</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.827797011963541</v>
+        <v>1.81077628782574</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.03416253573868683</v>
+        <v>0.06181482193016902</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.150184528355844</v>
+        <v>3.166775900070733</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777686</v>
+        <v>3.783205696777682</v>
       </c>
       <c r="C1999" t="n">
         <v>3.2885931327638</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.252108883298313</v>
+        <v>-3.294660693642817</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.987393155130728</v>
+        <v>1.970372430992926</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.03588757902873058</v>
+        <v>0.06353986522021277</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.310125680181039</v>
+        <v>3.326717051895928</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644424</v>
+        <v>3.779933725644421</v>
       </c>
       <c r="C2000" t="n">
         <v>3.325670955257447</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.406889890076569</v>
+        <v>-3.449441700421072</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.962558574913072</v>
+        <v>1.945537850775271</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.002519904974254472</v>
+        <v>0.03017219116573666</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.327182898242</v>
+        <v>3.34377426995689</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799972</v>
+        <v>3.769443619799968</v>
       </c>
       <c r="C2001" t="n">
         <v>3.322346311246992</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.355454556691909</v>
+        <v>-3.398006367036413</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.979808064256481</v>
+        <v>1.96278734011868</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.05395523835891414</v>
+        <v>0.08160752455039633</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.354719454262341</v>
+        <v>3.37131082597723</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331127</v>
+        <v>3.766673496331124</v>
       </c>
       <c r="C2002" t="n">
         <v>3.332352464891734</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.328503332365421</v>
+        <v>-3.371055142709925</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.000594707631818</v>
+        <v>1.983573983494017</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.06883558438663329</v>
+        <v>0.09648787057811548</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.373653815523714</v>
+        <v>3.390245187238603</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.76805206778412</v>
+        <v>3.768052067784117</v>
       </c>
       <c r="C2003" t="n">
         <v>3.516455597036694</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.464456340421737</v>
+        <v>-3.507008150766241</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.130316636554252</v>
+        <v>2.11329591241645</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.06883558438663329</v>
+        <v>0.09648787057811548</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.557756947668674</v>
+        <v>3.574348319383563</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714434</v>
+        <v>3.74392550571443</v>
       </c>
       <c r="C2004" t="n">
         <v>3.508572291939687</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.486864458226609</v>
+        <v>-3.529416268571113</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.113470084335296</v>
+        <v>2.096449360197494</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.06883558438663329</v>
+        <v>0.09648787057811548</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.549873642571667</v>
+        <v>3.566465014286556</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155044</v>
+        <v>3.719118627155041</v>
       </c>
       <c r="C2005" t="n">
         <v>3.510626291489324</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.639707735642976</v>
+        <v>-3.677422036050513</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.054386772918386</v>
+        <v>2.039301052755372</v>
       </c>
       <c r="F2005" t="n">
-        <v>-0.01491952897283605</v>
+        <v>0.009760861714574021</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.501674574105623</v>
+        <v>3.516482808518069</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161989</v>
+        <v>3.729452285161986</v>
       </c>
       <c r="C2006" t="n">
         <v>3.566880009211171</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.649148661531506</v>
+        <v>-3.686862961939043</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.106864120284822</v>
+        <v>2.091778400121807</v>
       </c>
       <c r="F2006" t="n">
-        <v>-0.01491952897283605</v>
+        <v>0.1321879792579654</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.55792829182747</v>
+        <v>3.646192796765951</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321646</v>
+        <v>3.714941193321643</v>
       </c>
       <c r="C2007" t="n">
         <v>3.569771103756472</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.64786189799195</v>
+        <v>-3.685576198399486</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.110269920245945</v>
+        <v>2.09518420008293</v>
       </c>
       <c r="F2007" t="n">
-        <v>-0.01363276543327946</v>
+        <v>0.133474742797522</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.561591444496505</v>
+        <v>3.649855949434985</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347715</v>
+        <v>3.727898186347711</v>
       </c>
       <c r="C2008" t="n">
         <v>3.567882916650247</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.649418951981241</v>
+        <v>-3.687133252388778</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.107758911544003</v>
+        <v>2.092673191380989</v>
       </c>
       <c r="F2008" t="n">
-        <v>-0.01363276543327946</v>
+        <v>0.133474742797522</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.55970325739028</v>
+        <v>3.647967762328761</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887759</v>
+        <v>3.710654104887755</v>
       </c>
       <c r="C2009" t="n">
         <v>3.56270314625311</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.656690837504706</v>
+        <v>-3.694405137912242</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.09967038693748</v>
+        <v>2.084584666774465</v>
       </c>
       <c r="F2009" t="n">
-        <v>-0.02090465095674421</v>
+        <v>0.1262028572740573</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.550160355679064</v>
+        <v>3.638424860617544</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343077</v>
+        <v>3.712897612343073</v>
       </c>
       <c r="C2010" t="n">
         <v>3.561137156463262</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.654849818446455</v>
+        <v>-3.692564118853991</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.098840804770933</v>
+        <v>2.083755084607918</v>
       </c>
       <c r="F2010" t="n">
-        <v>-0.01963642428527579</v>
+        <v>0.1274710839455257</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.549355301892096</v>
+        <v>3.637619806830577</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647117</v>
+        <v>3.754911907647114</v>
       </c>
       <c r="C2011" t="n">
         <v>3.574210563329181</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.661758523946135</v>
+        <v>-3.699472824353672</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.109150729436979</v>
+        <v>2.094065009273964</v>
       </c>
       <c r="F2011" t="n">
-        <v>-0.01963642428527579</v>
+        <v>0.1274710839455257</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.562428708758016</v>
+        <v>3.650693213696496</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74989685176354</v>
+        <v>3.749896851763537</v>
       </c>
       <c r="C2012" t="n">
         <v>3.574210563329181</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.663320166760995</v>
+        <v>-3.701034467168531</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.108526072311035</v>
+        <v>2.093440352148021</v>
       </c>
       <c r="F2012" t="n">
-        <v>-0.01963642428527579</v>
+        <v>0.1274710839455257</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.562428708758016</v>
+        <v>3.650693213696496</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392123</v>
+        <v>3.715834055392119</v>
       </c>
       <c r="C2013" t="n">
         <v>3.572734604456183</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.691220953870468</v>
+        <v>-3.728935254278004</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.095889798594248</v>
+        <v>2.080804078431234</v>
       </c>
       <c r="F2013" t="n">
-        <v>-0.05423334842821059</v>
+        <v>0.09287415980259089</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.540194595399257</v>
+        <v>3.628459100337737</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.436768009612625</v>
+        <v>3.436123456585796</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.444833860021118</v>
+        <v>3.569499048433381</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.691220953870468</v>
+        <v>-3.68382206272394</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.095889798594248</v>
+        <v>2.095613799030058</v>
       </c>
       <c r="F2014" t="n">
-        <v>-0.05423334842821059</v>
+        <v>0.2284584434337432</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.437897657007486</v>
+        <v>3.706574114493627</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240703.xlsx
+++ b/tame_output/ON/bt/strategyON_20240703.xlsx
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.4%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-530.0%</t>
+          <t>-531.3%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-32.0%</t>
+          <t>-30.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>77.1%</t>
+          <t>80.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-166.7%</t>
+          <t>-167.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-20.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-14.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-201.1%</t>
+          <t>-210.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-80.8%</t>
         </is>
       </c>
     </row>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355688</v>
+        <v>3.311888301355689</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279812</v>
+        <v>3.385382209279813</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440635</v>
+        <v>3.499971739440636</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.490059241608602</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410274</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390432</v>
+        <v>3.763182248390433</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098114</v>
+        <v>3.729969716098115</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493425</v>
+        <v>3.782922533493426</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.243067615442058</v>
+        <v>-7.256325043687905</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.06884167763892846</v>
+        <v>0.06353870634058945</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.431940725828709</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722821</v>
+        <v>3.828551486722822</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.134808478319536</v>
+        <v>-7.148065906565384</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1066774529471322</v>
+        <v>0.1013744816487931</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.431940725828709</v>
@@ -45596,10 +45596,10 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.011517343502406</v>
+        <v>-7.024774771748253</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1534920008845613</v>
+        <v>0.1481890295862223</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.308649591011578</v>
@@ -45619,10 +45619,10 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.990368144598962</v>
+        <v>-7.003625572844809</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1696526586832636</v>
+        <v>0.1643496873849251</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.287500392108135</v>
@@ -45642,10 +45642,10 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.746602702615518</v>
+        <v>-6.759860130861365</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2629395438236921</v>
+        <v>0.2576365725253535</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.287500392108135</v>
@@ -45665,10 +45665,10 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.644839882338223</v>
+        <v>-6.65809731058407</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.305768985854626</v>
+        <v>0.3004660145562874</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.274281323715706</v>
@@ -45688,10 +45688,10 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.394989488389148</v>
+        <v>-6.408246916634996</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3984512184179581</v>
+        <v>0.3931482471196195</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.274281323715706</v>
@@ -45711,10 +45711,10 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.219097395921716</v>
+        <v>-6.232354824167563</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4724071789255797</v>
+        <v>0.4671042076272407</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.274281323715706</v>
@@ -45734,10 +45734,10 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.047650932899253</v>
+        <v>-6.0609083611451</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5543132701891187</v>
+        <v>0.5490102988907801</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.102834860693243</v>
@@ -45757,10 +45757,10 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.973361367160914</v>
+        <v>-5.986618795406761</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5830495741007513</v>
+        <v>0.5777466028024127</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.028545294954904</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.909725624926979</v>
+        <v>-5.922983053172826</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6131986720486426</v>
+        <v>0.6078957007503036</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.9649095527209691</v>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.798298865601059</v>
+        <v>-5.811556293846906</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6389636345628062</v>
+        <v>0.6336606632644672</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.9649095527209691</v>
@@ -45826,10 +45826,10 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.557868368796199</v>
+        <v>-5.571125797042046</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7368789099096276</v>
+        <v>0.731575938611289</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.7244790559161088</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.485625800625004</v>
+        <v>-5.498883228870851</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7697052510129256</v>
+        <v>0.7644022797145871</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.7244790559161088</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.432627478343616</v>
+        <v>-5.445884906589463</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7915831638428208</v>
+        <v>0.7862801925444822</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.66914279691417</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.323822592863889</v>
+        <v>-5.337080021109736</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8321031892547053</v>
+        <v>0.8268002179563663</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.66914279691417</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.103801794826879</v>
+        <v>-5.117059223072726</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9216905454801236</v>
+        <v>0.9163875741817846</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.5279229518461898</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.970934105763601</v>
+        <v>-4.984191534009448</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9907318039072579</v>
+        <v>0.9854288326089191</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.5279229518461898</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.850761022399102</v>
+        <v>-4.86401845064495</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.039946881693359</v>
+        <v>1.03464391039502</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4077498684816908</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577003</v>
+        <v>3.791273551577004</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.706088877299365</v>
+        <v>-4.719346305545212</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.107903842294694</v>
+        <v>1.102600870996355</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.2630777233819534</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.765963704657057</v>
+        <v>-4.779221132902904</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.069991402753043</v>
+        <v>1.064688431454704</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.3229525507396455</v>
@@ -46033,10 +46033,10 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.679164206878049</v>
+        <v>-4.692421635123896</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.127111695187212</v>
+        <v>1.121808723888874</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.3229525507396455</v>
@@ -46056,10 +46056,10 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.681633913339855</v>
+        <v>-4.694891341585702</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.126196213975902</v>
+        <v>1.120893242677564</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.3254222572014517</v>
@@ -46079,10 +46079,10 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.750004099663865</v>
+        <v>-4.763261527909712</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.109855061921</v>
+        <v>1.104552090622661</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.3161465581652367</v>
@@ -46102,10 +46102,10 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.763792152510912</v>
+        <v>-4.777049580756759</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.094776549414073</v>
+        <v>1.089473578115734</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.3161465581652367</v>
@@ -46125,10 +46125,10 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.794785311839617</v>
+        <v>-4.808042740085464</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9070888507229775</v>
+        <v>0.9017858794246387</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.3161465581652367</v>
@@ -46148,10 +46148,10 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.619311052047149</v>
+        <v>-4.632568480292996</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9818457866317527</v>
+        <v>0.9765428153334139</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.3161465581652367</v>
@@ -46171,10 +46171,10 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.730247304688397</v>
+        <v>-4.743504732934245</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9132133143364602</v>
+        <v>0.9079103430381215</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.3161465581652367</v>
@@ -46194,10 +46194,10 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.696583759216115</v>
+        <v>-4.709841187461962</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9298101177452787</v>
+        <v>0.9245071464469399</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.2824830126929549</v>
@@ -46217,10 +46217,10 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.636731140012392</v>
+        <v>-4.649988568258239</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9639235518589002</v>
+        <v>0.9586205805605614</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.2824830126929549</v>
@@ -46240,10 +46240,10 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.550487676986014</v>
+        <v>-4.563745105231861</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9933672076433118</v>
+        <v>0.988064236344973</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.2824830126929549</v>
@@ -46263,10 +46263,10 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.595794496384994</v>
+        <v>-4.609051924630841</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9670202553282454</v>
+        <v>0.9617172840299064</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.3232931757021857</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803198</v>
+        <v>3.7535711658032</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.624827601087295</v>
+        <v>-4.638085029333142</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9559588864804265</v>
+        <v>0.9506559151820877</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3232931757021857</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809505</v>
+        <v>3.733390600809507</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.532017119636436</v>
+        <v>-4.545274547882283</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9223557709521359</v>
+        <v>0.9170527996537972</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.2304826942513263</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560432</v>
+        <v>3.748285816560434</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.576406588965863</v>
+        <v>-4.58966401721171</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9064734591449657</v>
+        <v>0.9011704878466269</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.274872163580754</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472745</v>
+        <v>3.721077195472747</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.463735370729613</v>
+        <v>-4.47699279897546</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9466176549511889</v>
+        <v>0.9413146836528501</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.1622009453445038</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798544</v>
+        <v>3.743047603798546</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.35135836954694</v>
+        <v>-4.364615797792787</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9970597512549253</v>
+        <v>0.9917567799565865</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.1622009453445038</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498872</v>
+        <v>3.689597840498874</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.379138767448293</v>
+        <v>-4.39239619569414</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9974447938629232</v>
+        <v>0.9921418225645844</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.1899813432458569</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705333</v>
+        <v>3.643069621705335</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.462140048473572</v>
+        <v>-4.475397476719419</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8026000014534649</v>
+        <v>0.7972970301551261</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2085522277730306</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729278</v>
+        <v>3.682716310729279</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.570754126916903</v>
+        <v>-4.58401155516275</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8793040307953381</v>
+        <v>0.8740010594969994</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2085522277730306</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190777</v>
+        <v>3.733012441190779</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.53534508866876</v>
+        <v>-4.548602516914607</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9079806721969184</v>
+        <v>0.9026777008985793</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2085522277730306</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913434</v>
+        <v>3.741174069913436</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.496961426110609</v>
+        <v>-4.510218854356456</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9207535785625474</v>
+        <v>0.9154506072642086</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.1701685652148794</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532495</v>
+        <v>3.751147197532497</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.319845096075443</v>
+        <v>-4.33310252432129</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9883291394219158</v>
+        <v>0.983026168123577</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.1701685652148794</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793912</v>
+        <v>3.741328448793914</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.364937340908988</v>
+        <v>-4.378194769154836</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9709756332504105</v>
+        <v>0.9656726619520717</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.2320646083842692</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011245</v>
+        <v>3.750729377011247</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.185561919670221</v>
+        <v>-4.198819347916068</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.036512777052332</v>
+        <v>1.031209805753993</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.07528785021355056</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982239</v>
+        <v>3.716991718982241</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.230576133190826</v>
+        <v>-4.243833561436674</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9993145469756795</v>
+        <v>0.9940115756773407</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.1056367455281552</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509548</v>
+        <v>3.73702660850955</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.497580643463261</v>
+        <v>-4.510838071709109</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8982043052056512</v>
+        <v>0.8929013339073124</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.2999997835711037</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760819</v>
+        <v>3.702309454760821</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.598778424900434</v>
+        <v>-4.612035853146281</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8569291145272835</v>
+        <v>0.8516261432289447</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.3684085971164229</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815464</v>
+        <v>3.705571661815465</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.592267458286122</v>
+        <v>-4.605524886531969</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8571334627273253</v>
+        <v>0.8518304914289865</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.3684085971164229</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378107</v>
+        <v>3.709510443378109</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.573229330578824</v>
+        <v>-4.586486758824671</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8612734330184892</v>
+        <v>0.8559704617201502</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.4265922084476175</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131259</v>
+        <v>3.73106447313126</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.604355961729443</v>
+        <v>-4.61761338997529</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.026404649496922</v>
+        <v>1.021101678198584</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.4265922084476175</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067875</v>
+        <v>3.722447362067877</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.618222723063361</v>
+        <v>-4.631480151309208</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.021691273949489</v>
+        <v>1.01638830265115</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.4644501251814404</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789131</v>
+        <v>3.787425580789133</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.573418551523431</v>
+        <v>-4.586675979769278</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.045621472962387</v>
+        <v>1.040318501664048</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.4644501251814404</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519918</v>
+        <v>3.78150125051992</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.425675581288428</v>
+        <v>-4.438933009534275</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.18387130884841</v>
+        <v>1.178568337550071</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.2966427679465573</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918118</v>
+        <v>3.802245929181182</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.527690263819649</v>
+        <v>-4.540947692065497</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.145859057367402</v>
+        <v>1.140556086069063</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.2966427679465573</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539474</v>
+        <v>3.805608985394742</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.521537557766865</v>
+        <v>-4.534794986012712</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.148982488180174</v>
+        <v>1.143679516881835</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.290490061893773</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890617</v>
+        <v>3.798239794890619</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.538346855917367</v>
+        <v>-4.551604284163214</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.141339245660084</v>
+        <v>1.136036274361745</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.3072993600442746</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798434</v>
+        <v>3.867362636798436</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.476048857141245</v>
+        <v>-4.489306285387092</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.232593998967353</v>
+        <v>1.227291027669015</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.3072993600442746</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992201</v>
+        <v>3.848729139992203</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.274258659476087</v>
+        <v>-4.287516087721934</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.021890950422815</v>
+        <v>1.016587979124476</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.1092811678751202</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852431</v>
+        <v>3.841444817852433</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.200880562387351</v>
+        <v>-4.214137990633198</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.121532421580484</v>
+        <v>1.116229450282145</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.03590307078638366</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319556</v>
+        <v>3.819063300319558</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.298621107012325</v>
+        <v>-4.311878535258172</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.097063939846538</v>
+        <v>1.091760968548199</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.05179234891936385</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489395</v>
+        <v>3.831819032489396</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.474958867135254</v>
+        <v>-4.488216295381101</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.025064816622038</v>
+        <v>1.019761845323699</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.2281301090422932</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397804</v>
+        <v>3.836411672397806</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.398536820703328</v>
+        <v>-4.411794248949175</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.054125253234737</v>
+        <v>1.048822281936399</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.2281301090422932</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316259</v>
+        <v>3.833513460316261</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.354163689064759</v>
+        <v>-4.367421117310606</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.071737373325601</v>
+        <v>1.066434402027262</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.1837569774037247</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105973</v>
+        <v>3.821562117105975</v>
       </c>
       <c r="C1977" t="n">
         <v>2.808153067403842</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.231329468177591</v>
+        <v>-4.244586896423439</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.115264855819059</v>
+        <v>1.10996188452072</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.1837569774037247</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190331</v>
+        <v>3.833011148190333</v>
       </c>
       <c r="C1978" t="n">
         <v>2.814534824431647</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.183673737616536</v>
+        <v>-4.196931165862383</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.140708905071285</v>
+        <v>1.135405933772946</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.136101246842669</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569622</v>
+        <v>3.822678210569626</v>
       </c>
       <c r="C1979" t="n">
         <v>2.819427197806371</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.083155579117781</v>
+        <v>-4.096413007363628</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.185808541845512</v>
+        <v>1.180505570547173</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.03558308834391444</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557298</v>
+        <v>3.828808877557301</v>
       </c>
       <c r="C1980" t="n">
         <v>2.806181870282244</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.14382216952017</v>
+        <v>-4.157079597766018</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.148296578160428</v>
+        <v>1.142993606862089</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.1172814050624481</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932774</v>
+        <v>3.816837033932776</v>
       </c>
       <c r="C1981" t="n">
         <v>2.810279572892872</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.098983767911772</v>
+        <v>-4.112241196157619</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.170329641414416</v>
+        <v>1.165026670116077</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.1127379721175786</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917058</v>
+        <v>3.81793235491706</v>
       </c>
       <c r="C1982" t="n">
         <v>2.81444051252395</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.19974240366877</v>
+        <v>-4.212999831914617</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.134187126742695</v>
+        <v>1.128884155444356</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.2015635408445841</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405967</v>
+        <v>3.826684745405969</v>
       </c>
       <c r="C1983" t="n">
         <v>2.820320115051787</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.15553956658287</v>
+        <v>-4.168796994828717</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.157747864104892</v>
+        <v>1.152444892806553</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.1573607037586836</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265652</v>
+        <v>3.838199629265654</v>
       </c>
       <c r="C1984" t="n">
         <v>2.818730115521035</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.192518594246312</v>
+        <v>-4.205776022492159</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.141366253508763</v>
+        <v>1.136063282210424</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.1203868019673531</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284887</v>
+        <v>3.863895080284888</v>
       </c>
       <c r="C1985" t="n">
         <v>2.869977880704075</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.212576673111153</v>
+        <v>-4.225834101357</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.184590787145866</v>
+        <v>1.179287815847527</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.1203868019673531</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321029</v>
+        <v>3.865338681321031</v>
       </c>
       <c r="C1986" t="n">
         <v>2.868418585298328</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.172645999933263</v>
+        <v>-4.18590342817911</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.199003761011275</v>
+        <v>1.193700789712937</v>
       </c>
       <c r="F1986" t="n">
         <v>-0.08045612878946273</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475146</v>
+        <v>3.864489842475148</v>
       </c>
       <c r="C1987" t="n">
         <v>2.863366813536598</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.121613907210735</v>
+        <v>-4.134871335456582</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.214364826338556</v>
+        <v>1.209061855040218</v>
       </c>
       <c r="F1987" t="n">
         <v>-0.02942403606693478</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404862</v>
+        <v>3.842547360404864</v>
       </c>
       <c r="C1988" t="n">
         <v>2.880554217629303</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.05638972608353</v>
+        <v>-4.069647154329377</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.257641902882144</v>
+        <v>1.252338931583805</v>
       </c>
       <c r="F1988" t="n">
         <v>0.03580014506027085</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882566</v>
+        <v>3.840061186882568</v>
       </c>
       <c r="C1989" t="n">
         <v>2.876515189928583</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.018962706012395</v>
+        <v>-4.032220134258242</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.268573683209878</v>
+        <v>1.263270711911539</v>
       </c>
       <c r="F1989" t="n">
         <v>0.04105168308945251</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899267</v>
+        <v>3.845169808992672</v>
       </c>
       <c r="C1990" t="n">
         <v>2.877771982259823</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.039074362047104</v>
+        <v>-4.052331790292951</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.261785813127235</v>
+        <v>1.256482841828896</v>
       </c>
       <c r="F1990" t="n">
         <v>0.0520790280868717</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636296</v>
+        <v>3.828661445636298</v>
       </c>
       <c r="C1991" t="n">
         <v>3.038329753281034</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.985329547619899</v>
+        <v>-3.998586975865746</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.443841509919327</v>
+        <v>1.438538538620988</v>
       </c>
       <c r="F1991" t="n">
         <v>0.06214233752733367</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957634</v>
+        <v>3.813222820957636</v>
       </c>
       <c r="C1992" t="n">
         <v>3.158442662498851</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.961537979013757</v>
+        <v>-3.974795407259604</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.573471046579601</v>
+        <v>1.568168075281263</v>
       </c>
       <c r="F1992" t="n">
         <v>0.08593390613347596</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799876</v>
+        <v>3.814230727998762</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15015063851271</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.935453894749949</v>
+        <v>-3.948711322995796</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.575612656298984</v>
+        <v>1.570309685000645</v>
       </c>
       <c r="F1993" t="n">
         <v>0.08593390613347596</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896933</v>
+        <v>3.803397818896936</v>
       </c>
       <c r="C1994" t="n">
         <v>3.14834383409649</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.857322713901002</v>
+        <v>-3.870580142146849</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.605058324222342</v>
+        <v>1.599755352924003</v>
       </c>
       <c r="F1994" t="n">
         <v>0.1601107170171605</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959863</v>
+        <v>3.796264143959865</v>
       </c>
       <c r="C1995" t="n">
         <v>3.165898239823281</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.848430252507719</v>
+        <v>-3.861687680753566</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.626169714506446</v>
+        <v>1.620866743208107</v>
       </c>
       <c r="F1995" t="n">
         <v>0.1601107170171605</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945373</v>
+        <v>3.794424941945374</v>
       </c>
       <c r="C1996" t="n">
         <v>3.157753287227865</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.016906369477597</v>
+        <v>-4.030163797723444</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.550634315123079</v>
+        <v>1.54533134382474</v>
       </c>
       <c r="F1996" t="n">
         <v>0.1321628813005797</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782715</v>
+        <v>3.795574066782716</v>
       </c>
       <c r="C1997" t="n">
         <v>3.139022984415727</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.319106840616013</v>
+        <v>-3.33236426886186</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.811023823855574</v>
+        <v>1.805720852557235</v>
       </c>
       <c r="F1997" t="n">
         <v>0.06181482193016902</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632645</v>
+        <v>3.784671345632646</v>
       </c>
       <c r="C1998" t="n">
         <v>3.129687006912631</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.296385736932861</v>
+        <v>-3.309643165178708</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.81077628782574</v>
+        <v>1.805473316527401</v>
       </c>
       <c r="F1998" t="n">
         <v>0.06181482193016902</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777682</v>
+        <v>3.783205696777684</v>
       </c>
       <c r="C1999" t="n">
         <v>3.2885931327638</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.294660693642817</v>
+        <v>-3.307918121888664</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.970372430992926</v>
+        <v>1.965069459694587</v>
       </c>
       <c r="F1999" t="n">
         <v>0.06353986522021277</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644421</v>
+        <v>3.779933725644423</v>
       </c>
       <c r="C2000" t="n">
         <v>3.325670955257447</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.449441700421072</v>
+        <v>-3.46269912866692</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.945537850775271</v>
+        <v>1.940234879476932</v>
       </c>
       <c r="F2000" t="n">
         <v>0.03017219116573666</v>
@@ -47568,16 +47568,16 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799968</v>
+        <v>3.76944361979997</v>
       </c>
       <c r="C2001" t="n">
         <v>3.322346311246992</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.398006367036413</v>
+        <v>-3.41126379528226</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.96278734011868</v>
+        <v>1.957484368820341</v>
       </c>
       <c r="F2001" t="n">
         <v>0.08160752455039633</v>
@@ -47591,16 +47591,16 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331124</v>
+        <v>3.766673496331125</v>
       </c>
       <c r="C2002" t="n">
         <v>3.332352464891734</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.371055142709925</v>
+        <v>-3.384312570955772</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.983573983494017</v>
+        <v>1.978271012195678</v>
       </c>
       <c r="F2002" t="n">
         <v>0.09648787057811548</v>
@@ -47614,16 +47614,16 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784117</v>
+        <v>3.768052067784119</v>
       </c>
       <c r="C2003" t="n">
         <v>3.516455597036694</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.507008150766241</v>
+        <v>-3.520265579012088</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.11329591241645</v>
+        <v>2.107992941118111</v>
       </c>
       <c r="F2003" t="n">
         <v>0.09648787057811548</v>
@@ -47637,16 +47637,16 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.74392550571443</v>
+        <v>3.743925505714432</v>
       </c>
       <c r="C2004" t="n">
         <v>3.508572291939687</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.529416268571113</v>
+        <v>-3.54267369681696</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.096449360197494</v>
+        <v>2.091146388899155</v>
       </c>
       <c r="F2004" t="n">
         <v>0.09648787057811548</v>
@@ -47660,16 +47660,16 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155041</v>
+        <v>3.719118627155042</v>
       </c>
       <c r="C2005" t="n">
         <v>3.510626291489324</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.677422036050513</v>
+        <v>-3.69067946429636</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.039301052755372</v>
+        <v>2.033998081457033</v>
       </c>
       <c r="F2005" t="n">
         <v>0.009760861714574021</v>
@@ -47683,16 +47683,16 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161986</v>
+        <v>3.729452285161988</v>
       </c>
       <c r="C2006" t="n">
         <v>3.566880009211171</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.686862961939043</v>
+        <v>-3.70012039018489</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.091778400121807</v>
+        <v>2.086475428823468</v>
       </c>
       <c r="F2006" t="n">
         <v>0.1321879792579654</v>
@@ -47706,16 +47706,16 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321643</v>
+        <v>3.714941193321645</v>
       </c>
       <c r="C2007" t="n">
         <v>3.569771103756472</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.685576198399486</v>
+        <v>-3.698833626645333</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.09518420008293</v>
+        <v>2.089881228784591</v>
       </c>
       <c r="F2007" t="n">
         <v>0.133474742797522</v>
@@ -47729,16 +47729,16 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347711</v>
+        <v>3.727898186347713</v>
       </c>
       <c r="C2008" t="n">
         <v>3.567882916650247</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.687133252388778</v>
+        <v>-3.700390680634625</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.092673191380989</v>
+        <v>2.08737022008265</v>
       </c>
       <c r="F2008" t="n">
         <v>0.133474742797522</v>
@@ -47752,16 +47752,16 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887755</v>
+        <v>3.710654104887757</v>
       </c>
       <c r="C2009" t="n">
         <v>3.56270314625311</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.694405137912242</v>
+        <v>-3.707662566158089</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.084584666774465</v>
+        <v>2.079281695476126</v>
       </c>
       <c r="F2009" t="n">
         <v>0.1262028572740573</v>
@@ -47775,16 +47775,16 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343073</v>
+        <v>3.712897612343075</v>
       </c>
       <c r="C2010" t="n">
         <v>3.561137156463262</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.692564118853991</v>
+        <v>-3.705821547099838</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.083755084607918</v>
+        <v>2.078452113309579</v>
       </c>
       <c r="F2010" t="n">
         <v>0.1274710839455257</v>
@@ -47798,16 +47798,16 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647114</v>
+        <v>3.754911907647116</v>
       </c>
       <c r="C2011" t="n">
         <v>3.574210563329181</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.699472824353672</v>
+        <v>-3.712730252599519</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.094065009273964</v>
+        <v>2.088762037975626</v>
       </c>
       <c r="F2011" t="n">
         <v>0.1274710839455257</v>
@@ -47821,16 +47821,16 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763537</v>
+        <v>3.749896851763538</v>
       </c>
       <c r="C2012" t="n">
         <v>3.574210563329181</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.701034467168531</v>
+        <v>-3.714291895414378</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.093440352148021</v>
+        <v>2.088137380849682</v>
       </c>
       <c r="F2012" t="n">
         <v>0.1274710839455257</v>
@@ -47844,16 +47844,16 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392119</v>
+        <v>3.715834055392121</v>
       </c>
       <c r="C2013" t="n">
         <v>3.572734604456183</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.728935254278004</v>
+        <v>-3.742192682523851</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.080804078431234</v>
+        <v>2.075501107132895</v>
       </c>
       <c r="F2013" t="n">
         <v>0.09287415980259089</v>
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.436123456585796</v>
+        <v>3.436123456585799</v>
       </c>
       <c r="C2014" t="n">
         <v>3.569499048433381</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.68382206272394</v>
+        <v>-3.697288185927104</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.095613799030058</v>
+        <v>2.090227349748792</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.2284584434337432</v>
+        <v>0.1377786563993381</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.706574114493627</v>
+        <v>3.652166242272985</v>
       </c>
     </row>
   </sheetData>
